--- a/Excel/HalidomConfig.xlsx
+++ b/Excel/HalidomConfig.xlsx
@@ -2975,7 +2975,7 @@
         <v>40000110</v>
       </c>
       <c r="D65" s="1">
-        <v>40000075</v>
+        <v>40000110</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>89</v>
@@ -3001,7 +3001,7 @@
         <v>40000111</v>
       </c>
       <c r="D66" s="1">
-        <v>40000076</v>
+        <v>40000111</v>
       </c>
       <c r="E66" s="1" t="s">
         <v>90</v>
@@ -3027,7 +3027,7 @@
         <v>40000112</v>
       </c>
       <c r="D67" s="1">
-        <v>40000077</v>
+        <v>40000112</v>
       </c>
       <c r="E67" s="1" t="s">
         <v>92</v>
@@ -3053,7 +3053,7 @@
         <v>40000113</v>
       </c>
       <c r="D68" s="1">
-        <v>40000078</v>
+        <v>40000113</v>
       </c>
       <c r="E68" s="1" t="s">
         <v>93</v>
@@ -3079,7 +3079,7 @@
         <v>40000114</v>
       </c>
       <c r="D69" s="1">
-        <v>40000079</v>
+        <v>40000114</v>
       </c>
       <c r="E69" s="1" t="s">
         <v>94</v>
@@ -3111,7 +3111,7 @@
         <v>40000115</v>
       </c>
       <c r="D70" s="1">
-        <v>40000080</v>
+        <v>40000115</v>
       </c>
       <c r="E70" s="1" t="s">
         <v>96</v>
@@ -3128,7 +3128,7 @@
         <v>40000116</v>
       </c>
       <c r="D71" s="1">
-        <v>40000081</v>
+        <v>40000116</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>97</v>
@@ -3145,7 +3145,7 @@
         <v>40000117</v>
       </c>
       <c r="D72" s="1">
-        <v>40000082</v>
+        <v>40000117</v>
       </c>
       <c r="E72" s="1" t="s">
         <v>98</v>
@@ -3162,7 +3162,7 @@
         <v>40000118</v>
       </c>
       <c r="D73" s="1">
-        <v>40000083</v>
+        <v>40000118</v>
       </c>
       <c r="E73" s="1" t="s">
         <v>99</v>
@@ -3179,7 +3179,7 @@
         <v>40000119</v>
       </c>
       <c r="D74" s="1">
-        <v>40000084</v>
+        <v>40000119</v>
       </c>
       <c r="E74" s="1" t="s">
         <v>100</v>
@@ -3196,7 +3196,7 @@
         <v>40000120</v>
       </c>
       <c r="D75" s="1">
-        <v>40000085</v>
+        <v>40000120</v>
       </c>
       <c r="E75" s="1" t="s">
         <v>101</v>
@@ -3213,7 +3213,7 @@
         <v>40000121</v>
       </c>
       <c r="D76" s="1">
-        <v>40000086</v>
+        <v>40000121</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>102</v>
@@ -3230,7 +3230,7 @@
         <v>40000122</v>
       </c>
       <c r="D77" s="1">
-        <v>40000087</v>
+        <v>40000122</v>
       </c>
       <c r="E77" s="1" t="s">
         <v>103</v>
@@ -3247,7 +3247,7 @@
         <v>40000123</v>
       </c>
       <c r="D78" s="1">
-        <v>40000088</v>
+        <v>40000123</v>
       </c>
       <c r="E78" s="1" t="s">
         <v>104</v>
@@ -3264,7 +3264,7 @@
         <v>40000124</v>
       </c>
       <c r="D79" s="1">
-        <v>40000089</v>
+        <v>40000124</v>
       </c>
       <c r="E79" s="1" t="s">
         <v>105</v>
@@ -3281,7 +3281,7 @@
         <v>40000125</v>
       </c>
       <c r="D80" s="1">
-        <v>40000090</v>
+        <v>40000125</v>
       </c>
       <c r="E80" s="1" t="s">
         <v>106</v>
@@ -3298,7 +3298,7 @@
         <v>40000126</v>
       </c>
       <c r="D81" s="1">
-        <v>40000091</v>
+        <v>40000126</v>
       </c>
       <c r="E81" s="1" t="s">
         <v>107</v>
@@ -3315,7 +3315,7 @@
         <v>40000127</v>
       </c>
       <c r="D82" s="1">
-        <v>40000092</v>
+        <v>40000127</v>
       </c>
       <c r="E82" s="1" t="s">
         <v>108</v>
@@ -3332,7 +3332,7 @@
         <v>40000128</v>
       </c>
       <c r="D83" s="1">
-        <v>40000093</v>
+        <v>40000128</v>
       </c>
       <c r="E83" s="1" t="s">
         <v>109</v>
@@ -3349,7 +3349,7 @@
         <v>40000129</v>
       </c>
       <c r="D84" s="1">
-        <v>40000094</v>
+        <v>40000129</v>
       </c>
       <c r="E84" s="1" t="s">
         <v>110</v>
@@ -3366,7 +3366,7 @@
         <v>40000130</v>
       </c>
       <c r="D85" s="1">
-        <v>40000095</v>
+        <v>40000130</v>
       </c>
       <c r="E85" s="1" t="s">
         <v>111</v>
@@ -3383,7 +3383,7 @@
         <v>40000131</v>
       </c>
       <c r="D86" s="1">
-        <v>40000096</v>
+        <v>40000131</v>
       </c>
       <c r="E86" s="1" t="s">
         <v>112</v>
@@ -3400,7 +3400,7 @@
         <v>40000132</v>
       </c>
       <c r="D87" s="1">
-        <v>40000097</v>
+        <v>40000132</v>
       </c>
       <c r="E87" s="1" t="s">
         <v>113</v>
@@ -3417,7 +3417,7 @@
         <v>40000133</v>
       </c>
       <c r="D88" s="1">
-        <v>40000098</v>
+        <v>40000133</v>
       </c>
       <c r="E88" s="1" t="s">
         <v>114</v>
@@ -3434,7 +3434,7 @@
         <v>40000134</v>
       </c>
       <c r="D89" s="1">
-        <v>40000099</v>
+        <v>40000134</v>
       </c>
       <c r="E89" s="1" t="s">
         <v>115</v>
@@ -3451,7 +3451,7 @@
         <v>40000135</v>
       </c>
       <c r="D90" s="1">
-        <v>40000100</v>
+        <v>40000135</v>
       </c>
       <c r="E90" s="1" t="s">
         <v>116</v>
@@ -3468,7 +3468,7 @@
         <v>40000136</v>
       </c>
       <c r="D91" s="1">
-        <v>40000101</v>
+        <v>40000136</v>
       </c>
       <c r="E91" s="1" t="s">
         <v>117</v>
@@ -3485,7 +3485,7 @@
         <v>40000137</v>
       </c>
       <c r="D92" s="1">
-        <v>40000102</v>
+        <v>40000137</v>
       </c>
       <c r="E92" s="1" t="s">
         <v>118</v>
@@ -3502,7 +3502,7 @@
         <v>40000138</v>
       </c>
       <c r="D93" s="1">
-        <v>40000103</v>
+        <v>40000138</v>
       </c>
       <c r="E93" s="1" t="s">
         <v>119</v>
@@ -3519,7 +3519,7 @@
         <v>40000139</v>
       </c>
       <c r="D94" s="1">
-        <v>40000104</v>
+        <v>40000139</v>
       </c>
       <c r="E94" s="1" t="s">
         <v>120</v>

--- a/Excel/HalidomConfig.xlsx
+++ b/Excel/HalidomConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="121">
   <si>
     <t>Id</t>
   </si>
@@ -314,22 +314,22 @@
     <t>地狱蛇胆</t>
   </si>
   <si>
+    <t>地狱狼爪</t>
+  </si>
+  <si>
+    <t>地狱虫皮</t>
+  </si>
+  <si>
+    <t>地狱鹰羽</t>
+  </si>
+  <si>
+    <t>地狱虫角</t>
+  </si>
+  <si>
+    <t>地狱蜈膏</t>
+  </si>
+  <si>
     <t>#</t>
-  </si>
-  <si>
-    <t>地狱狼爪</t>
-  </si>
-  <si>
-    <t>地狱虫皮</t>
-  </si>
-  <si>
-    <t>地狱鹰羽</t>
-  </si>
-  <si>
-    <t>地狱虫角</t>
-  </si>
-  <si>
-    <t>地狱蜈膏</t>
   </si>
   <si>
     <t>地狱虫心</t>
@@ -3100,13 +3100,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="70" customHeight="1" spans="1:5">
-      <c r="A70" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>95</v>
-      </c>
+    <row r="70" customHeight="1" spans="3:10">
       <c r="C70" s="1">
         <v>40000115</v>
       </c>
@@ -3114,16 +3108,25 @@
         <v>40000115</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="71" customHeight="1" spans="1:5">
-      <c r="A71" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B71" s="1" t="s">
-        <v>95</v>
-      </c>
+      <c r="F70" s="1">
+        <v>2004</v>
+      </c>
+      <c r="G70" s="1">
+        <v>7</v>
+      </c>
+      <c r="H70" s="1">
+        <v>7</v>
+      </c>
+      <c r="I70" s="1">
+        <v>4</v>
+      </c>
+      <c r="J70" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="71" customHeight="1" spans="3:10">
       <c r="C71" s="1">
         <v>40000116</v>
       </c>
@@ -3131,16 +3134,25 @@
         <v>40000116</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="72" customHeight="1" spans="1:5">
-      <c r="A72" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>95</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="F71" s="1">
+        <v>2005</v>
+      </c>
+      <c r="G71" s="1">
+        <v>7</v>
+      </c>
+      <c r="H71" s="1">
+        <v>7</v>
+      </c>
+      <c r="I71" s="1">
+        <v>4</v>
+      </c>
+      <c r="J71" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="72" customHeight="1" spans="3:10">
       <c r="C72" s="1">
         <v>40000117</v>
       </c>
@@ -3148,16 +3160,25 @@
         <v>40000117</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="73" customHeight="1" spans="1:5">
-      <c r="A73" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>95</v>
-      </c>
+        <v>97</v>
+      </c>
+      <c r="F72" s="1">
+        <v>2006</v>
+      </c>
+      <c r="G72" s="1">
+        <v>7</v>
+      </c>
+      <c r="H72" s="1">
+        <v>7</v>
+      </c>
+      <c r="I72" s="1">
+        <v>4</v>
+      </c>
+      <c r="J72" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="73" customHeight="1" spans="3:10">
       <c r="C73" s="1">
         <v>40000118</v>
       </c>
@@ -3165,16 +3186,25 @@
         <v>40000118</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="74" customHeight="1" spans="1:5">
-      <c r="A74" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>95</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="F73" s="1">
+        <v>2002</v>
+      </c>
+      <c r="G73" s="1">
+        <v>30</v>
+      </c>
+      <c r="H73" s="1">
+        <v>30</v>
+      </c>
+      <c r="I73" s="1">
+        <v>4</v>
+      </c>
+      <c r="J73" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="74" customHeight="1" spans="3:10">
       <c r="C74" s="1">
         <v>40000119</v>
       </c>
@@ -3182,15 +3212,30 @@
         <v>40000119</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
+      </c>
+      <c r="F74" s="1">
+        <v>2003</v>
+      </c>
+      <c r="G74" s="1">
+        <v>30</v>
+      </c>
+      <c r="H74" s="1">
+        <v>30</v>
+      </c>
+      <c r="I74" s="1">
+        <v>4</v>
+      </c>
+      <c r="J74" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="1:5">
       <c r="A75" s="1" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="C75" s="1">
         <v>40000120</v>
@@ -3204,10 +3249,10 @@
     </row>
     <row r="76" customHeight="1" spans="1:5">
       <c r="A76" s="1" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="C76" s="1">
         <v>40000121</v>
@@ -3221,10 +3266,10 @@
     </row>
     <row r="77" customHeight="1" spans="1:5">
       <c r="A77" s="1" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="C77" s="1">
         <v>40000122</v>
@@ -3238,10 +3283,10 @@
     </row>
     <row r="78" customHeight="1" spans="1:5">
       <c r="A78" s="1" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="C78" s="1">
         <v>40000123</v>
@@ -3255,10 +3300,10 @@
     </row>
     <row r="79" customHeight="1" spans="1:5">
       <c r="A79" s="1" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="C79" s="1">
         <v>40000124</v>
@@ -3272,10 +3317,10 @@
     </row>
     <row r="80" customHeight="1" spans="1:5">
       <c r="A80" s="1" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="C80" s="1">
         <v>40000125</v>
@@ -3289,10 +3334,10 @@
     </row>
     <row r="81" customHeight="1" spans="1:5">
       <c r="A81" s="1" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="C81" s="1">
         <v>40000126</v>
@@ -3306,10 +3351,10 @@
     </row>
     <row r="82" customHeight="1" spans="1:5">
       <c r="A82" s="1" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="C82" s="1">
         <v>40000127</v>
@@ -3323,10 +3368,10 @@
     </row>
     <row r="83" customHeight="1" spans="1:5">
       <c r="A83" s="1" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="C83" s="1">
         <v>40000128</v>
@@ -3340,10 +3385,10 @@
     </row>
     <row r="84" customHeight="1" spans="1:5">
       <c r="A84" s="1" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="C84" s="1">
         <v>40000129</v>
@@ -3357,10 +3402,10 @@
     </row>
     <row r="85" customHeight="1" spans="1:5">
       <c r="A85" s="1" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="C85" s="1">
         <v>40000130</v>
@@ -3374,10 +3419,10 @@
     </row>
     <row r="86" customHeight="1" spans="1:5">
       <c r="A86" s="1" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="C86" s="1">
         <v>40000131</v>
@@ -3391,10 +3436,10 @@
     </row>
     <row r="87" customHeight="1" spans="1:5">
       <c r="A87" s="1" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="C87" s="1">
         <v>40000132</v>
@@ -3408,10 +3453,10 @@
     </row>
     <row r="88" customHeight="1" spans="1:5">
       <c r="A88" s="1" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="C88" s="1">
         <v>40000133</v>
@@ -3425,10 +3470,10 @@
     </row>
     <row r="89" customHeight="1" spans="1:5">
       <c r="A89" s="1" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="C89" s="1">
         <v>40000134</v>
@@ -3442,10 +3487,10 @@
     </row>
     <row r="90" customHeight="1" spans="1:5">
       <c r="A90" s="1" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="C90" s="1">
         <v>40000135</v>
@@ -3459,10 +3504,10 @@
     </row>
     <row r="91" customHeight="1" spans="1:5">
       <c r="A91" s="1" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="C91" s="1">
         <v>40000136</v>
@@ -3476,10 +3521,10 @@
     </row>
     <row r="92" customHeight="1" spans="1:5">
       <c r="A92" s="1" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="C92" s="1">
         <v>40000137</v>
@@ -3493,10 +3538,10 @@
     </row>
     <row r="93" customHeight="1" spans="1:5">
       <c r="A93" s="1" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="C93" s="1">
         <v>40000138</v>
@@ -3510,10 +3555,10 @@
     </row>
     <row r="94" customHeight="1" spans="1:5">
       <c r="A94" s="1" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="C94" s="1">
         <v>40000139</v>

--- a/Excel/HalidomConfig.xlsx
+++ b/Excel/HalidomConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="121">
   <si>
     <t>Id</t>
   </si>
@@ -329,22 +329,22 @@
     <t>地狱蜈膏</t>
   </si>
   <si>
+    <t>地狱虫心</t>
+  </si>
+  <si>
+    <t>地狱龙皮</t>
+  </si>
+  <si>
+    <t>地狱猪皮</t>
+  </si>
+  <si>
+    <t>地狱猪心</t>
+  </si>
+  <si>
+    <t>地狱蝎皮</t>
+  </si>
+  <si>
     <t>#</t>
-  </si>
-  <si>
-    <t>地狱虫心</t>
-  </si>
-  <si>
-    <t>地狱龙皮</t>
-  </si>
-  <si>
-    <t>地狱猪皮</t>
-  </si>
-  <si>
-    <t>地狱猪心</t>
-  </si>
-  <si>
-    <t>地狱蝎皮</t>
   </si>
   <si>
     <t>地狱宝甲</t>
@@ -3230,13 +3230,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="75" customHeight="1" spans="1:5">
-      <c r="A75" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>100</v>
-      </c>
+    <row r="75" customHeight="1" spans="3:10">
       <c r="C75" s="1">
         <v>40000120</v>
       </c>
@@ -3244,16 +3238,25 @@
         <v>40000120</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="76" customHeight="1" spans="1:5">
-      <c r="A76" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B76" s="1" t="s">
-        <v>100</v>
-      </c>
+      <c r="F75" s="1">
+        <v>2001</v>
+      </c>
+      <c r="G75" s="1">
+        <v>7</v>
+      </c>
+      <c r="H75" s="1">
+        <v>7</v>
+      </c>
+      <c r="I75" s="1">
+        <v>4</v>
+      </c>
+      <c r="J75" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="76" customHeight="1" spans="3:10">
       <c r="C76" s="1">
         <v>40000121</v>
       </c>
@@ -3261,16 +3264,25 @@
         <v>40000121</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="77" customHeight="1" spans="1:5">
-      <c r="A77" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>100</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="F76" s="1">
+        <v>2010</v>
+      </c>
+      <c r="G76" s="1">
+        <v>7</v>
+      </c>
+      <c r="H76" s="1">
+        <v>7</v>
+      </c>
+      <c r="I76" s="1">
+        <v>4</v>
+      </c>
+      <c r="J76" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="77" customHeight="1" spans="3:10">
       <c r="C77" s="1">
         <v>40000122</v>
       </c>
@@ -3278,16 +3290,25 @@
         <v>40000122</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="78" customHeight="1" spans="1:5">
-      <c r="A78" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>100</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="F77" s="1">
+        <v>2011</v>
+      </c>
+      <c r="G77" s="1">
+        <v>10</v>
+      </c>
+      <c r="H77" s="1">
+        <v>10</v>
+      </c>
+      <c r="I77" s="1">
+        <v>4</v>
+      </c>
+      <c r="J77" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="78" customHeight="1" spans="3:10">
       <c r="C78" s="1">
         <v>40000123</v>
       </c>
@@ -3295,16 +3316,25 @@
         <v>40000123</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="79" customHeight="1" spans="1:5">
-      <c r="A79" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="B79" s="1" t="s">
-        <v>100</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="F78" s="1">
+        <v>2003</v>
+      </c>
+      <c r="G78" s="1">
+        <v>30</v>
+      </c>
+      <c r="H78" s="1">
+        <v>30</v>
+      </c>
+      <c r="I78" s="1">
+        <v>4</v>
+      </c>
+      <c r="J78" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="79" customHeight="1" spans="3:10">
       <c r="C79" s="1">
         <v>40000124</v>
       </c>
@@ -3312,15 +3342,30 @@
         <v>40000124</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
+      </c>
+      <c r="F79" s="1">
+        <v>2002</v>
+      </c>
+      <c r="G79" s="1">
+        <v>30</v>
+      </c>
+      <c r="H79" s="1">
+        <v>30</v>
+      </c>
+      <c r="I79" s="1">
+        <v>4</v>
+      </c>
+      <c r="J79" s="1" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="80" customHeight="1" spans="1:5">
       <c r="A80" s="1" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C80" s="1">
         <v>40000125</v>
@@ -3334,10 +3379,10 @@
     </row>
     <row r="81" customHeight="1" spans="1:5">
       <c r="A81" s="1" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C81" s="1">
         <v>40000126</v>
@@ -3351,10 +3396,10 @@
     </row>
     <row r="82" customHeight="1" spans="1:5">
       <c r="A82" s="1" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C82" s="1">
         <v>40000127</v>
@@ -3368,10 +3413,10 @@
     </row>
     <row r="83" customHeight="1" spans="1:5">
       <c r="A83" s="1" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C83" s="1">
         <v>40000128</v>
@@ -3385,10 +3430,10 @@
     </row>
     <row r="84" customHeight="1" spans="1:5">
       <c r="A84" s="1" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C84" s="1">
         <v>40000129</v>
@@ -3402,10 +3447,10 @@
     </row>
     <row r="85" customHeight="1" spans="1:5">
       <c r="A85" s="1" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C85" s="1">
         <v>40000130</v>
@@ -3419,10 +3464,10 @@
     </row>
     <row r="86" customHeight="1" spans="1:5">
       <c r="A86" s="1" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C86" s="1">
         <v>40000131</v>
@@ -3436,10 +3481,10 @@
     </row>
     <row r="87" customHeight="1" spans="1:5">
       <c r="A87" s="1" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C87" s="1">
         <v>40000132</v>
@@ -3453,10 +3498,10 @@
     </row>
     <row r="88" customHeight="1" spans="1:5">
       <c r="A88" s="1" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C88" s="1">
         <v>40000133</v>
@@ -3470,10 +3515,10 @@
     </row>
     <row r="89" customHeight="1" spans="1:5">
       <c r="A89" s="1" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C89" s="1">
         <v>40000134</v>
@@ -3487,10 +3532,10 @@
     </row>
     <row r="90" customHeight="1" spans="1:5">
       <c r="A90" s="1" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C90" s="1">
         <v>40000135</v>
@@ -3504,10 +3549,10 @@
     </row>
     <row r="91" customHeight="1" spans="1:5">
       <c r="A91" s="1" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C91" s="1">
         <v>40000136</v>
@@ -3521,10 +3566,10 @@
     </row>
     <row r="92" customHeight="1" spans="1:5">
       <c r="A92" s="1" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C92" s="1">
         <v>40000137</v>
@@ -3538,10 +3583,10 @@
     </row>
     <row r="93" customHeight="1" spans="1:5">
       <c r="A93" s="1" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C93" s="1">
         <v>40000138</v>
@@ -3555,10 +3600,10 @@
     </row>
     <row r="94" customHeight="1" spans="1:5">
       <c r="A94" s="1" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C94" s="1">
         <v>40000139</v>

--- a/Excel/HalidomConfig.xlsx
+++ b/Excel/HalidomConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="121">
   <si>
     <t>Id</t>
   </si>
@@ -344,22 +344,22 @@
     <t>地狱蝎皮</t>
   </si>
   <si>
+    <t>地狱宝甲</t>
+  </si>
+  <si>
+    <t>地狱号角</t>
+  </si>
+  <si>
+    <t>地狱雕像</t>
+  </si>
+  <si>
+    <t>地狱神像</t>
+  </si>
+  <si>
+    <t>地狱獠牙</t>
+  </si>
+  <si>
     <t>#</t>
-  </si>
-  <si>
-    <t>地狱宝甲</t>
-  </si>
-  <si>
-    <t>地狱号角</t>
-  </si>
-  <si>
-    <t>地狱雕像</t>
-  </si>
-  <si>
-    <t>地狱神像</t>
-  </si>
-  <si>
-    <t>地狱獠牙</t>
   </si>
   <si>
     <t>地狱树心</t>
@@ -3360,13 +3360,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="80" customHeight="1" spans="1:5">
-      <c r="A80" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="B80" s="1" t="s">
-        <v>105</v>
-      </c>
+    <row r="80" customHeight="1" spans="3:10">
       <c r="C80" s="1">
         <v>40000125</v>
       </c>
@@ -3374,16 +3368,25 @@
         <v>40000125</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="81" customHeight="1" spans="1:5">
-      <c r="A81" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B81" s="1" t="s">
-        <v>105</v>
-      </c>
+      <c r="F80" s="1">
+        <v>2004</v>
+      </c>
+      <c r="G80" s="1">
+        <v>7</v>
+      </c>
+      <c r="H80" s="1">
+        <v>7</v>
+      </c>
+      <c r="I80" s="1">
+        <v>4</v>
+      </c>
+      <c r="J80" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="81" customHeight="1" spans="3:10">
       <c r="C81" s="1">
         <v>40000126</v>
       </c>
@@ -3391,16 +3394,25 @@
         <v>40000126</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="82" customHeight="1" spans="1:5">
-      <c r="A82" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="B82" s="1" t="s">
-        <v>105</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="F81" s="1">
+        <v>2005</v>
+      </c>
+      <c r="G81" s="1">
+        <v>7</v>
+      </c>
+      <c r="H81" s="1">
+        <v>7</v>
+      </c>
+      <c r="I81" s="1">
+        <v>4</v>
+      </c>
+      <c r="J81" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="82" customHeight="1" spans="3:10">
       <c r="C82" s="1">
         <v>40000127</v>
       </c>
@@ -3408,16 +3420,25 @@
         <v>40000127</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="83" customHeight="1" spans="1:5">
-      <c r="A83" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>105</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="F82" s="1">
+        <v>2006</v>
+      </c>
+      <c r="G82" s="1">
+        <v>7</v>
+      </c>
+      <c r="H82" s="1">
+        <v>7</v>
+      </c>
+      <c r="I82" s="1">
+        <v>4</v>
+      </c>
+      <c r="J82" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="83" customHeight="1" spans="3:10">
       <c r="C83" s="1">
         <v>40000128</v>
       </c>
@@ -3425,16 +3446,25 @@
         <v>40000128</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="84" customHeight="1" spans="1:5">
-      <c r="A84" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="B84" s="1" t="s">
-        <v>105</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="F83" s="1">
+        <v>2002</v>
+      </c>
+      <c r="G83" s="1">
+        <v>30</v>
+      </c>
+      <c r="H83" s="1">
+        <v>30</v>
+      </c>
+      <c r="I83" s="1">
+        <v>4</v>
+      </c>
+      <c r="J83" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="84" customHeight="1" spans="3:10">
       <c r="C84" s="1">
         <v>40000129</v>
       </c>
@@ -3442,15 +3472,30 @@
         <v>40000129</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
+      </c>
+      <c r="F84" s="1">
+        <v>2003</v>
+      </c>
+      <c r="G84" s="1">
+        <v>30</v>
+      </c>
+      <c r="H84" s="1">
+        <v>30</v>
+      </c>
+      <c r="I84" s="1">
+        <v>4</v>
+      </c>
+      <c r="J84" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="85" customHeight="1" spans="1:5">
       <c r="A85" s="1" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C85" s="1">
         <v>40000130</v>
@@ -3464,10 +3509,10 @@
     </row>
     <row r="86" customHeight="1" spans="1:5">
       <c r="A86" s="1" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C86" s="1">
         <v>40000131</v>
@@ -3481,10 +3526,10 @@
     </row>
     <row r="87" customHeight="1" spans="1:5">
       <c r="A87" s="1" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C87" s="1">
         <v>40000132</v>
@@ -3498,10 +3543,10 @@
     </row>
     <row r="88" customHeight="1" spans="1:5">
       <c r="A88" s="1" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C88" s="1">
         <v>40000133</v>
@@ -3515,10 +3560,10 @@
     </row>
     <row r="89" customHeight="1" spans="1:5">
       <c r="A89" s="1" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C89" s="1">
         <v>40000134</v>
@@ -3532,10 +3577,10 @@
     </row>
     <row r="90" customHeight="1" spans="1:5">
       <c r="A90" s="1" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C90" s="1">
         <v>40000135</v>
@@ -3549,10 +3594,10 @@
     </row>
     <row r="91" customHeight="1" spans="1:5">
       <c r="A91" s="1" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C91" s="1">
         <v>40000136</v>
@@ -3566,10 +3611,10 @@
     </row>
     <row r="92" customHeight="1" spans="1:5">
       <c r="A92" s="1" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C92" s="1">
         <v>40000137</v>
@@ -3583,10 +3628,10 @@
     </row>
     <row r="93" customHeight="1" spans="1:5">
       <c r="A93" s="1" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C93" s="1">
         <v>40000138</v>
@@ -3600,10 +3645,10 @@
     </row>
     <row r="94" customHeight="1" spans="1:5">
       <c r="A94" s="1" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C94" s="1">
         <v>40000139</v>

--- a/Excel/HalidomConfig.xlsx
+++ b/Excel/HalidomConfig.xlsx
@@ -359,22 +359,22 @@
     <t>地狱獠牙</t>
   </si>
   <si>
+    <t>地狱树心</t>
+  </si>
+  <si>
+    <t>地狱魔心</t>
+  </si>
+  <si>
+    <t>地狱尸心</t>
+  </si>
+  <si>
+    <t>地狱法杖</t>
+  </si>
+  <si>
+    <t>地狱权杖</t>
+  </si>
+  <si>
     <t>#</t>
-  </si>
-  <si>
-    <t>地狱树心</t>
-  </si>
-  <si>
-    <t>地狱魔心</t>
-  </si>
-  <si>
-    <t>地狱尸心</t>
-  </si>
-  <si>
-    <t>地狱法杖</t>
-  </si>
-  <si>
-    <t>地狱权杖</t>
   </si>
   <si>
     <t>地狱战锤</t>
@@ -3490,13 +3490,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="85" customHeight="1" spans="1:5">
-      <c r="A85" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="B85" s="1" t="s">
-        <v>110</v>
-      </c>
+    <row r="85" customHeight="1" spans="3:10">
       <c r="C85" s="1">
         <v>40000130</v>
       </c>
@@ -3504,16 +3498,25 @@
         <v>40000130</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="86" customHeight="1" spans="1:5">
-      <c r="A86" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="B86" s="1" t="s">
-        <v>110</v>
-      </c>
+      <c r="F85" s="1">
+        <v>2001</v>
+      </c>
+      <c r="G85" s="1">
+        <v>7</v>
+      </c>
+      <c r="H85" s="1">
+        <v>7</v>
+      </c>
+      <c r="I85" s="1">
+        <v>4</v>
+      </c>
+      <c r="J85" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="86" customHeight="1" spans="3:10">
       <c r="C86" s="1">
         <v>40000131</v>
       </c>
@@ -3521,16 +3524,25 @@
         <v>40000131</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="87" customHeight="1" spans="1:5">
-      <c r="A87" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="B87" s="1" t="s">
-        <v>110</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="F86" s="1">
+        <v>2002</v>
+      </c>
+      <c r="G86" s="1">
+        <v>30</v>
+      </c>
+      <c r="H86" s="1">
+        <v>30</v>
+      </c>
+      <c r="I86" s="1">
+        <v>4</v>
+      </c>
+      <c r="J86" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="87" customHeight="1" spans="3:10">
       <c r="C87" s="1">
         <v>40000132</v>
       </c>
@@ -3538,16 +3550,25 @@
         <v>40000132</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="88" customHeight="1" spans="1:5">
-      <c r="A88" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="B88" s="1" t="s">
-        <v>110</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="F87" s="1">
+        <v>2011</v>
+      </c>
+      <c r="G87" s="1">
+        <v>7</v>
+      </c>
+      <c r="H87" s="1">
+        <v>7</v>
+      </c>
+      <c r="I87" s="1">
+        <v>4</v>
+      </c>
+      <c r="J87" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="88" customHeight="1" spans="3:10">
       <c r="C88" s="1">
         <v>40000133</v>
       </c>
@@ -3555,16 +3576,25 @@
         <v>40000133</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="89" customHeight="1" spans="1:5">
-      <c r="A89" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="B89" s="1" t="s">
-        <v>110</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="F88" s="1">
+        <v>2003</v>
+      </c>
+      <c r="G88" s="1">
+        <v>30</v>
+      </c>
+      <c r="H88" s="1">
+        <v>30</v>
+      </c>
+      <c r="I88" s="1">
+        <v>4</v>
+      </c>
+      <c r="J88" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="89" customHeight="1" spans="3:10">
       <c r="C89" s="1">
         <v>40000134</v>
       </c>
@@ -3572,15 +3602,30 @@
         <v>40000134</v>
       </c>
       <c r="E89" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="F89" s="1">
+        <v>2002</v>
+      </c>
+      <c r="G89" s="1">
+        <v>30</v>
+      </c>
+      <c r="H89" s="1">
+        <v>30</v>
+      </c>
+      <c r="I89" s="1">
+        <v>4</v>
+      </c>
+      <c r="J89" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="90" customHeight="1" spans="1:10">
+      <c r="A90" s="1" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="90" customHeight="1" spans="1:5">
-      <c r="A90" s="1" t="s">
-        <v>110</v>
-      </c>
       <c r="B90" s="1" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="C90" s="1">
         <v>40000135</v>
@@ -3591,13 +3636,28 @@
       <c r="E90" s="1" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="91" customHeight="1" spans="1:5">
+      <c r="F90" s="1">
+        <v>2004</v>
+      </c>
+      <c r="G90" s="1">
+        <v>7</v>
+      </c>
+      <c r="H90" s="1">
+        <v>7</v>
+      </c>
+      <c r="I90" s="1">
+        <v>4</v>
+      </c>
+      <c r="J90" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="91" customHeight="1" spans="1:10">
       <c r="A91" s="1" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="C91" s="1">
         <v>40000136</v>
@@ -3608,13 +3668,28 @@
       <c r="E91" s="1" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="92" customHeight="1" spans="1:5">
+      <c r="F91" s="1">
+        <v>2005</v>
+      </c>
+      <c r="G91" s="1">
+        <v>7</v>
+      </c>
+      <c r="H91" s="1">
+        <v>7</v>
+      </c>
+      <c r="I91" s="1">
+        <v>4</v>
+      </c>
+      <c r="J91" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="92" customHeight="1" spans="1:10">
       <c r="A92" s="1" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="C92" s="1">
         <v>40000137</v>
@@ -3625,13 +3700,28 @@
       <c r="E92" s="1" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="93" customHeight="1" spans="1:5">
+      <c r="F92" s="1">
+        <v>2006</v>
+      </c>
+      <c r="G92" s="1">
+        <v>7</v>
+      </c>
+      <c r="H92" s="1">
+        <v>7</v>
+      </c>
+      <c r="I92" s="1">
+        <v>4</v>
+      </c>
+      <c r="J92" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="93" customHeight="1" spans="1:10">
       <c r="A93" s="1" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="C93" s="1">
         <v>40000138</v>
@@ -3642,13 +3732,28 @@
       <c r="E93" s="1" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="94" customHeight="1" spans="1:5">
+      <c r="F93" s="1">
+        <v>2002</v>
+      </c>
+      <c r="G93" s="1">
+        <v>30</v>
+      </c>
+      <c r="H93" s="1">
+        <v>30</v>
+      </c>
+      <c r="I93" s="1">
+        <v>4</v>
+      </c>
+      <c r="J93" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="94" customHeight="1" spans="1:10">
       <c r="A94" s="1" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="C94" s="1">
         <v>40000139</v>
@@ -3658,6 +3763,21 @@
       </c>
       <c r="E94" s="1" t="s">
         <v>120</v>
+      </c>
+      <c r="F94" s="1">
+        <v>2003</v>
+      </c>
+      <c r="G94" s="1">
+        <v>30</v>
+      </c>
+      <c r="H94" s="1">
+        <v>30</v>
+      </c>
+      <c r="I94" s="1">
+        <v>4</v>
+      </c>
+      <c r="J94" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/HalidomConfig.xlsx
+++ b/Excel/HalidomConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="120">
   <si>
     <t>Id</t>
   </si>
@@ -372,9 +372,6 @@
   </si>
   <si>
     <t>地狱权杖</t>
-  </si>
-  <si>
-    <t>#</t>
   </si>
   <si>
     <t>地狱战锤</t>
@@ -1347,7 +1344,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:J94"/>
+  <dimension ref="C3:J94"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -3620,13 +3617,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="90" customHeight="1" spans="1:10">
-      <c r="A90" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="B90" s="1" t="s">
-        <v>115</v>
-      </c>
+    <row r="90" customHeight="1" spans="3:10">
       <c r="C90" s="1">
         <v>40000135</v>
       </c>
@@ -3634,7 +3625,7 @@
         <v>40000135</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F90" s="1">
         <v>2004</v>
@@ -3652,13 +3643,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="91" customHeight="1" spans="1:10">
-      <c r="A91" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="B91" s="1" t="s">
-        <v>115</v>
-      </c>
+    <row r="91" customHeight="1" spans="3:10">
       <c r="C91" s="1">
         <v>40000136</v>
       </c>
@@ -3666,7 +3651,7 @@
         <v>40000136</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F91" s="1">
         <v>2005</v>
@@ -3684,13 +3669,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="92" customHeight="1" spans="1:10">
-      <c r="A92" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="B92" s="1" t="s">
-        <v>115</v>
-      </c>
+    <row r="92" customHeight="1" spans="3:10">
       <c r="C92" s="1">
         <v>40000137</v>
       </c>
@@ -3698,7 +3677,7 @@
         <v>40000137</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F92" s="1">
         <v>2006</v>
@@ -3716,13 +3695,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="93" customHeight="1" spans="1:10">
-      <c r="A93" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="B93" s="1" t="s">
-        <v>115</v>
-      </c>
+    <row r="93" customHeight="1" spans="3:10">
       <c r="C93" s="1">
         <v>40000138</v>
       </c>
@@ -3730,7 +3703,7 @@
         <v>40000138</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F93" s="1">
         <v>2002</v>
@@ -3748,13 +3721,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="94" customHeight="1" spans="1:10">
-      <c r="A94" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="B94" s="1" t="s">
-        <v>115</v>
-      </c>
+    <row r="94" customHeight="1" spans="3:10">
       <c r="C94" s="1">
         <v>40000139</v>
       </c>
@@ -3762,7 +3729,7 @@
         <v>40000139</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F94" s="1">
         <v>2003</v>

--- a/Excel/HalidomConfig.xlsx
+++ b/Excel/HalidomConfig.xlsx
@@ -27,12 +27,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="121">
   <si>
     <t>Id</t>
   </si>
   <si>
     <t>ItemId</t>
+  </si>
+  <si>
+    <t>Level</t>
   </si>
   <si>
     <t>Name</t>
@@ -1344,18 +1347,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:J94"/>
+  <dimension ref="C3:K94"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
-    <col min="1" max="4" width="9" style="1"/>
-    <col min="5" max="5" width="12.625" style="1" customWidth="1"/>
-    <col min="6" max="8" width="12.25" style="1" customWidth="1"/>
-    <col min="9" max="9" width="11.125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="26.75" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="9" style="1"/>
+    <col min="1" max="5" width="9" style="1"/>
+    <col min="6" max="6" width="12.625" style="1" customWidth="1"/>
+    <col min="7" max="9" width="12.25" style="1" customWidth="1"/>
+    <col min="10" max="10" width="11.125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="26.75" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:10">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C3" s="2" t="s">
         <v>0</v>
       </c>
@@ -1380,8 +1383,11 @@
       <c r="J3" s="2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="K3" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C4" s="2" t="s">
         <v>0</v>
       </c>
@@ -1406,2350 +1412,2623 @@
       <c r="J4" s="2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="K4" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>9</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="K5" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C6" s="1">
         <v>40000051</v>
       </c>
       <c r="D6" s="1">
         <v>40000051</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" s="1">
+      <c r="E6" s="1">
         <v>1</v>
       </c>
+      <c r="F6" s="1" t="s">
+        <v>12</v>
+      </c>
       <c r="G6" s="1">
-        <v>800000000</v>
+        <v>1</v>
       </c>
       <c r="H6" s="1">
         <v>800000000</v>
       </c>
       <c r="I6" s="1">
-        <v>4</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:10">
+        <v>800000000</v>
+      </c>
+      <c r="J6" s="1">
+        <v>4</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C7" s="1">
         <v>40000052</v>
       </c>
       <c r="D7" s="1">
         <v>40000052</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F7" s="1">
+      <c r="E7" s="1">
+        <v>2</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7" s="1">
         <v>15</v>
-      </c>
-      <c r="G7" s="1">
-        <v>100</v>
       </c>
       <c r="H7" s="1">
         <v>100</v>
       </c>
       <c r="I7" s="1">
-        <v>4</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:10">
+        <v>100</v>
+      </c>
+      <c r="J7" s="1">
+        <v>4</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C8" s="1">
         <v>40000053</v>
       </c>
       <c r="D8" s="1">
         <v>40000053</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F8" s="1">
+      <c r="E8" s="1">
+        <v>3</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8" s="1">
         <v>2003</v>
-      </c>
-      <c r="G8" s="1">
-        <v>5</v>
       </c>
       <c r="H8" s="1">
         <v>5</v>
       </c>
       <c r="I8" s="1">
-        <v>4</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:10">
+        <v>5</v>
+      </c>
+      <c r="J8" s="1">
+        <v>4</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C9" s="1">
         <v>40000054</v>
       </c>
       <c r="D9" s="1">
         <v>40000054</v>
       </c>
-      <c r="E9" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F9" s="1">
+      <c r="E9" s="1">
+        <v>4</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G9" s="1">
         <v>5</v>
-      </c>
-      <c r="G9" s="1">
-        <v>80000000</v>
       </c>
       <c r="H9" s="1">
         <v>80000000</v>
       </c>
       <c r="I9" s="1">
-        <v>4</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:10">
+        <v>80000000</v>
+      </c>
+      <c r="J9" s="1">
+        <v>4</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C10" s="1">
         <v>40000055</v>
       </c>
       <c r="D10" s="1">
         <v>40000055</v>
       </c>
-      <c r="E10" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F10" s="1">
+      <c r="E10" s="1">
+        <v>5</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G10" s="1">
         <v>16</v>
-      </c>
-      <c r="G10" s="1">
-        <v>100</v>
       </c>
       <c r="H10" s="1">
         <v>100</v>
       </c>
       <c r="I10" s="1">
-        <v>4</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:10">
+        <v>100</v>
+      </c>
+      <c r="J10" s="1">
+        <v>4</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C11" s="1">
         <v>40000056</v>
       </c>
       <c r="D11" s="1">
         <v>40000056</v>
       </c>
-      <c r="E11" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F11" s="1">
+      <c r="E11" s="1">
+        <v>6</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G11" s="1">
         <v>2</v>
-      </c>
-      <c r="G11" s="1">
-        <v>150000000</v>
       </c>
       <c r="H11" s="1">
         <v>150000000</v>
       </c>
       <c r="I11" s="1">
-        <v>4</v>
-      </c>
-      <c r="J11" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:10">
+        <v>150000000</v>
+      </c>
+      <c r="J11" s="1">
+        <v>4</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C12" s="1">
         <v>40000057</v>
       </c>
       <c r="D12" s="1">
         <v>40000057</v>
       </c>
-      <c r="E12" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F12" s="1">
+      <c r="E12" s="1">
+        <v>7</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G12" s="1">
         <v>3</v>
-      </c>
-      <c r="G12" s="1">
-        <v>150000000</v>
       </c>
       <c r="H12" s="1">
         <v>150000000</v>
       </c>
       <c r="I12" s="1">
-        <v>4</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="13" customHeight="1" spans="3:10">
+        <v>150000000</v>
+      </c>
+      <c r="J12" s="1">
+        <v>4</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="3:11">
       <c r="C13" s="1">
         <v>40000058</v>
       </c>
       <c r="D13" s="1">
         <v>40000058</v>
       </c>
-      <c r="E13" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F13" s="1">
-        <v>4</v>
+      <c r="E13" s="1">
+        <v>8</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="G13" s="1">
-        <v>150000000</v>
+        <v>4</v>
       </c>
       <c r="H13" s="1">
         <v>150000000</v>
       </c>
       <c r="I13" s="1">
-        <v>4</v>
-      </c>
-      <c r="J13" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="14" customHeight="1" spans="3:10">
+        <v>150000000</v>
+      </c>
+      <c r="J13" s="1">
+        <v>4</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="3:11">
       <c r="C14" s="1">
         <v>40000059</v>
       </c>
       <c r="D14" s="1">
         <v>40000059</v>
       </c>
-      <c r="E14" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F14" s="1">
+      <c r="E14" s="1">
+        <v>9</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G14" s="1">
         <v>5</v>
-      </c>
-      <c r="G14" s="1">
-        <v>100000000</v>
       </c>
       <c r="H14" s="1">
         <v>100000000</v>
       </c>
       <c r="I14" s="1">
-        <v>4</v>
-      </c>
-      <c r="J14" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="15" customHeight="1" spans="3:10">
+        <v>100000000</v>
+      </c>
+      <c r="J14" s="1">
+        <v>4</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="3:11">
       <c r="C15" s="1">
         <v>40000060</v>
       </c>
       <c r="D15" s="1">
         <v>40000060</v>
       </c>
-      <c r="E15" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F15" s="1">
+      <c r="E15" s="1">
+        <v>10</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G15" s="1">
         <v>1</v>
-      </c>
-      <c r="G15" s="1">
-        <v>1000000000</v>
       </c>
       <c r="H15" s="1">
         <v>1000000000</v>
       </c>
       <c r="I15" s="1">
-        <v>4</v>
-      </c>
-      <c r="J15" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="16" customHeight="1" spans="3:10">
+        <v>1000000000</v>
+      </c>
+      <c r="J15" s="1">
+        <v>4</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="3:11">
       <c r="C16" s="1">
         <v>40000061</v>
       </c>
       <c r="D16" s="1">
         <v>40000061</v>
       </c>
-      <c r="E16" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F16" s="1">
+      <c r="E16" s="1">
+        <v>11</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G16" s="1">
         <v>15</v>
-      </c>
-      <c r="G16" s="1">
-        <v>150</v>
       </c>
       <c r="H16" s="1">
         <v>150</v>
       </c>
       <c r="I16" s="1">
-        <v>4</v>
-      </c>
-      <c r="J16" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="17" customHeight="1" spans="3:10">
+        <v>150</v>
+      </c>
+      <c r="J16" s="1">
+        <v>4</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="3:11">
       <c r="C17" s="1">
         <v>40000062</v>
       </c>
       <c r="D17" s="1">
         <v>40000062</v>
       </c>
-      <c r="E17" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F17" s="1">
+      <c r="E17" s="1">
+        <v>12</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G17" s="1">
         <v>2003</v>
-      </c>
-      <c r="G17" s="1">
-        <v>8</v>
       </c>
       <c r="H17" s="1">
         <v>8</v>
       </c>
       <c r="I17" s="1">
-        <v>4</v>
-      </c>
-      <c r="J17" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" customHeight="1" spans="3:10">
+        <v>8</v>
+      </c>
+      <c r="J17" s="1">
+        <v>4</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="3:11">
       <c r="C18" s="1">
         <v>40000063</v>
       </c>
       <c r="D18" s="1">
         <v>40000063</v>
       </c>
-      <c r="E18" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F18" s="1">
+      <c r="E18" s="1">
+        <v>13</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G18" s="1">
         <v>33</v>
-      </c>
-      <c r="G18" s="1">
-        <v>10</v>
       </c>
       <c r="H18" s="1">
         <v>10</v>
       </c>
       <c r="I18" s="1">
-        <v>4</v>
-      </c>
-      <c r="J18" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="19" customHeight="1" spans="3:10">
+        <v>10</v>
+      </c>
+      <c r="J18" s="1">
+        <v>4</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19" customHeight="1" spans="3:11">
       <c r="C19" s="1">
         <v>40000064</v>
       </c>
       <c r="D19" s="1">
         <v>40000064</v>
       </c>
-      <c r="E19" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F19" s="1">
+      <c r="E19" s="1">
+        <v>14</v>
+      </c>
+      <c r="F19" s="1" t="s">
         <v>34</v>
       </c>
       <c r="G19" s="1">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="H19" s="1">
         <v>10</v>
       </c>
       <c r="I19" s="1">
-        <v>4</v>
-      </c>
-      <c r="J19" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="20" customHeight="1" spans="3:10">
+        <v>10</v>
+      </c>
+      <c r="J19" s="1">
+        <v>4</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="3:11">
       <c r="C20" s="1">
         <v>40000065</v>
       </c>
       <c r="D20" s="1">
         <v>40000065</v>
       </c>
-      <c r="E20" s="1" t="s">
+      <c r="E20" s="1">
+        <v>15</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G20" s="1">
         <v>35</v>
-      </c>
-      <c r="F20" s="1">
-        <v>35</v>
-      </c>
-      <c r="G20" s="1">
-        <v>10</v>
       </c>
       <c r="H20" s="1">
         <v>10</v>
       </c>
       <c r="I20" s="1">
-        <v>4</v>
-      </c>
-      <c r="J20" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="21" customHeight="1" spans="3:10">
+        <v>10</v>
+      </c>
+      <c r="J20" s="1">
+        <v>4</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="3:11">
       <c r="C21" s="1">
         <v>40000066</v>
       </c>
       <c r="D21" s="1">
         <v>40000066</v>
       </c>
-      <c r="E21" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F21" s="1">
+      <c r="E21" s="1">
+        <v>16</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G21" s="1">
         <v>1</v>
-      </c>
-      <c r="G21" s="1">
-        <v>1500000000</v>
       </c>
       <c r="H21" s="1">
         <v>1500000000</v>
       </c>
       <c r="I21" s="1">
-        <v>4</v>
-      </c>
-      <c r="J21" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="22" customHeight="1" spans="3:10">
+        <v>1500000000</v>
+      </c>
+      <c r="J21" s="1">
+        <v>4</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" customHeight="1" spans="3:11">
       <c r="C22" s="1">
         <v>40000067</v>
       </c>
       <c r="D22" s="1">
         <v>40000067</v>
       </c>
-      <c r="E22" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F22" s="1">
+      <c r="E22" s="1">
+        <v>17</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G22" s="1">
         <v>2003</v>
-      </c>
-      <c r="G22" s="1">
-        <v>10</v>
       </c>
       <c r="H22" s="1">
         <v>10</v>
       </c>
       <c r="I22" s="1">
-        <v>4</v>
-      </c>
-      <c r="J22" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="23" customHeight="1" spans="3:10">
+        <v>10</v>
+      </c>
+      <c r="J22" s="1">
+        <v>4</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" spans="3:11">
       <c r="C23" s="1">
         <v>40000068</v>
       </c>
       <c r="D23" s="1">
         <v>40000068</v>
       </c>
-      <c r="E23" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F23" s="1">
+      <c r="E23" s="1">
+        <v>18</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G23" s="1">
         <v>2011</v>
-      </c>
-      <c r="G23" s="1">
-        <v>10</v>
       </c>
       <c r="H23" s="1">
         <v>10</v>
       </c>
       <c r="I23" s="1">
-        <v>4</v>
-      </c>
-      <c r="J23" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="24" customHeight="1" spans="3:10">
+        <v>10</v>
+      </c>
+      <c r="J23" s="1">
+        <v>4</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="24" customHeight="1" spans="3:11">
       <c r="C24" s="1">
         <v>40000069</v>
       </c>
       <c r="D24" s="1">
         <v>40000069</v>
       </c>
-      <c r="E24" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F24" s="1">
+      <c r="E24" s="1">
+        <v>19</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G24" s="1">
         <v>2004</v>
-      </c>
-      <c r="G24" s="1">
-        <v>5</v>
       </c>
       <c r="H24" s="1">
         <v>5</v>
       </c>
       <c r="I24" s="1">
-        <v>4</v>
-      </c>
-      <c r="J24" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="25" customHeight="1" spans="3:10">
+        <v>5</v>
+      </c>
+      <c r="J24" s="1">
+        <v>4</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="25" customHeight="1" spans="3:11">
       <c r="C25" s="1">
         <v>40000070</v>
       </c>
       <c r="D25" s="1">
         <v>40000070</v>
       </c>
-      <c r="E25" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F25" s="1">
+      <c r="E25" s="1">
+        <v>20</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G25" s="1">
         <v>2005</v>
-      </c>
-      <c r="G25" s="1">
-        <v>5</v>
       </c>
       <c r="H25" s="1">
         <v>5</v>
       </c>
       <c r="I25" s="1">
-        <v>4</v>
-      </c>
-      <c r="J25" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="26" customHeight="1" spans="3:10">
+        <v>5</v>
+      </c>
+      <c r="J25" s="1">
+        <v>4</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="26" customHeight="1" spans="3:11">
       <c r="C26" s="1">
         <v>40000071</v>
       </c>
       <c r="D26" s="1">
         <v>40000071</v>
       </c>
-      <c r="E26" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="F26" s="1">
+      <c r="E26" s="1">
+        <v>21</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G26" s="1">
         <v>2006</v>
-      </c>
-      <c r="G26" s="1">
-        <v>5</v>
       </c>
       <c r="H26" s="1">
         <v>5</v>
       </c>
       <c r="I26" s="1">
-        <v>4</v>
-      </c>
-      <c r="J26" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="27" customHeight="1" spans="3:10">
+        <v>5</v>
+      </c>
+      <c r="J26" s="1">
+        <v>4</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="27" customHeight="1" spans="3:11">
       <c r="C27" s="1">
         <v>40000072</v>
       </c>
       <c r="D27" s="1">
         <v>40000072</v>
       </c>
-      <c r="E27" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F27" s="1">
+      <c r="E27" s="1">
+        <v>22</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G27" s="1">
         <v>2003</v>
-      </c>
-      <c r="G27" s="1">
-        <v>20</v>
       </c>
       <c r="H27" s="1">
         <v>20</v>
       </c>
       <c r="I27" s="1">
-        <v>4</v>
-      </c>
-      <c r="J27" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="28" customHeight="1" spans="3:10">
+        <v>20</v>
+      </c>
+      <c r="J27" s="1">
+        <v>4</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="3:11">
       <c r="C28" s="1">
         <v>40000073</v>
       </c>
       <c r="D28" s="1">
         <v>40000073</v>
       </c>
-      <c r="E28" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F28" s="1">
+      <c r="E28" s="1">
+        <v>23</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="G28" s="1">
         <v>2002</v>
-      </c>
-      <c r="G28" s="1">
-        <v>10</v>
       </c>
       <c r="H28" s="1">
         <v>10</v>
       </c>
       <c r="I28" s="1">
-        <v>4</v>
-      </c>
-      <c r="J28" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="29" customHeight="1" spans="3:10">
+        <v>10</v>
+      </c>
+      <c r="J28" s="1">
+        <v>4</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="29" customHeight="1" spans="3:11">
       <c r="C29" s="1">
         <v>40000074</v>
       </c>
       <c r="D29" s="1">
         <v>40000074</v>
       </c>
-      <c r="E29" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="F29" s="1">
+      <c r="E29" s="1">
+        <v>24</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="G29" s="1">
         <v>2001</v>
-      </c>
-      <c r="G29" s="1">
-        <v>5</v>
       </c>
       <c r="H29" s="1">
         <v>5</v>
       </c>
       <c r="I29" s="1">
-        <v>4</v>
-      </c>
-      <c r="J29" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="30" customHeight="1" spans="3:10">
+        <v>5</v>
+      </c>
+      <c r="J29" s="1">
+        <v>4</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="30" customHeight="1" spans="3:11">
       <c r="C30" s="1">
         <v>40000075</v>
       </c>
       <c r="D30" s="1">
         <v>40000075</v>
       </c>
-      <c r="E30" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="F30" s="1">
+      <c r="E30" s="1">
+        <v>25</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G30" s="1">
         <v>1</v>
-      </c>
-      <c r="G30" s="1">
-        <v>5000000000</v>
       </c>
       <c r="H30" s="1">
         <v>5000000000</v>
       </c>
       <c r="I30" s="1">
-        <v>4</v>
-      </c>
-      <c r="J30" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="31" customHeight="1" spans="3:10">
+        <v>5000000000</v>
+      </c>
+      <c r="J30" s="1">
+        <v>4</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="31" customHeight="1" spans="3:11">
       <c r="C31" s="1">
         <v>40000076</v>
       </c>
       <c r="D31" s="1">
         <v>40000076</v>
       </c>
-      <c r="E31" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="F31" s="1">
+      <c r="E31" s="1">
+        <v>26</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G31" s="1">
         <v>15</v>
-      </c>
-      <c r="G31" s="1">
-        <v>200</v>
       </c>
       <c r="H31" s="1">
         <v>200</v>
       </c>
       <c r="I31" s="1">
-        <v>4</v>
-      </c>
-      <c r="J31" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="32" customHeight="1" spans="3:10">
+        <v>200</v>
+      </c>
+      <c r="J31" s="1">
+        <v>4</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="32" customHeight="1" spans="3:11">
       <c r="C32" s="1">
         <v>40000077</v>
       </c>
       <c r="D32" s="1">
         <v>40000077</v>
       </c>
-      <c r="E32" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F32" s="1">
+      <c r="E32" s="1">
+        <v>27</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G32" s="1">
         <v>2003</v>
-      </c>
-      <c r="G32" s="1">
-        <v>25</v>
       </c>
       <c r="H32" s="1">
         <v>25</v>
       </c>
       <c r="I32" s="1">
-        <v>4</v>
-      </c>
-      <c r="J32" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="33" customHeight="1" spans="3:10">
+        <v>25</v>
+      </c>
+      <c r="J32" s="1">
+        <v>4</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="33" customHeight="1" spans="3:11">
       <c r="C33" s="1">
         <v>40000078</v>
       </c>
       <c r="D33" s="1">
         <v>40000078</v>
       </c>
-      <c r="E33" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F33" s="1">
+      <c r="E33" s="1">
+        <v>28</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="G33" s="1">
         <v>5</v>
-      </c>
-      <c r="G33" s="1">
-        <v>500000000</v>
       </c>
       <c r="H33" s="1">
         <v>500000000</v>
       </c>
       <c r="I33" s="1">
-        <v>4</v>
-      </c>
-      <c r="J33" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="34" customHeight="1" spans="3:10">
+        <v>500000000</v>
+      </c>
+      <c r="J33" s="1">
+        <v>4</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="34" customHeight="1" spans="3:11">
       <c r="C34" s="1">
         <v>40000079</v>
       </c>
       <c r="D34" s="1">
         <v>40000079</v>
       </c>
-      <c r="E34" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="F34" s="1">
+      <c r="E34" s="1">
+        <v>29</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G34" s="1">
         <v>16</v>
-      </c>
-      <c r="G34" s="1">
-        <v>200</v>
       </c>
       <c r="H34" s="1">
         <v>200</v>
       </c>
       <c r="I34" s="1">
-        <v>4</v>
-      </c>
-      <c r="J34" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="35" customHeight="1" spans="3:10">
+        <v>200</v>
+      </c>
+      <c r="J34" s="1">
+        <v>4</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="35" customHeight="1" spans="3:11">
       <c r="C35" s="1">
         <v>40000080</v>
       </c>
       <c r="D35" s="1">
         <v>40000080</v>
       </c>
-      <c r="E35" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="F35" s="1">
+      <c r="E35" s="1">
+        <v>30</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G35" s="1">
         <v>12</v>
-      </c>
-      <c r="G35" s="1">
-        <v>15</v>
       </c>
       <c r="H35" s="1">
         <v>15</v>
       </c>
       <c r="I35" s="1">
-        <v>4</v>
-      </c>
-      <c r="J35" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="36" customHeight="1" spans="3:10">
+        <v>15</v>
+      </c>
+      <c r="J35" s="1">
+        <v>4</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="36" customHeight="1" spans="3:11">
       <c r="C36" s="1">
         <v>40000081</v>
       </c>
       <c r="D36" s="1">
         <v>40000081</v>
       </c>
-      <c r="E36" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="F36" s="1">
+      <c r="E36" s="1">
+        <v>31</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G36" s="1">
         <v>14</v>
-      </c>
-      <c r="G36" s="1">
-        <v>200</v>
       </c>
       <c r="H36" s="1">
         <v>200</v>
       </c>
       <c r="I36" s="1">
-        <v>4</v>
-      </c>
-      <c r="J36" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="37" customHeight="1" spans="3:10">
+        <v>200</v>
+      </c>
+      <c r="J36" s="1">
+        <v>4</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="37" customHeight="1" spans="3:11">
       <c r="C37" s="1">
         <v>40000082</v>
       </c>
       <c r="D37" s="1">
         <v>40000082</v>
       </c>
-      <c r="E37" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="F37" s="1">
+      <c r="E37" s="1">
+        <v>32</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="G37" s="1">
         <v>2004</v>
-      </c>
-      <c r="G37" s="1">
-        <v>6</v>
       </c>
       <c r="H37" s="1">
         <v>6</v>
       </c>
       <c r="I37" s="1">
-        <v>4</v>
-      </c>
-      <c r="J37" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="38" customHeight="1" spans="3:10">
+        <v>6</v>
+      </c>
+      <c r="J37" s="1">
+        <v>4</v>
+      </c>
+      <c r="K37" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="38" customHeight="1" spans="3:11">
       <c r="C38" s="1">
         <v>40000083</v>
       </c>
       <c r="D38" s="1">
         <v>40000083</v>
       </c>
-      <c r="E38" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="F38" s="1">
+      <c r="E38" s="1">
+        <v>33</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="G38" s="1">
         <v>2005</v>
-      </c>
-      <c r="G38" s="1">
-        <v>6</v>
       </c>
       <c r="H38" s="1">
         <v>6</v>
       </c>
       <c r="I38" s="1">
-        <v>4</v>
-      </c>
-      <c r="J38" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="39" customHeight="1" spans="3:10">
+        <v>6</v>
+      </c>
+      <c r="J38" s="1">
+        <v>4</v>
+      </c>
+      <c r="K38" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="39" customHeight="1" spans="3:11">
       <c r="C39" s="1">
         <v>40000084</v>
       </c>
       <c r="D39" s="1">
         <v>40000084</v>
       </c>
-      <c r="E39" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="F39" s="1">
+      <c r="E39" s="1">
+        <v>34</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G39" s="1">
         <v>2006</v>
-      </c>
-      <c r="G39" s="1">
-        <v>6</v>
       </c>
       <c r="H39" s="1">
         <v>6</v>
       </c>
       <c r="I39" s="1">
-        <v>4</v>
-      </c>
-      <c r="J39" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="40" customHeight="1" spans="3:10">
+        <v>6</v>
+      </c>
+      <c r="J39" s="1">
+        <v>4</v>
+      </c>
+      <c r="K39" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="40" customHeight="1" spans="3:11">
       <c r="C40" s="1">
         <v>40000085</v>
       </c>
       <c r="D40" s="1">
         <v>40000085</v>
       </c>
-      <c r="E40" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="F40" s="1">
+      <c r="E40" s="1">
+        <v>35</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G40" s="1">
         <v>15</v>
-      </c>
-      <c r="G40" s="1">
-        <v>300</v>
       </c>
       <c r="H40" s="1">
         <v>300</v>
       </c>
       <c r="I40" s="1">
-        <v>4</v>
-      </c>
-      <c r="J40" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="41" customHeight="1" spans="3:10">
+        <v>300</v>
+      </c>
+      <c r="J40" s="1">
+        <v>4</v>
+      </c>
+      <c r="K40" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="41" customHeight="1" spans="3:11">
       <c r="C41" s="1">
         <v>40000086</v>
       </c>
       <c r="D41" s="1">
         <v>40000086</v>
       </c>
-      <c r="E41" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="F41" s="1">
+      <c r="E41" s="1">
+        <v>36</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G41" s="1">
         <v>16</v>
-      </c>
-      <c r="G41" s="1">
-        <v>300</v>
       </c>
       <c r="H41" s="1">
         <v>300</v>
       </c>
       <c r="I41" s="1">
-        <v>4</v>
-      </c>
-      <c r="J41" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="42" customHeight="1" spans="3:10">
+        <v>300</v>
+      </c>
+      <c r="J41" s="1">
+        <v>4</v>
+      </c>
+      <c r="K41" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="42" customHeight="1" spans="3:11">
       <c r="C42" s="1">
         <v>40000087</v>
       </c>
       <c r="D42" s="1">
         <v>40000087</v>
       </c>
-      <c r="E42" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="F42" s="1">
+      <c r="E42" s="1">
+        <v>37</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="G42" s="1">
         <v>2002</v>
-      </c>
-      <c r="G42" s="1">
-        <v>25</v>
       </c>
       <c r="H42" s="1">
         <v>25</v>
       </c>
       <c r="I42" s="1">
-        <v>4</v>
-      </c>
-      <c r="J42" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="43" customHeight="1" spans="3:10">
+        <v>25</v>
+      </c>
+      <c r="J42" s="1">
+        <v>4</v>
+      </c>
+      <c r="K42" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="43" customHeight="1" spans="3:11">
       <c r="C43" s="1">
         <v>40000088</v>
       </c>
       <c r="D43" s="1">
         <v>40000088</v>
       </c>
-      <c r="E43" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="F43" s="1">
+      <c r="E43" s="1">
+        <v>38</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="G43" s="1">
         <v>2003</v>
-      </c>
-      <c r="G43" s="1">
-        <v>25</v>
       </c>
       <c r="H43" s="1">
         <v>25</v>
       </c>
       <c r="I43" s="1">
-        <v>4</v>
-      </c>
-      <c r="J43" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="44" customHeight="1" spans="3:10">
+        <v>25</v>
+      </c>
+      <c r="J43" s="1">
+        <v>4</v>
+      </c>
+      <c r="K43" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="44" customHeight="1" spans="3:11">
       <c r="C44" s="1">
         <v>40000089</v>
       </c>
       <c r="D44" s="1">
         <v>40000089</v>
       </c>
-      <c r="E44" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="F44" s="1">
+      <c r="E44" s="1">
+        <v>39</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G44" s="1">
         <v>2011</v>
-      </c>
-      <c r="G44" s="1">
-        <v>10</v>
       </c>
       <c r="H44" s="1">
         <v>10</v>
       </c>
       <c r="I44" s="1">
-        <v>4</v>
-      </c>
-      <c r="J44" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="45" customHeight="1" spans="3:10">
+        <v>10</v>
+      </c>
+      <c r="J44" s="1">
+        <v>4</v>
+      </c>
+      <c r="K44" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="45" customHeight="1" spans="3:11">
       <c r="C45" s="1">
         <v>40000090</v>
       </c>
       <c r="D45" s="1">
         <v>40000090</v>
       </c>
-      <c r="E45" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="F45" s="1">
+      <c r="E45" s="1">
+        <v>40</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G45" s="1">
         <v>2004</v>
-      </c>
-      <c r="G45" s="1">
-        <v>5</v>
       </c>
       <c r="H45" s="1">
         <v>5</v>
       </c>
       <c r="I45" s="1">
-        <v>4</v>
-      </c>
-      <c r="J45" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="46" customHeight="1" spans="3:10">
+        <v>5</v>
+      </c>
+      <c r="J45" s="1">
+        <v>4</v>
+      </c>
+      <c r="K45" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="46" customHeight="1" spans="3:11">
       <c r="C46" s="1">
         <v>40000091</v>
       </c>
       <c r="D46" s="1">
         <v>40000091</v>
       </c>
-      <c r="E46" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="F46" s="1">
+      <c r="E46" s="1">
+        <v>41</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G46" s="1">
         <v>2005</v>
-      </c>
-      <c r="G46" s="1">
-        <v>5</v>
       </c>
       <c r="H46" s="1">
         <v>5</v>
       </c>
       <c r="I46" s="1">
-        <v>4</v>
-      </c>
-      <c r="J46" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="47" customHeight="1" spans="3:10">
+        <v>5</v>
+      </c>
+      <c r="J46" s="1">
+        <v>4</v>
+      </c>
+      <c r="K46" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="47" customHeight="1" spans="3:11">
       <c r="C47" s="1">
         <v>40000092</v>
       </c>
       <c r="D47" s="1">
         <v>40000092</v>
       </c>
-      <c r="E47" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="F47" s="1">
+      <c r="E47" s="1">
+        <v>42</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="G47" s="1">
         <v>2006</v>
-      </c>
-      <c r="G47" s="1">
-        <v>5</v>
       </c>
       <c r="H47" s="1">
         <v>5</v>
       </c>
       <c r="I47" s="1">
-        <v>4</v>
-      </c>
-      <c r="J47" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="48" customHeight="1" spans="3:10">
+        <v>5</v>
+      </c>
+      <c r="J47" s="1">
+        <v>4</v>
+      </c>
+      <c r="K47" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="48" customHeight="1" spans="3:11">
       <c r="C48" s="1">
         <v>40000093</v>
       </c>
       <c r="D48" s="1">
         <v>40000093</v>
       </c>
-      <c r="E48" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="F48" s="1">
+      <c r="E48" s="1">
+        <v>43</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G48" s="1">
         <v>2002</v>
-      </c>
-      <c r="G48" s="1">
-        <v>20</v>
       </c>
       <c r="H48" s="1">
         <v>20</v>
       </c>
       <c r="I48" s="1">
-        <v>4</v>
-      </c>
-      <c r="J48" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="49" customHeight="1" spans="3:10">
+        <v>20</v>
+      </c>
+      <c r="J48" s="1">
+        <v>4</v>
+      </c>
+      <c r="K48" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="49" customHeight="1" spans="3:11">
       <c r="C49" s="1">
         <v>40000094</v>
       </c>
       <c r="D49" s="1">
         <v>40000094</v>
       </c>
-      <c r="E49" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="F49" s="1">
+      <c r="E49" s="1">
+        <v>44</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G49" s="1">
         <v>2003</v>
-      </c>
-      <c r="G49" s="1">
-        <v>20</v>
       </c>
       <c r="H49" s="1">
         <v>20</v>
       </c>
       <c r="I49" s="1">
-        <v>4</v>
-      </c>
-      <c r="J49" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="50" customHeight="1" spans="3:10">
+        <v>20</v>
+      </c>
+      <c r="J49" s="1">
+        <v>4</v>
+      </c>
+      <c r="K49" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="50" customHeight="1" spans="3:11">
       <c r="C50" s="1">
         <v>40000095</v>
       </c>
       <c r="D50" s="1">
         <v>40000095</v>
       </c>
-      <c r="E50" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="F50" s="1">
+      <c r="E50" s="1">
+        <v>45</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="G50" s="1">
         <v>15</v>
-      </c>
-      <c r="G50" s="1">
-        <v>500</v>
       </c>
       <c r="H50" s="1">
         <v>500</v>
       </c>
       <c r="I50" s="1">
-        <v>4</v>
-      </c>
-      <c r="J50" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="51" customHeight="1" spans="3:10">
+        <v>500</v>
+      </c>
+      <c r="J50" s="1">
+        <v>4</v>
+      </c>
+      <c r="K50" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="51" customHeight="1" spans="3:11">
       <c r="C51" s="1">
         <v>40000096</v>
       </c>
       <c r="D51" s="1">
         <v>40000096</v>
       </c>
-      <c r="E51" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="F51" s="1">
+      <c r="E51" s="1">
+        <v>46</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G51" s="1">
         <v>16</v>
-      </c>
-      <c r="G51" s="1">
-        <v>500</v>
       </c>
       <c r="H51" s="1">
         <v>500</v>
       </c>
       <c r="I51" s="1">
-        <v>4</v>
-      </c>
-      <c r="J51" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="52" customHeight="1" spans="3:10">
+        <v>500</v>
+      </c>
+      <c r="J51" s="1">
+        <v>4</v>
+      </c>
+      <c r="K51" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="52" customHeight="1" spans="3:11">
       <c r="C52" s="1">
         <v>40000097</v>
       </c>
       <c r="D52" s="1">
         <v>40000097</v>
       </c>
-      <c r="E52" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="F52" s="1">
+      <c r="E52" s="1">
+        <v>47</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G52" s="1">
         <v>2002</v>
-      </c>
-      <c r="G52" s="1">
-        <v>25</v>
       </c>
       <c r="H52" s="1">
         <v>25</v>
       </c>
       <c r="I52" s="1">
-        <v>4</v>
-      </c>
-      <c r="J52" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="53" customHeight="1" spans="3:10">
+        <v>25</v>
+      </c>
+      <c r="J52" s="1">
+        <v>4</v>
+      </c>
+      <c r="K52" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="53" customHeight="1" spans="3:11">
       <c r="C53" s="1">
         <v>40000098</v>
       </c>
       <c r="D53" s="1">
         <v>40000098</v>
       </c>
-      <c r="E53" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="F53" s="1">
+      <c r="E53" s="1">
+        <v>48</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="G53" s="1">
         <v>2003</v>
-      </c>
-      <c r="G53" s="1">
-        <v>25</v>
       </c>
       <c r="H53" s="1">
         <v>25</v>
       </c>
       <c r="I53" s="1">
-        <v>4</v>
-      </c>
-      <c r="J53" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="54" customHeight="1" spans="3:10">
+        <v>25</v>
+      </c>
+      <c r="J53" s="1">
+        <v>4</v>
+      </c>
+      <c r="K53" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="54" customHeight="1" spans="3:11">
       <c r="C54" s="1">
         <v>40000099</v>
       </c>
       <c r="D54" s="1">
         <v>40000099</v>
       </c>
-      <c r="E54" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="F54" s="1">
+      <c r="E54" s="1">
+        <v>49</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="G54" s="1">
         <v>2001</v>
-      </c>
-      <c r="G54" s="1">
-        <v>5</v>
       </c>
       <c r="H54" s="1">
         <v>5</v>
       </c>
       <c r="I54" s="1">
-        <v>4</v>
-      </c>
-      <c r="J54" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="55" customHeight="1" spans="3:10">
+        <v>5</v>
+      </c>
+      <c r="J54" s="1">
+        <v>4</v>
+      </c>
+      <c r="K54" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="55" customHeight="1" spans="3:11">
       <c r="C55" s="1">
         <v>40000100</v>
       </c>
       <c r="D55" s="1">
         <v>40000100</v>
       </c>
-      <c r="E55" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="F55" s="1">
+      <c r="E55" s="1">
+        <v>50</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="G55" s="1">
         <v>2004</v>
-      </c>
-      <c r="G55" s="1">
-        <v>5</v>
       </c>
       <c r="H55" s="1">
         <v>5</v>
       </c>
       <c r="I55" s="1">
-        <v>4</v>
-      </c>
-      <c r="J55" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="56" customHeight="1" spans="3:10">
+        <v>5</v>
+      </c>
+      <c r="J55" s="1">
+        <v>4</v>
+      </c>
+      <c r="K55" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="56" customHeight="1" spans="3:11">
       <c r="C56" s="1">
         <v>40000101</v>
       </c>
       <c r="D56" s="1">
         <v>40000101</v>
       </c>
-      <c r="E56" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="F56" s="1">
+      <c r="E56" s="1">
+        <v>51</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="G56" s="1">
         <v>2003</v>
-      </c>
-      <c r="G56" s="1">
-        <v>25</v>
       </c>
       <c r="H56" s="1">
         <v>25</v>
       </c>
       <c r="I56" s="1">
-        <v>4</v>
-      </c>
-      <c r="J56" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="57" customHeight="1" spans="3:10">
+        <v>25</v>
+      </c>
+      <c r="J56" s="1">
+        <v>4</v>
+      </c>
+      <c r="K56" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="57" customHeight="1" spans="3:11">
       <c r="C57" s="1">
         <v>40000102</v>
       </c>
       <c r="D57" s="1">
         <v>40000102</v>
       </c>
-      <c r="E57" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="F57" s="1">
+      <c r="E57" s="1">
+        <v>52</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G57" s="1">
         <v>2002</v>
-      </c>
-      <c r="G57" s="1">
-        <v>25</v>
       </c>
       <c r="H57" s="1">
         <v>25</v>
       </c>
       <c r="I57" s="1">
-        <v>4</v>
-      </c>
-      <c r="J57" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="58" customHeight="1" spans="3:10">
+        <v>25</v>
+      </c>
+      <c r="J57" s="1">
+        <v>4</v>
+      </c>
+      <c r="K57" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="58" customHeight="1" spans="3:11">
       <c r="C58" s="1">
         <v>40000103</v>
       </c>
       <c r="D58" s="1">
         <v>40000103</v>
       </c>
-      <c r="E58" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="F58" s="1">
+      <c r="E58" s="1">
+        <v>53</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="G58" s="1">
         <v>2011</v>
-      </c>
-      <c r="G58" s="1">
-        <v>10</v>
       </c>
       <c r="H58" s="1">
         <v>10</v>
       </c>
       <c r="I58" s="1">
-        <v>4</v>
-      </c>
-      <c r="J58" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="59" customHeight="1" spans="3:10">
+        <v>10</v>
+      </c>
+      <c r="J58" s="1">
+        <v>4</v>
+      </c>
+      <c r="K58" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="59" customHeight="1" spans="3:11">
       <c r="C59" s="1">
         <v>40000104</v>
       </c>
       <c r="D59" s="1">
         <v>40000104</v>
       </c>
-      <c r="E59" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="F59" s="1">
+      <c r="E59" s="1">
+        <v>54</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="G59" s="1">
         <v>2001</v>
-      </c>
-      <c r="G59" s="1">
-        <v>5</v>
       </c>
       <c r="H59" s="1">
         <v>5</v>
       </c>
       <c r="I59" s="1">
-        <v>4</v>
-      </c>
-      <c r="J59" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="60" customHeight="1" spans="3:10">
+        <v>5</v>
+      </c>
+      <c r="J59" s="1">
+        <v>4</v>
+      </c>
+      <c r="K59" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="60" customHeight="1" spans="3:11">
       <c r="C60" s="1">
         <v>40000105</v>
       </c>
       <c r="D60" s="1">
         <v>40000105</v>
       </c>
-      <c r="E60" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="F60" s="1">
+      <c r="E60" s="1">
+        <v>55</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="G60" s="1">
         <v>2004</v>
-      </c>
-      <c r="G60" s="1">
-        <v>7</v>
       </c>
       <c r="H60" s="1">
         <v>7</v>
       </c>
       <c r="I60" s="1">
-        <v>4</v>
-      </c>
-      <c r="J60" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="61" customHeight="1" spans="3:10">
+        <v>7</v>
+      </c>
+      <c r="J60" s="1">
+        <v>4</v>
+      </c>
+      <c r="K60" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="61" customHeight="1" spans="3:11">
       <c r="C61" s="1">
         <v>40000106</v>
       </c>
       <c r="D61" s="1">
         <v>40000106</v>
       </c>
-      <c r="E61" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="F61" s="1">
+      <c r="E61" s="1">
+        <v>56</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="G61" s="1">
         <v>2005</v>
-      </c>
-      <c r="G61" s="1">
-        <v>7</v>
       </c>
       <c r="H61" s="1">
         <v>7</v>
       </c>
       <c r="I61" s="1">
-        <v>4</v>
-      </c>
-      <c r="J61" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="62" customHeight="1" spans="3:10">
+        <v>7</v>
+      </c>
+      <c r="J61" s="1">
+        <v>4</v>
+      </c>
+      <c r="K61" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="62" customHeight="1" spans="3:11">
       <c r="C62" s="1">
         <v>40000107</v>
       </c>
       <c r="D62" s="1">
         <v>40000107</v>
       </c>
-      <c r="E62" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="F62" s="1">
+      <c r="E62" s="1">
+        <v>57</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G62" s="1">
         <v>2006</v>
-      </c>
-      <c r="G62" s="1">
-        <v>7</v>
       </c>
       <c r="H62" s="1">
         <v>7</v>
       </c>
       <c r="I62" s="1">
-        <v>4</v>
-      </c>
-      <c r="J62" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="63" customHeight="1" spans="3:10">
+        <v>7</v>
+      </c>
+      <c r="J62" s="1">
+        <v>4</v>
+      </c>
+      <c r="K62" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="63" customHeight="1" spans="3:11">
       <c r="C63" s="1">
         <v>40000108</v>
       </c>
       <c r="D63" s="1">
         <v>40000108</v>
       </c>
-      <c r="E63" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="F63" s="1">
+      <c r="E63" s="1">
+        <v>58</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="G63" s="1">
         <v>2003</v>
-      </c>
-      <c r="G63" s="1">
-        <v>30</v>
       </c>
       <c r="H63" s="1">
         <v>30</v>
       </c>
       <c r="I63" s="1">
-        <v>4</v>
-      </c>
-      <c r="J63" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="64" customHeight="1" spans="3:10">
+        <v>30</v>
+      </c>
+      <c r="J63" s="1">
+        <v>4</v>
+      </c>
+      <c r="K63" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="64" customHeight="1" spans="3:11">
       <c r="C64" s="1">
         <v>40000109</v>
       </c>
       <c r="D64" s="1">
         <v>40000109</v>
       </c>
-      <c r="E64" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="F64" s="1">
+      <c r="E64" s="1">
+        <v>59</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="G64" s="1">
         <v>2002</v>
-      </c>
-      <c r="G64" s="1">
-        <v>30</v>
       </c>
       <c r="H64" s="1">
         <v>30</v>
       </c>
       <c r="I64" s="1">
-        <v>4</v>
-      </c>
-      <c r="J64" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="65" customHeight="1" spans="3:10">
+        <v>30</v>
+      </c>
+      <c r="J64" s="1">
+        <v>4</v>
+      </c>
+      <c r="K64" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="65" customHeight="1" spans="3:11">
       <c r="C65" s="1">
         <v>40000110</v>
       </c>
       <c r="D65" s="1">
         <v>40000110</v>
       </c>
-      <c r="E65" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="F65" s="1">
+      <c r="E65" s="1">
+        <v>60</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G65" s="1">
         <v>2001</v>
-      </c>
-      <c r="G65" s="1">
-        <v>7</v>
       </c>
       <c r="H65" s="1">
         <v>7</v>
       </c>
       <c r="I65" s="1">
-        <v>4</v>
-      </c>
-      <c r="J65" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="66" customHeight="1" spans="3:10">
+        <v>7</v>
+      </c>
+      <c r="J65" s="1">
+        <v>4</v>
+      </c>
+      <c r="K65" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="66" customHeight="1" spans="3:11">
       <c r="C66" s="1">
         <v>40000111</v>
       </c>
       <c r="D66" s="1">
         <v>40000111</v>
       </c>
-      <c r="E66" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="F66" s="1">
+      <c r="E66" s="1">
+        <v>61</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="G66" s="1">
         <v>2010</v>
-      </c>
-      <c r="G66" s="1">
-        <v>7</v>
       </c>
       <c r="H66" s="1">
         <v>7</v>
       </c>
       <c r="I66" s="1">
-        <v>4</v>
-      </c>
-      <c r="J66" s="1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="67" customHeight="1" spans="3:10">
+        <v>7</v>
+      </c>
+      <c r="J66" s="1">
+        <v>4</v>
+      </c>
+      <c r="K66" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="67" customHeight="1" spans="3:11">
       <c r="C67" s="1">
         <v>40000112</v>
       </c>
       <c r="D67" s="1">
         <v>40000112</v>
       </c>
-      <c r="E67" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="F67" s="1">
+      <c r="E67" s="1">
+        <v>62</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="G67" s="1">
         <v>2011</v>
-      </c>
-      <c r="G67" s="1">
-        <v>10</v>
       </c>
       <c r="H67" s="1">
         <v>10</v>
       </c>
       <c r="I67" s="1">
-        <v>4</v>
-      </c>
-      <c r="J67" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="68" customHeight="1" spans="3:10">
+        <v>10</v>
+      </c>
+      <c r="J67" s="1">
+        <v>4</v>
+      </c>
+      <c r="K67" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="68" customHeight="1" spans="3:11">
       <c r="C68" s="1">
         <v>40000113</v>
       </c>
       <c r="D68" s="1">
         <v>40000113</v>
       </c>
-      <c r="E68" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="F68" s="1">
+      <c r="E68" s="1">
+        <v>63</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="G68" s="1">
         <v>2002</v>
-      </c>
-      <c r="G68" s="1">
-        <v>30</v>
       </c>
       <c r="H68" s="1">
         <v>30</v>
       </c>
       <c r="I68" s="1">
-        <v>4</v>
-      </c>
-      <c r="J68" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="69" customHeight="1" spans="3:10">
+        <v>30</v>
+      </c>
+      <c r="J68" s="1">
+        <v>4</v>
+      </c>
+      <c r="K68" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="69" customHeight="1" spans="3:11">
       <c r="C69" s="1">
         <v>40000114</v>
       </c>
       <c r="D69" s="1">
         <v>40000114</v>
       </c>
-      <c r="E69" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="F69" s="1">
+      <c r="E69" s="1">
+        <v>64</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="G69" s="1">
         <v>2003</v>
-      </c>
-      <c r="G69" s="1">
-        <v>30</v>
       </c>
       <c r="H69" s="1">
         <v>30</v>
       </c>
       <c r="I69" s="1">
-        <v>4</v>
-      </c>
-      <c r="J69" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="70" customHeight="1" spans="3:10">
+        <v>30</v>
+      </c>
+      <c r="J69" s="1">
+        <v>4</v>
+      </c>
+      <c r="K69" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="70" customHeight="1" spans="3:11">
       <c r="C70" s="1">
         <v>40000115</v>
       </c>
       <c r="D70" s="1">
         <v>40000115</v>
       </c>
-      <c r="E70" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="F70" s="1">
+      <c r="E70" s="1">
+        <v>65</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="G70" s="1">
         <v>2004</v>
-      </c>
-      <c r="G70" s="1">
-        <v>7</v>
       </c>
       <c r="H70" s="1">
         <v>7</v>
       </c>
       <c r="I70" s="1">
-        <v>4</v>
-      </c>
-      <c r="J70" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="71" customHeight="1" spans="3:10">
+        <v>7</v>
+      </c>
+      <c r="J70" s="1">
+        <v>4</v>
+      </c>
+      <c r="K70" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="71" customHeight="1" spans="3:11">
       <c r="C71" s="1">
         <v>40000116</v>
       </c>
       <c r="D71" s="1">
         <v>40000116</v>
       </c>
-      <c r="E71" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="F71" s="1">
+      <c r="E71" s="1">
+        <v>66</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="G71" s="1">
         <v>2005</v>
-      </c>
-      <c r="G71" s="1">
-        <v>7</v>
       </c>
       <c r="H71" s="1">
         <v>7</v>
       </c>
       <c r="I71" s="1">
-        <v>4</v>
-      </c>
-      <c r="J71" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="72" customHeight="1" spans="3:10">
+        <v>7</v>
+      </c>
+      <c r="J71" s="1">
+        <v>4</v>
+      </c>
+      <c r="K71" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="72" customHeight="1" spans="3:11">
       <c r="C72" s="1">
         <v>40000117</v>
       </c>
       <c r="D72" s="1">
         <v>40000117</v>
       </c>
-      <c r="E72" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="F72" s="1">
+      <c r="E72" s="1">
+        <v>67</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="G72" s="1">
         <v>2006</v>
-      </c>
-      <c r="G72" s="1">
-        <v>7</v>
       </c>
       <c r="H72" s="1">
         <v>7</v>
       </c>
       <c r="I72" s="1">
-        <v>4</v>
-      </c>
-      <c r="J72" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="73" customHeight="1" spans="3:10">
+        <v>7</v>
+      </c>
+      <c r="J72" s="1">
+        <v>4</v>
+      </c>
+      <c r="K72" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="73" customHeight="1" spans="3:11">
       <c r="C73" s="1">
         <v>40000118</v>
       </c>
       <c r="D73" s="1">
         <v>40000118</v>
       </c>
-      <c r="E73" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="F73" s="1">
+      <c r="E73" s="1">
+        <v>68</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="G73" s="1">
         <v>2002</v>
-      </c>
-      <c r="G73" s="1">
-        <v>30</v>
       </c>
       <c r="H73" s="1">
         <v>30</v>
       </c>
       <c r="I73" s="1">
-        <v>4</v>
-      </c>
-      <c r="J73" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="74" customHeight="1" spans="3:10">
+        <v>30</v>
+      </c>
+      <c r="J73" s="1">
+        <v>4</v>
+      </c>
+      <c r="K73" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="74" customHeight="1" spans="3:11">
       <c r="C74" s="1">
         <v>40000119</v>
       </c>
       <c r="D74" s="1">
         <v>40000119</v>
       </c>
-      <c r="E74" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="F74" s="1">
+      <c r="E74" s="1">
+        <v>69</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="G74" s="1">
         <v>2003</v>
-      </c>
-      <c r="G74" s="1">
-        <v>30</v>
       </c>
       <c r="H74" s="1">
         <v>30</v>
       </c>
       <c r="I74" s="1">
-        <v>4</v>
-      </c>
-      <c r="J74" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="75" customHeight="1" spans="3:10">
+        <v>30</v>
+      </c>
+      <c r="J74" s="1">
+        <v>4</v>
+      </c>
+      <c r="K74" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="75" customHeight="1" spans="3:11">
       <c r="C75" s="1">
         <v>40000120</v>
       </c>
       <c r="D75" s="1">
         <v>40000120</v>
       </c>
-      <c r="E75" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="F75" s="1">
+      <c r="E75" s="1">
+        <v>70</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="G75" s="1">
         <v>2001</v>
-      </c>
-      <c r="G75" s="1">
-        <v>7</v>
       </c>
       <c r="H75" s="1">
         <v>7</v>
       </c>
       <c r="I75" s="1">
-        <v>4</v>
-      </c>
-      <c r="J75" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="76" customHeight="1" spans="3:10">
+        <v>7</v>
+      </c>
+      <c r="J75" s="1">
+        <v>4</v>
+      </c>
+      <c r="K75" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="76" customHeight="1" spans="3:11">
       <c r="C76" s="1">
         <v>40000121</v>
       </c>
       <c r="D76" s="1">
         <v>40000121</v>
       </c>
-      <c r="E76" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="F76" s="1">
+      <c r="E76" s="1">
+        <v>71</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="G76" s="1">
         <v>2010</v>
-      </c>
-      <c r="G76" s="1">
-        <v>7</v>
       </c>
       <c r="H76" s="1">
         <v>7</v>
       </c>
       <c r="I76" s="1">
-        <v>4</v>
-      </c>
-      <c r="J76" s="1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="77" customHeight="1" spans="3:10">
+        <v>7</v>
+      </c>
+      <c r="J76" s="1">
+        <v>4</v>
+      </c>
+      <c r="K76" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="77" customHeight="1" spans="3:11">
       <c r="C77" s="1">
         <v>40000122</v>
       </c>
       <c r="D77" s="1">
         <v>40000122</v>
       </c>
-      <c r="E77" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="F77" s="1">
+      <c r="E77" s="1">
+        <v>72</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="G77" s="1">
         <v>2011</v>
-      </c>
-      <c r="G77" s="1">
-        <v>10</v>
       </c>
       <c r="H77" s="1">
         <v>10</v>
       </c>
       <c r="I77" s="1">
-        <v>4</v>
-      </c>
-      <c r="J77" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="78" customHeight="1" spans="3:10">
+        <v>10</v>
+      </c>
+      <c r="J77" s="1">
+        <v>4</v>
+      </c>
+      <c r="K77" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="78" customHeight="1" spans="3:11">
       <c r="C78" s="1">
         <v>40000123</v>
       </c>
       <c r="D78" s="1">
         <v>40000123</v>
       </c>
-      <c r="E78" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="F78" s="1">
+      <c r="E78" s="1">
+        <v>73</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="G78" s="1">
         <v>2003</v>
-      </c>
-      <c r="G78" s="1">
-        <v>30</v>
       </c>
       <c r="H78" s="1">
         <v>30</v>
       </c>
       <c r="I78" s="1">
-        <v>4</v>
-      </c>
-      <c r="J78" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="79" customHeight="1" spans="3:10">
+        <v>30</v>
+      </c>
+      <c r="J78" s="1">
+        <v>4</v>
+      </c>
+      <c r="K78" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="79" customHeight="1" spans="3:11">
       <c r="C79" s="1">
         <v>40000124</v>
       </c>
       <c r="D79" s="1">
         <v>40000124</v>
       </c>
-      <c r="E79" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="F79" s="1">
+      <c r="E79" s="1">
+        <v>74</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="G79" s="1">
         <v>2002</v>
-      </c>
-      <c r="G79" s="1">
-        <v>30</v>
       </c>
       <c r="H79" s="1">
         <v>30</v>
       </c>
       <c r="I79" s="1">
-        <v>4</v>
-      </c>
-      <c r="J79" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="80" customHeight="1" spans="3:10">
+        <v>30</v>
+      </c>
+      <c r="J79" s="1">
+        <v>4</v>
+      </c>
+      <c r="K79" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="80" customHeight="1" spans="3:11">
       <c r="C80" s="1">
         <v>40000125</v>
       </c>
       <c r="D80" s="1">
         <v>40000125</v>
       </c>
-      <c r="E80" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="F80" s="1">
+      <c r="E80" s="1">
+        <v>75</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="G80" s="1">
         <v>2004</v>
-      </c>
-      <c r="G80" s="1">
-        <v>7</v>
       </c>
       <c r="H80" s="1">
         <v>7</v>
       </c>
       <c r="I80" s="1">
-        <v>4</v>
-      </c>
-      <c r="J80" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="81" customHeight="1" spans="3:10">
+        <v>7</v>
+      </c>
+      <c r="J80" s="1">
+        <v>4</v>
+      </c>
+      <c r="K80" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="81" customHeight="1" spans="3:11">
       <c r="C81" s="1">
         <v>40000126</v>
       </c>
       <c r="D81" s="1">
         <v>40000126</v>
       </c>
-      <c r="E81" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="F81" s="1">
+      <c r="E81" s="1">
+        <v>76</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="G81" s="1">
         <v>2005</v>
-      </c>
-      <c r="G81" s="1">
-        <v>7</v>
       </c>
       <c r="H81" s="1">
         <v>7</v>
       </c>
       <c r="I81" s="1">
-        <v>4</v>
-      </c>
-      <c r="J81" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="82" customHeight="1" spans="3:10">
+        <v>7</v>
+      </c>
+      <c r="J81" s="1">
+        <v>4</v>
+      </c>
+      <c r="K81" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="82" customHeight="1" spans="3:11">
       <c r="C82" s="1">
         <v>40000127</v>
       </c>
       <c r="D82" s="1">
         <v>40000127</v>
       </c>
-      <c r="E82" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="F82" s="1">
+      <c r="E82" s="1">
+        <v>77</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="G82" s="1">
         <v>2006</v>
-      </c>
-      <c r="G82" s="1">
-        <v>7</v>
       </c>
       <c r="H82" s="1">
         <v>7</v>
       </c>
       <c r="I82" s="1">
-        <v>4</v>
-      </c>
-      <c r="J82" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="83" customHeight="1" spans="3:10">
+        <v>7</v>
+      </c>
+      <c r="J82" s="1">
+        <v>4</v>
+      </c>
+      <c r="K82" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="83" customHeight="1" spans="3:11">
       <c r="C83" s="1">
         <v>40000128</v>
       </c>
       <c r="D83" s="1">
         <v>40000128</v>
       </c>
-      <c r="E83" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="F83" s="1">
+      <c r="E83" s="1">
+        <v>78</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="G83" s="1">
         <v>2002</v>
-      </c>
-      <c r="G83" s="1">
-        <v>30</v>
       </c>
       <c r="H83" s="1">
         <v>30</v>
       </c>
       <c r="I83" s="1">
-        <v>4</v>
-      </c>
-      <c r="J83" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="84" customHeight="1" spans="3:10">
+        <v>30</v>
+      </c>
+      <c r="J83" s="1">
+        <v>4</v>
+      </c>
+      <c r="K83" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="84" customHeight="1" spans="3:11">
       <c r="C84" s="1">
         <v>40000129</v>
       </c>
       <c r="D84" s="1">
         <v>40000129</v>
       </c>
-      <c r="E84" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="F84" s="1">
+      <c r="E84" s="1">
+        <v>79</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="G84" s="1">
         <v>2003</v>
-      </c>
-      <c r="G84" s="1">
-        <v>30</v>
       </c>
       <c r="H84" s="1">
         <v>30</v>
       </c>
       <c r="I84" s="1">
-        <v>4</v>
-      </c>
-      <c r="J84" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="85" customHeight="1" spans="3:10">
+        <v>30</v>
+      </c>
+      <c r="J84" s="1">
+        <v>4</v>
+      </c>
+      <c r="K84" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="85" customHeight="1" spans="3:11">
       <c r="C85" s="1">
         <v>40000130</v>
       </c>
       <c r="D85" s="1">
         <v>40000130</v>
       </c>
-      <c r="E85" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="F85" s="1">
+      <c r="E85" s="1">
+        <v>80</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G85" s="1">
         <v>2001</v>
-      </c>
-      <c r="G85" s="1">
-        <v>7</v>
       </c>
       <c r="H85" s="1">
         <v>7</v>
       </c>
       <c r="I85" s="1">
-        <v>4</v>
-      </c>
-      <c r="J85" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="86" customHeight="1" spans="3:10">
+        <v>7</v>
+      </c>
+      <c r="J85" s="1">
+        <v>4</v>
+      </c>
+      <c r="K85" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="86" customHeight="1" spans="3:11">
       <c r="C86" s="1">
         <v>40000131</v>
       </c>
       <c r="D86" s="1">
         <v>40000131</v>
       </c>
-      <c r="E86" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="F86" s="1">
+      <c r="E86" s="1">
+        <v>81</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="G86" s="1">
         <v>2002</v>
-      </c>
-      <c r="G86" s="1">
-        <v>30</v>
       </c>
       <c r="H86" s="1">
         <v>30</v>
       </c>
       <c r="I86" s="1">
-        <v>4</v>
-      </c>
-      <c r="J86" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="87" customHeight="1" spans="3:10">
+        <v>30</v>
+      </c>
+      <c r="J86" s="1">
+        <v>4</v>
+      </c>
+      <c r="K86" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="87" customHeight="1" spans="3:11">
       <c r="C87" s="1">
         <v>40000132</v>
       </c>
       <c r="D87" s="1">
         <v>40000132</v>
       </c>
-      <c r="E87" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="F87" s="1">
+      <c r="E87" s="1">
+        <v>82</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="G87" s="1">
         <v>2011</v>
-      </c>
-      <c r="G87" s="1">
-        <v>7</v>
       </c>
       <c r="H87" s="1">
         <v>7</v>
       </c>
       <c r="I87" s="1">
-        <v>4</v>
-      </c>
-      <c r="J87" s="1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="88" customHeight="1" spans="3:10">
+        <v>7</v>
+      </c>
+      <c r="J87" s="1">
+        <v>4</v>
+      </c>
+      <c r="K87" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="88" customHeight="1" spans="3:11">
       <c r="C88" s="1">
         <v>40000133</v>
       </c>
       <c r="D88" s="1">
         <v>40000133</v>
       </c>
-      <c r="E88" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="F88" s="1">
+      <c r="E88" s="1">
+        <v>83</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="G88" s="1">
         <v>2003</v>
-      </c>
-      <c r="G88" s="1">
-        <v>30</v>
       </c>
       <c r="H88" s="1">
         <v>30</v>
       </c>
       <c r="I88" s="1">
-        <v>4</v>
-      </c>
-      <c r="J88" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="89" customHeight="1" spans="3:10">
+        <v>30</v>
+      </c>
+      <c r="J88" s="1">
+        <v>4</v>
+      </c>
+      <c r="K88" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="89" customHeight="1" spans="3:11">
       <c r="C89" s="1">
         <v>40000134</v>
       </c>
       <c r="D89" s="1">
         <v>40000134</v>
       </c>
-      <c r="E89" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="F89" s="1">
+      <c r="E89" s="1">
+        <v>84</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="G89" s="1">
         <v>2002</v>
-      </c>
-      <c r="G89" s="1">
-        <v>30</v>
       </c>
       <c r="H89" s="1">
         <v>30</v>
       </c>
       <c r="I89" s="1">
-        <v>4</v>
-      </c>
-      <c r="J89" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="90" customHeight="1" spans="3:10">
+        <v>30</v>
+      </c>
+      <c r="J89" s="1">
+        <v>4</v>
+      </c>
+      <c r="K89" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="90" customHeight="1" spans="3:11">
       <c r="C90" s="1">
         <v>40000135</v>
       </c>
       <c r="D90" s="1">
         <v>40000135</v>
       </c>
-      <c r="E90" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="F90" s="1">
+      <c r="E90" s="1">
+        <v>85</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="G90" s="1">
         <v>2004</v>
-      </c>
-      <c r="G90" s="1">
-        <v>7</v>
       </c>
       <c r="H90" s="1">
         <v>7</v>
       </c>
       <c r="I90" s="1">
-        <v>4</v>
-      </c>
-      <c r="J90" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="91" customHeight="1" spans="3:10">
+        <v>7</v>
+      </c>
+      <c r="J90" s="1">
+        <v>4</v>
+      </c>
+      <c r="K90" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="91" customHeight="1" spans="3:11">
       <c r="C91" s="1">
         <v>40000136</v>
       </c>
       <c r="D91" s="1">
         <v>40000136</v>
       </c>
-      <c r="E91" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="F91" s="1">
+      <c r="E91" s="1">
+        <v>86</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G91" s="1">
         <v>2005</v>
-      </c>
-      <c r="G91" s="1">
-        <v>7</v>
       </c>
       <c r="H91" s="1">
         <v>7</v>
       </c>
       <c r="I91" s="1">
-        <v>4</v>
-      </c>
-      <c r="J91" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="92" customHeight="1" spans="3:10">
+        <v>7</v>
+      </c>
+      <c r="J91" s="1">
+        <v>4</v>
+      </c>
+      <c r="K91" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="92" customHeight="1" spans="3:11">
       <c r="C92" s="1">
         <v>40000137</v>
       </c>
       <c r="D92" s="1">
         <v>40000137</v>
       </c>
-      <c r="E92" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="F92" s="1">
+      <c r="E92" s="1">
+        <v>87</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="G92" s="1">
         <v>2006</v>
-      </c>
-      <c r="G92" s="1">
-        <v>7</v>
       </c>
       <c r="H92" s="1">
         <v>7</v>
       </c>
       <c r="I92" s="1">
-        <v>4</v>
-      </c>
-      <c r="J92" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="93" customHeight="1" spans="3:10">
+        <v>7</v>
+      </c>
+      <c r="J92" s="1">
+        <v>4</v>
+      </c>
+      <c r="K92" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="93" customHeight="1" spans="3:11">
       <c r="C93" s="1">
         <v>40000138</v>
       </c>
       <c r="D93" s="1">
         <v>40000138</v>
       </c>
-      <c r="E93" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="F93" s="1">
+      <c r="E93" s="1">
+        <v>88</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="G93" s="1">
         <v>2002</v>
-      </c>
-      <c r="G93" s="1">
-        <v>30</v>
       </c>
       <c r="H93" s="1">
         <v>30</v>
       </c>
       <c r="I93" s="1">
-        <v>4</v>
-      </c>
-      <c r="J93" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="94" customHeight="1" spans="3:10">
+        <v>30</v>
+      </c>
+      <c r="J93" s="1">
+        <v>4</v>
+      </c>
+      <c r="K93" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="94" customHeight="1" spans="3:11">
       <c r="C94" s="1">
         <v>40000139</v>
       </c>
       <c r="D94" s="1">
         <v>40000139</v>
       </c>
-      <c r="E94" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="F94" s="1">
+      <c r="E94" s="1">
+        <v>89</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="G94" s="1">
         <v>2003</v>
-      </c>
-      <c r="G94" s="1">
-        <v>30</v>
       </c>
       <c r="H94" s="1">
         <v>30</v>
       </c>
       <c r="I94" s="1">
-        <v>4</v>
-      </c>
-      <c r="J94" s="1" t="s">
-        <v>16</v>
+        <v>30</v>
+      </c>
+      <c r="J94" s="1">
+        <v>4</v>
+      </c>
+      <c r="K94" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:E5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3 E4 E5 F3:F5 C3:D5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/HalidomConfig.xlsx
+++ b/Excel/HalidomConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="162">
   <si>
     <t>Id</t>
   </si>
@@ -35,27 +35,30 @@
     <t>ItemId</t>
   </si>
   <si>
+    <t>Layer</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>AttrId</t>
+  </si>
+  <si>
+    <t>AttrValue</t>
+  </si>
+  <si>
+    <t>RiseAttr</t>
+  </si>
+  <si>
+    <t>MaxLevel</t>
+  </si>
+  <si>
+    <t>Des</t>
+  </si>
+  <si>
     <t>Level</t>
   </si>
   <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>AttrId</t>
-  </si>
-  <si>
-    <t>AttrValue</t>
-  </si>
-  <si>
-    <t>RiseAttr</t>
-  </si>
-  <si>
-    <t>MaxLevel</t>
-  </si>
-  <si>
-    <t>Des</t>
-  </si>
-  <si>
     <t>int</t>
   </si>
   <si>
@@ -390,6 +393,126 @@
   </si>
   <si>
     <t>地狱龙爪</t>
+  </si>
+  <si>
+    <t>深渊鸡爪</t>
+  </si>
+  <si>
+    <t>深渊鹿茸</t>
+  </si>
+  <si>
+    <t>魔法倍率</t>
+  </si>
+  <si>
+    <t>深渊草帽</t>
+  </si>
+  <si>
+    <t>深渊猫爪</t>
+  </si>
+  <si>
+    <t>韧性倍率</t>
+  </si>
+  <si>
+    <t>深渊花朵</t>
+  </si>
+  <si>
+    <t>深渊冰晶</t>
+  </si>
+  <si>
+    <t>深渊蝠翼</t>
+  </si>
+  <si>
+    <t>物伤倍率</t>
+  </si>
+  <si>
+    <t>深渊魂火</t>
+  </si>
+  <si>
+    <t>法伤倍率</t>
+  </si>
+  <si>
+    <t>深渊腐肉</t>
+  </si>
+  <si>
+    <t>道伤倍率</t>
+  </si>
+  <si>
+    <t>深渊蛇胆</t>
+  </si>
+  <si>
+    <t>深渊狼爪</t>
+  </si>
+  <si>
+    <t>深渊虫皮</t>
+  </si>
+  <si>
+    <t>深渊鹰羽</t>
+  </si>
+  <si>
+    <t>深渊虫角</t>
+  </si>
+  <si>
+    <t>深渊蜈膏</t>
+  </si>
+  <si>
+    <t>深渊虫心</t>
+  </si>
+  <si>
+    <t>深渊龙皮</t>
+  </si>
+  <si>
+    <t>深渊猪皮</t>
+  </si>
+  <si>
+    <t>深渊猪心</t>
+  </si>
+  <si>
+    <t>深渊蝎皮</t>
+  </si>
+  <si>
+    <t>深渊宝甲</t>
+  </si>
+  <si>
+    <t>深渊号角</t>
+  </si>
+  <si>
+    <t>深渊雕像</t>
+  </si>
+  <si>
+    <t>深渊神像</t>
+  </si>
+  <si>
+    <t>深渊獠牙</t>
+  </si>
+  <si>
+    <t>深渊树心</t>
+  </si>
+  <si>
+    <t>深渊魔心</t>
+  </si>
+  <si>
+    <t>深渊尸心</t>
+  </si>
+  <si>
+    <t>深渊法杖</t>
+  </si>
+  <si>
+    <t>深渊权杖</t>
+  </si>
+  <si>
+    <t>深渊战锤</t>
+  </si>
+  <si>
+    <t>深渊血核</t>
+  </si>
+  <si>
+    <t>深渊魔核</t>
+  </si>
+  <si>
+    <t>深渊龙甲</t>
+  </si>
+  <si>
+    <t>深渊龙爪</t>
   </si>
 </sst>
 </file>
@@ -568,12 +691,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -898,7 +1027,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -922,16 +1051,16 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -940,92 +1069,93 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1347,7 +1477,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:K94"/>
+  <dimension ref="C3:K129"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="5" width="9" style="1"/>
@@ -1359,90 +1489,90 @@
   </cols>
   <sheetData>
     <row r="3" s="1" customFormat="1" customHeight="1" spans="3:11">
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="H3" s="2" t="s">
+      <c r="G3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="K3" s="2" t="s">
+      <c r="J3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="K3" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" customHeight="1" spans="3:11">
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="F4" s="2" t="s">
+      <c r="E4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="H4" s="2" t="s">
+      <c r="G4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="I4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="K4" s="2" t="s">
+      <c r="J4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="K4" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" customHeight="1" spans="3:11">
-      <c r="C5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H5" s="2" t="s">
+      <c r="D5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="G5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K5" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -1456,7 +1586,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G6" s="1">
         <v>1</v>
@@ -1471,7 +1601,7 @@
         <v>4</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -1482,10 +1612,10 @@
         <v>40000052</v>
       </c>
       <c r="E7" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G7" s="1">
         <v>15</v>
@@ -1500,7 +1630,7 @@
         <v>4</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -1511,10 +1641,10 @@
         <v>40000053</v>
       </c>
       <c r="E8" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G8" s="1">
         <v>2003</v>
@@ -1529,7 +1659,7 @@
         <v>4</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -1540,10 +1670,10 @@
         <v>40000054</v>
       </c>
       <c r="E9" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G9" s="1">
         <v>5</v>
@@ -1558,7 +1688,7 @@
         <v>4</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -1569,10 +1699,10 @@
         <v>40000055</v>
       </c>
       <c r="E10" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G10" s="1">
         <v>16</v>
@@ -1587,7 +1717,7 @@
         <v>4</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -1598,10 +1728,10 @@
         <v>40000056</v>
       </c>
       <c r="E11" s="1">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G11" s="1">
         <v>2</v>
@@ -1616,7 +1746,7 @@
         <v>4</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -1627,10 +1757,10 @@
         <v>40000057</v>
       </c>
       <c r="E12" s="1">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G12" s="1">
         <v>3</v>
@@ -1645,7 +1775,7 @@
         <v>4</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="3:11">
@@ -1656,10 +1786,10 @@
         <v>40000058</v>
       </c>
       <c r="E13" s="1">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G13" s="1">
         <v>4</v>
@@ -1674,7 +1804,7 @@
         <v>4</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="3:11">
@@ -1685,10 +1815,10 @@
         <v>40000059</v>
       </c>
       <c r="E14" s="1">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G14" s="1">
         <v>5</v>
@@ -1703,7 +1833,7 @@
         <v>4</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="3:11">
@@ -1714,10 +1844,10 @@
         <v>40000060</v>
       </c>
       <c r="E15" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G15" s="1">
         <v>1</v>
@@ -1732,7 +1862,7 @@
         <v>4</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="3:11">
@@ -1743,10 +1873,10 @@
         <v>40000061</v>
       </c>
       <c r="E16" s="1">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G16" s="1">
         <v>15</v>
@@ -1761,7 +1891,7 @@
         <v>4</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="3:11">
@@ -1772,10 +1902,10 @@
         <v>40000062</v>
       </c>
       <c r="E17" s="1">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G17" s="1">
         <v>2003</v>
@@ -1790,7 +1920,7 @@
         <v>4</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="3:11">
@@ -1801,10 +1931,10 @@
         <v>40000063</v>
       </c>
       <c r="E18" s="1">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G18" s="1">
         <v>33</v>
@@ -1819,7 +1949,7 @@
         <v>4</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="3:11">
@@ -1830,10 +1960,10 @@
         <v>40000064</v>
       </c>
       <c r="E19" s="1">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G19" s="1">
         <v>34</v>
@@ -1848,7 +1978,7 @@
         <v>4</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="3:11">
@@ -1859,10 +1989,10 @@
         <v>40000065</v>
       </c>
       <c r="E20" s="1">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G20" s="1">
         <v>35</v>
@@ -1877,7 +2007,7 @@
         <v>4</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="3:11">
@@ -1888,10 +2018,10 @@
         <v>40000066</v>
       </c>
       <c r="E21" s="1">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G21" s="1">
         <v>1</v>
@@ -1906,7 +2036,7 @@
         <v>4</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="3:11">
@@ -1917,10 +2047,10 @@
         <v>40000067</v>
       </c>
       <c r="E22" s="1">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G22" s="1">
         <v>2003</v>
@@ -1935,7 +2065,7 @@
         <v>4</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="3:11">
@@ -1946,10 +2076,10 @@
         <v>40000068</v>
       </c>
       <c r="E23" s="1">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G23" s="1">
         <v>2011</v>
@@ -1964,7 +2094,7 @@
         <v>4</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="3:11">
@@ -1975,10 +2105,10 @@
         <v>40000069</v>
       </c>
       <c r="E24" s="1">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G24" s="1">
         <v>2004</v>
@@ -1993,7 +2123,7 @@
         <v>4</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="3:11">
@@ -2004,10 +2134,10 @@
         <v>40000070</v>
       </c>
       <c r="E25" s="1">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G25" s="1">
         <v>2005</v>
@@ -2022,7 +2152,7 @@
         <v>4</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="3:11">
@@ -2033,10 +2163,10 @@
         <v>40000071</v>
       </c>
       <c r="E26" s="1">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G26" s="1">
         <v>2006</v>
@@ -2051,7 +2181,7 @@
         <v>4</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="3:11">
@@ -2062,10 +2192,10 @@
         <v>40000072</v>
       </c>
       <c r="E27" s="1">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G27" s="1">
         <v>2003</v>
@@ -2080,7 +2210,7 @@
         <v>4</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="3:11">
@@ -2091,10 +2221,10 @@
         <v>40000073</v>
       </c>
       <c r="E28" s="1">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G28" s="1">
         <v>2002</v>
@@ -2109,7 +2239,7 @@
         <v>4</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="3:11">
@@ -2120,10 +2250,10 @@
         <v>40000074</v>
       </c>
       <c r="E29" s="1">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G29" s="1">
         <v>2001</v>
@@ -2138,7 +2268,7 @@
         <v>4</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="3:11">
@@ -2149,10 +2279,10 @@
         <v>40000075</v>
       </c>
       <c r="E30" s="1">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G30" s="1">
         <v>1</v>
@@ -2167,7 +2297,7 @@
         <v>4</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="3:11">
@@ -2178,10 +2308,10 @@
         <v>40000076</v>
       </c>
       <c r="E31" s="1">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G31" s="1">
         <v>15</v>
@@ -2196,7 +2326,7 @@
         <v>4</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="3:11">
@@ -2207,10 +2337,10 @@
         <v>40000077</v>
       </c>
       <c r="E32" s="1">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G32" s="1">
         <v>2003</v>
@@ -2225,7 +2355,7 @@
         <v>4</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="3:11">
@@ -2236,10 +2366,10 @@
         <v>40000078</v>
       </c>
       <c r="E33" s="1">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G33" s="1">
         <v>5</v>
@@ -2254,7 +2384,7 @@
         <v>4</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="3:11">
@@ -2265,10 +2395,10 @@
         <v>40000079</v>
       </c>
       <c r="E34" s="1">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G34" s="1">
         <v>16</v>
@@ -2283,7 +2413,7 @@
         <v>4</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="3:11">
@@ -2294,10 +2424,10 @@
         <v>40000080</v>
       </c>
       <c r="E35" s="1">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G35" s="1">
         <v>12</v>
@@ -2312,7 +2442,7 @@
         <v>4</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="3:11">
@@ -2323,10 +2453,10 @@
         <v>40000081</v>
       </c>
       <c r="E36" s="1">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G36" s="1">
         <v>14</v>
@@ -2341,7 +2471,7 @@
         <v>4</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="3:11">
@@ -2352,10 +2482,10 @@
         <v>40000082</v>
       </c>
       <c r="E37" s="1">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G37" s="1">
         <v>2004</v>
@@ -2370,7 +2500,7 @@
         <v>4</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="3:11">
@@ -2381,10 +2511,10 @@
         <v>40000083</v>
       </c>
       <c r="E38" s="1">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G38" s="1">
         <v>2005</v>
@@ -2399,7 +2529,7 @@
         <v>4</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="3:11">
@@ -2410,10 +2540,10 @@
         <v>40000084</v>
       </c>
       <c r="E39" s="1">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G39" s="1">
         <v>2006</v>
@@ -2428,7 +2558,7 @@
         <v>4</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="3:11">
@@ -2439,10 +2569,10 @@
         <v>40000085</v>
       </c>
       <c r="E40" s="1">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G40" s="1">
         <v>15</v>
@@ -2457,7 +2587,7 @@
         <v>4</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="3:11">
@@ -2468,10 +2598,10 @@
         <v>40000086</v>
       </c>
       <c r="E41" s="1">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G41" s="1">
         <v>16</v>
@@ -2486,7 +2616,7 @@
         <v>4</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="3:11">
@@ -2497,10 +2627,10 @@
         <v>40000087</v>
       </c>
       <c r="E42" s="1">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G42" s="1">
         <v>2002</v>
@@ -2515,7 +2645,7 @@
         <v>4</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="3:11">
@@ -2526,10 +2656,10 @@
         <v>40000088</v>
       </c>
       <c r="E43" s="1">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G43" s="1">
         <v>2003</v>
@@ -2544,7 +2674,7 @@
         <v>4</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="3:11">
@@ -2555,10 +2685,10 @@
         <v>40000089</v>
       </c>
       <c r="E44" s="1">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G44" s="1">
         <v>2011</v>
@@ -2573,7 +2703,7 @@
         <v>4</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="3:11">
@@ -2584,10 +2714,10 @@
         <v>40000090</v>
       </c>
       <c r="E45" s="1">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G45" s="1">
         <v>2004</v>
@@ -2602,7 +2732,7 @@
         <v>4</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="3:11">
@@ -2613,10 +2743,10 @@
         <v>40000091</v>
       </c>
       <c r="E46" s="1">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G46" s="1">
         <v>2005</v>
@@ -2631,7 +2761,7 @@
         <v>4</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="3:11">
@@ -2642,10 +2772,10 @@
         <v>40000092</v>
       </c>
       <c r="E47" s="1">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G47" s="1">
         <v>2006</v>
@@ -2660,7 +2790,7 @@
         <v>4</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="3:11">
@@ -2671,10 +2801,10 @@
         <v>40000093</v>
       </c>
       <c r="E48" s="1">
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G48" s="1">
         <v>2002</v>
@@ -2689,7 +2819,7 @@
         <v>4</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="49" customHeight="1" spans="3:11">
@@ -2700,10 +2830,10 @@
         <v>40000094</v>
       </c>
       <c r="E49" s="1">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G49" s="1">
         <v>2003</v>
@@ -2718,7 +2848,7 @@
         <v>4</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="50" customHeight="1" spans="3:11">
@@ -2729,10 +2859,10 @@
         <v>40000095</v>
       </c>
       <c r="E50" s="1">
-        <v>45</v>
+        <v>2</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G50" s="1">
         <v>15</v>
@@ -2747,7 +2877,7 @@
         <v>4</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="3:11">
@@ -2758,10 +2888,10 @@
         <v>40000096</v>
       </c>
       <c r="E51" s="1">
-        <v>46</v>
+        <v>2</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G51" s="1">
         <v>16</v>
@@ -2776,7 +2906,7 @@
         <v>4</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="3:11">
@@ -2787,10 +2917,10 @@
         <v>40000097</v>
       </c>
       <c r="E52" s="1">
-        <v>47</v>
+        <v>2</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G52" s="1">
         <v>2002</v>
@@ -2805,7 +2935,7 @@
         <v>4</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="3:11">
@@ -2816,10 +2946,10 @@
         <v>40000098</v>
       </c>
       <c r="E53" s="1">
-        <v>48</v>
+        <v>2</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G53" s="1">
         <v>2003</v>
@@ -2834,7 +2964,7 @@
         <v>4</v>
       </c>
       <c r="K53" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="54" customHeight="1" spans="3:11">
@@ -2845,10 +2975,10 @@
         <v>40000099</v>
       </c>
       <c r="E54" s="1">
-        <v>49</v>
+        <v>2</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G54" s="1">
         <v>2001</v>
@@ -2863,7 +2993,7 @@
         <v>4</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="3:11">
@@ -2874,10 +3004,10 @@
         <v>40000100</v>
       </c>
       <c r="E55" s="1">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G55" s="1">
         <v>2004</v>
@@ -2892,7 +3022,7 @@
         <v>4</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="3:11">
@@ -2903,10 +3033,10 @@
         <v>40000101</v>
       </c>
       <c r="E56" s="1">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G56" s="1">
         <v>2003</v>
@@ -2921,7 +3051,7 @@
         <v>4</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="3:11">
@@ -2932,10 +3062,10 @@
         <v>40000102</v>
       </c>
       <c r="E57" s="1">
-        <v>52</v>
+        <v>2</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G57" s="1">
         <v>2002</v>
@@ -2950,7 +3080,7 @@
         <v>4</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="3:11">
@@ -2961,10 +3091,10 @@
         <v>40000103</v>
       </c>
       <c r="E58" s="1">
-        <v>53</v>
+        <v>2</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G58" s="1">
         <v>2011</v>
@@ -2979,7 +3109,7 @@
         <v>4</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="3:11">
@@ -2990,10 +3120,10 @@
         <v>40000104</v>
       </c>
       <c r="E59" s="1">
-        <v>54</v>
+        <v>2</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G59" s="1">
         <v>2001</v>
@@ -3008,7 +3138,7 @@
         <v>4</v>
       </c>
       <c r="K59" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="3:11">
@@ -3019,10 +3149,10 @@
         <v>40000105</v>
       </c>
       <c r="E60" s="1">
-        <v>55</v>
+        <v>3</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G60" s="1">
         <v>2004</v>
@@ -3037,7 +3167,7 @@
         <v>4</v>
       </c>
       <c r="K60" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="3:11">
@@ -3048,10 +3178,10 @@
         <v>40000106</v>
       </c>
       <c r="E61" s="1">
-        <v>56</v>
+        <v>3</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G61" s="1">
         <v>2005</v>
@@ -3066,7 +3196,7 @@
         <v>4</v>
       </c>
       <c r="K61" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="3:11">
@@ -3077,10 +3207,10 @@
         <v>40000107</v>
       </c>
       <c r="E62" s="1">
-        <v>57</v>
+        <v>3</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G62" s="1">
         <v>2006</v>
@@ -3095,7 +3225,7 @@
         <v>4</v>
       </c>
       <c r="K62" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="3:11">
@@ -3106,10 +3236,10 @@
         <v>40000108</v>
       </c>
       <c r="E63" s="1">
-        <v>58</v>
+        <v>3</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G63" s="1">
         <v>2003</v>
@@ -3124,7 +3254,7 @@
         <v>4</v>
       </c>
       <c r="K63" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="3:11">
@@ -3135,10 +3265,10 @@
         <v>40000109</v>
       </c>
       <c r="E64" s="1">
-        <v>59</v>
+        <v>3</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G64" s="1">
         <v>2002</v>
@@ -3153,7 +3283,7 @@
         <v>4</v>
       </c>
       <c r="K64" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="3:11">
@@ -3164,10 +3294,10 @@
         <v>40000110</v>
       </c>
       <c r="E65" s="1">
-        <v>60</v>
+        <v>3</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G65" s="1">
         <v>2001</v>
@@ -3182,7 +3312,7 @@
         <v>4</v>
       </c>
       <c r="K65" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="3:11">
@@ -3193,10 +3323,10 @@
         <v>40000111</v>
       </c>
       <c r="E66" s="1">
-        <v>61</v>
+        <v>3</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G66" s="1">
         <v>2010</v>
@@ -3211,7 +3341,7 @@
         <v>4</v>
       </c>
       <c r="K66" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="3:11">
@@ -3222,10 +3352,10 @@
         <v>40000112</v>
       </c>
       <c r="E67" s="1">
-        <v>62</v>
+        <v>3</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G67" s="1">
         <v>2011</v>
@@ -3240,7 +3370,7 @@
         <v>4</v>
       </c>
       <c r="K67" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="68" customHeight="1" spans="3:11">
@@ -3251,10 +3381,10 @@
         <v>40000113</v>
       </c>
       <c r="E68" s="1">
-        <v>63</v>
+        <v>3</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G68" s="1">
         <v>2002</v>
@@ -3269,7 +3399,7 @@
         <v>4</v>
       </c>
       <c r="K68" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="69" customHeight="1" spans="3:11">
@@ -3280,10 +3410,10 @@
         <v>40000114</v>
       </c>
       <c r="E69" s="1">
-        <v>64</v>
+        <v>3</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G69" s="1">
         <v>2003</v>
@@ -3298,7 +3428,7 @@
         <v>4</v>
       </c>
       <c r="K69" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="70" customHeight="1" spans="3:11">
@@ -3309,10 +3439,10 @@
         <v>40000115</v>
       </c>
       <c r="E70" s="1">
-        <v>65</v>
+        <v>3</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G70" s="1">
         <v>2004</v>
@@ -3327,7 +3457,7 @@
         <v>4</v>
       </c>
       <c r="K70" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="3:11">
@@ -3338,10 +3468,10 @@
         <v>40000116</v>
       </c>
       <c r="E71" s="1">
-        <v>66</v>
+        <v>3</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G71" s="1">
         <v>2005</v>
@@ -3356,7 +3486,7 @@
         <v>4</v>
       </c>
       <c r="K71" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="3:11">
@@ -3367,10 +3497,10 @@
         <v>40000117</v>
       </c>
       <c r="E72" s="1">
-        <v>67</v>
+        <v>3</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G72" s="1">
         <v>2006</v>
@@ -3385,7 +3515,7 @@
         <v>4</v>
       </c>
       <c r="K72" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="3:11">
@@ -3396,10 +3526,10 @@
         <v>40000118</v>
       </c>
       <c r="E73" s="1">
-        <v>68</v>
+        <v>3</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G73" s="1">
         <v>2002</v>
@@ -3414,7 +3544,7 @@
         <v>4</v>
       </c>
       <c r="K73" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="3:11">
@@ -3425,10 +3555,10 @@
         <v>40000119</v>
       </c>
       <c r="E74" s="1">
-        <v>69</v>
+        <v>3</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G74" s="1">
         <v>2003</v>
@@ -3443,7 +3573,7 @@
         <v>4</v>
       </c>
       <c r="K74" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="3:11">
@@ -3454,10 +3584,10 @@
         <v>40000120</v>
       </c>
       <c r="E75" s="1">
-        <v>70</v>
+        <v>3</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G75" s="1">
         <v>2001</v>
@@ -3472,7 +3602,7 @@
         <v>4</v>
       </c>
       <c r="K75" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="3:11">
@@ -3483,10 +3613,10 @@
         <v>40000121</v>
       </c>
       <c r="E76" s="1">
-        <v>71</v>
+        <v>3</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G76" s="1">
         <v>2010</v>
@@ -3501,7 +3631,7 @@
         <v>4</v>
       </c>
       <c r="K76" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="3:11">
@@ -3512,10 +3642,10 @@
         <v>40000122</v>
       </c>
       <c r="E77" s="1">
-        <v>72</v>
+        <v>3</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G77" s="1">
         <v>2011</v>
@@ -3530,7 +3660,7 @@
         <v>4</v>
       </c>
       <c r="K77" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="78" customHeight="1" spans="3:11">
@@ -3541,10 +3671,10 @@
         <v>40000123</v>
       </c>
       <c r="E78" s="1">
-        <v>73</v>
+        <v>3</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G78" s="1">
         <v>2003</v>
@@ -3559,7 +3689,7 @@
         <v>4</v>
       </c>
       <c r="K78" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="79" customHeight="1" spans="3:11">
@@ -3570,10 +3700,10 @@
         <v>40000124</v>
       </c>
       <c r="E79" s="1">
-        <v>74</v>
+        <v>3</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G79" s="1">
         <v>2002</v>
@@ -3588,7 +3718,7 @@
         <v>4</v>
       </c>
       <c r="K79" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="80" customHeight="1" spans="3:11">
@@ -3599,10 +3729,10 @@
         <v>40000125</v>
       </c>
       <c r="E80" s="1">
-        <v>75</v>
+        <v>3</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G80" s="1">
         <v>2004</v>
@@ -3617,7 +3747,7 @@
         <v>4</v>
       </c>
       <c r="K80" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="81" customHeight="1" spans="3:11">
@@ -3628,10 +3758,10 @@
         <v>40000126</v>
       </c>
       <c r="E81" s="1">
-        <v>76</v>
+        <v>3</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G81" s="1">
         <v>2005</v>
@@ -3646,7 +3776,7 @@
         <v>4</v>
       </c>
       <c r="K81" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="82" customHeight="1" spans="3:11">
@@ -3657,10 +3787,10 @@
         <v>40000127</v>
       </c>
       <c r="E82" s="1">
-        <v>77</v>
+        <v>3</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G82" s="1">
         <v>2006</v>
@@ -3675,7 +3805,7 @@
         <v>4</v>
       </c>
       <c r="K82" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="83" customHeight="1" spans="3:11">
@@ -3686,10 +3816,10 @@
         <v>40000128</v>
       </c>
       <c r="E83" s="1">
-        <v>78</v>
+        <v>3</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G83" s="1">
         <v>2002</v>
@@ -3704,7 +3834,7 @@
         <v>4</v>
       </c>
       <c r="K83" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="84" customHeight="1" spans="3:11">
@@ -3715,10 +3845,10 @@
         <v>40000129</v>
       </c>
       <c r="E84" s="1">
-        <v>79</v>
+        <v>3</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G84" s="1">
         <v>2003</v>
@@ -3733,7 +3863,7 @@
         <v>4</v>
       </c>
       <c r="K84" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="85" customHeight="1" spans="3:11">
@@ -3744,10 +3874,10 @@
         <v>40000130</v>
       </c>
       <c r="E85" s="1">
-        <v>80</v>
+        <v>3</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G85" s="1">
         <v>2001</v>
@@ -3762,7 +3892,7 @@
         <v>4</v>
       </c>
       <c r="K85" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="86" customHeight="1" spans="3:11">
@@ -3773,10 +3903,10 @@
         <v>40000131</v>
       </c>
       <c r="E86" s="1">
-        <v>81</v>
+        <v>3</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G86" s="1">
         <v>2002</v>
@@ -3791,7 +3921,7 @@
         <v>4</v>
       </c>
       <c r="K86" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="87" customHeight="1" spans="3:11">
@@ -3802,10 +3932,10 @@
         <v>40000132</v>
       </c>
       <c r="E87" s="1">
-        <v>82</v>
+        <v>3</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G87" s="1">
         <v>2011</v>
@@ -3820,7 +3950,7 @@
         <v>4</v>
       </c>
       <c r="K87" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="88" customHeight="1" spans="3:11">
@@ -3831,10 +3961,10 @@
         <v>40000133</v>
       </c>
       <c r="E88" s="1">
-        <v>83</v>
+        <v>3</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G88" s="1">
         <v>2003</v>
@@ -3849,7 +3979,7 @@
         <v>4</v>
       </c>
       <c r="K88" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="89" customHeight="1" spans="3:11">
@@ -3860,10 +3990,10 @@
         <v>40000134</v>
       </c>
       <c r="E89" s="1">
-        <v>84</v>
+        <v>3</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G89" s="1">
         <v>2002</v>
@@ -3878,7 +4008,7 @@
         <v>4</v>
       </c>
       <c r="K89" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="90" customHeight="1" spans="3:11">
@@ -3889,10 +4019,10 @@
         <v>40000135</v>
       </c>
       <c r="E90" s="1">
-        <v>85</v>
+        <v>3</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G90" s="1">
         <v>2004</v>
@@ -3907,7 +4037,7 @@
         <v>4</v>
       </c>
       <c r="K90" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="91" customHeight="1" spans="3:11">
@@ -3918,10 +4048,10 @@
         <v>40000136</v>
       </c>
       <c r="E91" s="1">
-        <v>86</v>
+        <v>3</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G91" s="1">
         <v>2005</v>
@@ -3936,7 +4066,7 @@
         <v>4</v>
       </c>
       <c r="K91" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="92" customHeight="1" spans="3:11">
@@ -3947,10 +4077,10 @@
         <v>40000137</v>
       </c>
       <c r="E92" s="1">
-        <v>87</v>
+        <v>3</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G92" s="1">
         <v>2006</v>
@@ -3965,7 +4095,7 @@
         <v>4</v>
       </c>
       <c r="K92" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="93" customHeight="1" spans="3:11">
@@ -3976,10 +4106,10 @@
         <v>40000138</v>
       </c>
       <c r="E93" s="1">
-        <v>88</v>
+        <v>3</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G93" s="1">
         <v>2002</v>
@@ -3994,7 +4124,7 @@
         <v>4</v>
       </c>
       <c r="K93" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="94" customHeight="1" spans="3:11">
@@ -4005,10 +4135,10 @@
         <v>40000139</v>
       </c>
       <c r="E94" s="1">
-        <v>89</v>
+        <v>3</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G94" s="1">
         <v>2003</v>
@@ -4023,12 +4153,1027 @@
         <v>4</v>
       </c>
       <c r="K94" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="95" s="2" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C95" s="2">
+        <v>40000140</v>
+      </c>
+      <c r="D95" s="2">
+        <v>40000140</v>
+      </c>
+      <c r="E95" s="2">
+        <v>4</v>
+      </c>
+      <c r="F95" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="G95" s="2">
+        <v>2004</v>
+      </c>
+      <c r="H95" s="2">
+        <v>7</v>
+      </c>
+      <c r="I95" s="2">
+        <v>7</v>
+      </c>
+      <c r="J95" s="2">
+        <v>4</v>
+      </c>
+      <c r="K95" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="96" customHeight="1" spans="3:11">
+      <c r="C96" s="1">
+        <v>40000141</v>
+      </c>
+      <c r="D96" s="1">
+        <v>40000141</v>
+      </c>
+      <c r="E96" s="1">
+        <v>4</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="G96" s="1">
+        <v>2005</v>
+      </c>
+      <c r="H96" s="1">
+        <v>7</v>
+      </c>
+      <c r="I96" s="1">
+        <v>7</v>
+      </c>
+      <c r="J96" s="1">
+        <v>4</v>
+      </c>
+      <c r="K96" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="97" customHeight="1" spans="3:11">
+      <c r="C97" s="1">
+        <v>40000142</v>
+      </c>
+      <c r="D97" s="1">
+        <v>40000142</v>
+      </c>
+      <c r="E97" s="1">
+        <v>4</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="G97" s="1">
+        <v>2006</v>
+      </c>
+      <c r="H97" s="1">
+        <v>7</v>
+      </c>
+      <c r="I97" s="1">
+        <v>7</v>
+      </c>
+      <c r="J97" s="1">
+        <v>4</v>
+      </c>
+      <c r="K97" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="98" customHeight="1" spans="3:11">
+      <c r="C98" s="1">
+        <v>40000143</v>
+      </c>
+      <c r="D98" s="1">
+        <v>40000143</v>
+      </c>
+      <c r="E98" s="1">
+        <v>4</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="G98" s="1">
+        <v>2012</v>
+      </c>
+      <c r="H98" s="1">
+        <v>25</v>
+      </c>
+      <c r="I98" s="1">
+        <v>25</v>
+      </c>
+      <c r="J98" s="1">
+        <v>4</v>
+      </c>
+      <c r="K98" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="99" customHeight="1" spans="3:11">
+      <c r="C99" s="1">
+        <v>40000144</v>
+      </c>
+      <c r="D99" s="1">
+        <v>40000144</v>
+      </c>
+      <c r="E99" s="1">
+        <v>4</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="G99" s="1">
+        <v>2001</v>
+      </c>
+      <c r="H99" s="1">
+        <v>7</v>
+      </c>
+      <c r="I99" s="1">
+        <v>7</v>
+      </c>
+      <c r="J99" s="1">
+        <v>4</v>
+      </c>
+      <c r="K99" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="100" customHeight="1" spans="3:11">
+      <c r="C100" s="1">
+        <v>40000145</v>
+      </c>
+      <c r="D100" s="1">
+        <v>40000145</v>
+      </c>
+      <c r="E100" s="1">
+        <v>4</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="G100" s="1">
+        <v>2003</v>
+      </c>
+      <c r="H100" s="1">
+        <v>40</v>
+      </c>
+      <c r="I100" s="1">
+        <v>40</v>
+      </c>
+      <c r="J100" s="1">
+        <v>4</v>
+      </c>
+      <c r="K100" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="101" customHeight="1" spans="3:11">
+      <c r="C101" s="1">
+        <v>40000146</v>
+      </c>
+      <c r="D101" s="1">
+        <v>40000146</v>
+      </c>
+      <c r="E101" s="1">
+        <v>4</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="G101" s="1">
+        <v>2007</v>
+      </c>
+      <c r="H101" s="1">
+        <v>7</v>
+      </c>
+      <c r="I101" s="1">
+        <v>7</v>
+      </c>
+      <c r="J101" s="1">
+        <v>4</v>
+      </c>
+      <c r="K101" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="102" customHeight="1" spans="3:11">
+      <c r="C102" s="1">
+        <v>40000147</v>
+      </c>
+      <c r="D102" s="1">
+        <v>40000147</v>
+      </c>
+      <c r="E102" s="1">
+        <v>4</v>
+      </c>
+      <c r="F102" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="G102" s="1">
+        <v>2008</v>
+      </c>
+      <c r="H102" s="1">
+        <v>7</v>
+      </c>
+      <c r="I102" s="1">
+        <v>7</v>
+      </c>
+      <c r="J102" s="1">
+        <v>4</v>
+      </c>
+      <c r="K102" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="103" customHeight="1" spans="3:11">
+      <c r="C103" s="1">
+        <v>40000148</v>
+      </c>
+      <c r="D103" s="1">
+        <v>40000148</v>
+      </c>
+      <c r="E103" s="1">
+        <v>4</v>
+      </c>
+      <c r="F103" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="G103" s="1">
+        <v>2009</v>
+      </c>
+      <c r="H103" s="1">
+        <v>7</v>
+      </c>
+      <c r="I103" s="1">
+        <v>7</v>
+      </c>
+      <c r="J103" s="1">
+        <v>4</v>
+      </c>
+      <c r="K103" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="104" customHeight="1" spans="3:11">
+      <c r="C104" s="1">
+        <v>40000149</v>
+      </c>
+      <c r="D104" s="1">
+        <v>40000149</v>
+      </c>
+      <c r="E104" s="1">
+        <v>4</v>
+      </c>
+      <c r="F104" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="G104" s="1">
+        <v>2012</v>
+      </c>
+      <c r="H104" s="1">
+        <v>25</v>
+      </c>
+      <c r="I104" s="1">
+        <v>25</v>
+      </c>
+      <c r="J104" s="1">
+        <v>4</v>
+      </c>
+      <c r="K104" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="105" customHeight="1" spans="3:11">
+      <c r="C105" s="1">
+        <v>40000150</v>
+      </c>
+      <c r="D105" s="1">
+        <v>40000150</v>
+      </c>
+      <c r="E105" s="1">
+        <v>4</v>
+      </c>
+      <c r="F105" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="G105" s="1">
+        <v>2011</v>
+      </c>
+      <c r="H105" s="1">
+        <v>7</v>
+      </c>
+      <c r="I105" s="1">
+        <v>7</v>
+      </c>
+      <c r="J105" s="1">
+        <v>4</v>
+      </c>
+      <c r="K105" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="106" customHeight="1" spans="3:11">
+      <c r="C106" s="1">
+        <v>40000151</v>
+      </c>
+      <c r="D106" s="1">
+        <v>40000151</v>
+      </c>
+      <c r="E106" s="1">
+        <v>4</v>
+      </c>
+      <c r="F106" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="G106" s="1">
+        <v>2003</v>
+      </c>
+      <c r="H106" s="1">
+        <v>40</v>
+      </c>
+      <c r="I106" s="1">
+        <v>40</v>
+      </c>
+      <c r="J106" s="1">
+        <v>4</v>
+      </c>
+      <c r="K106" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="107" customHeight="1" spans="3:11">
+      <c r="C107" s="1">
+        <v>40000152</v>
+      </c>
+      <c r="D107" s="1">
+        <v>40000152</v>
+      </c>
+      <c r="E107" s="1">
+        <v>4</v>
+      </c>
+      <c r="F107" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="G107" s="1">
+        <v>2004</v>
+      </c>
+      <c r="H107" s="1">
+        <v>7</v>
+      </c>
+      <c r="I107" s="1">
+        <v>7</v>
+      </c>
+      <c r="J107" s="1">
+        <v>4</v>
+      </c>
+      <c r="K107" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="108" customHeight="1" spans="3:11">
+      <c r="C108" s="1">
+        <v>40000153</v>
+      </c>
+      <c r="D108" s="1">
+        <v>40000153</v>
+      </c>
+      <c r="E108" s="1">
+        <v>4</v>
+      </c>
+      <c r="F108" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="G108" s="1">
+        <v>2005</v>
+      </c>
+      <c r="H108" s="1">
+        <v>7</v>
+      </c>
+      <c r="I108" s="1">
+        <v>7</v>
+      </c>
+      <c r="J108" s="1">
+        <v>4</v>
+      </c>
+      <c r="K108" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="109" customHeight="1" spans="3:11">
+      <c r="C109" s="1">
+        <v>40000154</v>
+      </c>
+      <c r="D109" s="1">
+        <v>40000154</v>
+      </c>
+      <c r="E109" s="1">
+        <v>4</v>
+      </c>
+      <c r="F109" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="G109" s="1">
+        <v>2006</v>
+      </c>
+      <c r="H109" s="1">
+        <v>25</v>
+      </c>
+      <c r="I109" s="1">
+        <v>25</v>
+      </c>
+      <c r="J109" s="1">
+        <v>4</v>
+      </c>
+      <c r="K109" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="110" customHeight="1" spans="3:11">
+      <c r="C110" s="1">
+        <v>40000155</v>
+      </c>
+      <c r="D110" s="1">
+        <v>40000155</v>
+      </c>
+      <c r="E110" s="1">
+        <v>4</v>
+      </c>
+      <c r="F110" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="G110" s="1">
+        <v>2012</v>
+      </c>
+      <c r="H110" s="1">
+        <v>7</v>
+      </c>
+      <c r="I110" s="1">
+        <v>7</v>
+      </c>
+      <c r="J110" s="1">
+        <v>4</v>
+      </c>
+      <c r="K110" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="111" customHeight="1" spans="3:11">
+      <c r="C111" s="1">
+        <v>40000156</v>
+      </c>
+      <c r="D111" s="1">
+        <v>40000156</v>
+      </c>
+      <c r="E111" s="1">
+        <v>4</v>
+      </c>
+      <c r="F111" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="G111" s="1">
+        <v>2001</v>
+      </c>
+      <c r="H111" s="1">
+        <v>40</v>
+      </c>
+      <c r="I111" s="1">
+        <v>40</v>
+      </c>
+      <c r="J111" s="1">
+        <v>4</v>
+      </c>
+      <c r="K111" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="112" customHeight="1" spans="3:11">
+      <c r="C112" s="1">
+        <v>40000157</v>
+      </c>
+      <c r="D112" s="1">
+        <v>40000157</v>
+      </c>
+      <c r="E112" s="1">
+        <v>4</v>
+      </c>
+      <c r="F112" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="G112" s="1">
+        <v>2003</v>
+      </c>
+      <c r="H112" s="1">
+        <v>7</v>
+      </c>
+      <c r="I112" s="1">
+        <v>7</v>
+      </c>
+      <c r="J112" s="1">
+        <v>4</v>
+      </c>
+      <c r="K112" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="113" customHeight="1" spans="3:11">
+      <c r="C113" s="1">
+        <v>40000158</v>
+      </c>
+      <c r="D113" s="1">
+        <v>40000158</v>
+      </c>
+      <c r="E113" s="1">
+        <v>4</v>
+      </c>
+      <c r="F113" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="G113" s="1">
+        <v>2007</v>
+      </c>
+      <c r="H113" s="1">
+        <v>7</v>
+      </c>
+      <c r="I113" s="1">
+        <v>7</v>
+      </c>
+      <c r="J113" s="1">
+        <v>4</v>
+      </c>
+      <c r="K113" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="114" customHeight="1" spans="3:11">
+      <c r="C114" s="1">
+        <v>40000159</v>
+      </c>
+      <c r="D114" s="1">
+        <v>40000159</v>
+      </c>
+      <c r="E114" s="1">
+        <v>4</v>
+      </c>
+      <c r="F114" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="G114" s="1">
+        <v>2008</v>
+      </c>
+      <c r="H114" s="1">
+        <v>7</v>
+      </c>
+      <c r="I114" s="1">
+        <v>7</v>
+      </c>
+      <c r="J114" s="1">
+        <v>4</v>
+      </c>
+      <c r="K114" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="115" customHeight="1" spans="3:11">
+      <c r="C115" s="1">
+        <v>40000160</v>
+      </c>
+      <c r="D115" s="1">
+        <v>40000160</v>
+      </c>
+      <c r="E115" s="1">
+        <v>4</v>
+      </c>
+      <c r="F115" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="G115" s="1">
+        <v>2009</v>
+      </c>
+      <c r="H115" s="1">
+        <v>25</v>
+      </c>
+      <c r="I115" s="1">
+        <v>25</v>
+      </c>
+      <c r="J115" s="1">
+        <v>4</v>
+      </c>
+      <c r="K115" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="116" customHeight="1" spans="3:11">
+      <c r="C116" s="1">
+        <v>40000161</v>
+      </c>
+      <c r="D116" s="1">
+        <v>40000161</v>
+      </c>
+      <c r="E116" s="1">
+        <v>4</v>
+      </c>
+      <c r="F116" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="G116" s="1">
+        <v>2012</v>
+      </c>
+      <c r="H116" s="1">
+        <v>7</v>
+      </c>
+      <c r="I116" s="1">
+        <v>7</v>
+      </c>
+      <c r="J116" s="1">
+        <v>4</v>
+      </c>
+      <c r="K116" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="117" customHeight="1" spans="3:11">
+      <c r="C117" s="1">
+        <v>40000162</v>
+      </c>
+      <c r="D117" s="1">
+        <v>40000162</v>
+      </c>
+      <c r="E117" s="1">
+        <v>4</v>
+      </c>
+      <c r="F117" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="G117" s="1">
+        <v>2011</v>
+      </c>
+      <c r="H117" s="1">
+        <v>40</v>
+      </c>
+      <c r="I117" s="1">
+        <v>40</v>
+      </c>
+      <c r="J117" s="1">
+        <v>4</v>
+      </c>
+      <c r="K117" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="118" customHeight="1" spans="3:11">
+      <c r="C118" s="1">
+        <v>40000163</v>
+      </c>
+      <c r="D118" s="1">
+        <v>40000163</v>
+      </c>
+      <c r="E118" s="1">
+        <v>4</v>
+      </c>
+      <c r="F118" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="G118" s="1">
+        <v>2003</v>
+      </c>
+      <c r="H118" s="1">
+        <v>40</v>
+      </c>
+      <c r="I118" s="1">
+        <v>40</v>
+      </c>
+      <c r="J118" s="1">
+        <v>4</v>
+      </c>
+      <c r="K118" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="119" customHeight="1" spans="3:11">
+      <c r="C119" s="1">
+        <v>40000164</v>
+      </c>
+      <c r="D119" s="1">
+        <v>40000164</v>
+      </c>
+      <c r="E119" s="1">
+        <v>4</v>
+      </c>
+      <c r="F119" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="G119" s="1">
+        <v>2004</v>
+      </c>
+      <c r="H119" s="1">
+        <v>7</v>
+      </c>
+      <c r="I119" s="1">
+        <v>7</v>
+      </c>
+      <c r="J119" s="1">
+        <v>4</v>
+      </c>
+      <c r="K119" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="120" customHeight="1" spans="3:11">
+      <c r="C120" s="1">
+        <v>40000165</v>
+      </c>
+      <c r="D120" s="1">
+        <v>40000165</v>
+      </c>
+      <c r="E120" s="1">
+        <v>4</v>
+      </c>
+      <c r="F120" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="G120" s="1">
+        <v>2005</v>
+      </c>
+      <c r="H120" s="1">
+        <v>7</v>
+      </c>
+      <c r="I120" s="1">
+        <v>7</v>
+      </c>
+      <c r="J120" s="1">
+        <v>4</v>
+      </c>
+      <c r="K120" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="121" customHeight="1" spans="3:11">
+      <c r="C121" s="1">
+        <v>40000166</v>
+      </c>
+      <c r="D121" s="1">
+        <v>40000166</v>
+      </c>
+      <c r="E121" s="1">
+        <v>4</v>
+      </c>
+      <c r="F121" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="G121" s="1">
+        <v>2006</v>
+      </c>
+      <c r="H121" s="1">
+        <v>25</v>
+      </c>
+      <c r="I121" s="1">
+        <v>25</v>
+      </c>
+      <c r="J121" s="1">
+        <v>4</v>
+      </c>
+      <c r="K121" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="122" customHeight="1" spans="3:11">
+      <c r="C122" s="1">
+        <v>40000167</v>
+      </c>
+      <c r="D122" s="1">
+        <v>40000167</v>
+      </c>
+      <c r="E122" s="1">
+        <v>4</v>
+      </c>
+      <c r="F122" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="G122" s="1">
+        <v>2012</v>
+      </c>
+      <c r="H122" s="1">
+        <v>7</v>
+      </c>
+      <c r="I122" s="1">
+        <v>7</v>
+      </c>
+      <c r="J122" s="1">
+        <v>4</v>
+      </c>
+      <c r="K122" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="123" customHeight="1" spans="3:11">
+      <c r="C123" s="1">
+        <v>40000168</v>
+      </c>
+      <c r="D123" s="1">
+        <v>40000168</v>
+      </c>
+      <c r="E123" s="1">
+        <v>4</v>
+      </c>
+      <c r="F123" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="G123" s="1">
+        <v>2001</v>
+      </c>
+      <c r="H123" s="1">
+        <v>40</v>
+      </c>
+      <c r="I123" s="1">
+        <v>40</v>
+      </c>
+      <c r="J123" s="1">
+        <v>4</v>
+      </c>
+      <c r="K123" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="124" customHeight="1" spans="3:11">
+      <c r="C124" s="1">
+        <v>40000169</v>
+      </c>
+      <c r="D124" s="1">
+        <v>40000169</v>
+      </c>
+      <c r="E124" s="1">
+        <v>4</v>
+      </c>
+      <c r="F124" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="G124" s="1">
+        <v>2003</v>
+      </c>
+      <c r="H124" s="1">
+        <v>7</v>
+      </c>
+      <c r="I124" s="1">
+        <v>7</v>
+      </c>
+      <c r="J124" s="1">
+        <v>4</v>
+      </c>
+      <c r="K124" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="125" customHeight="1" spans="3:11">
+      <c r="C125" s="1">
+        <v>40000170</v>
+      </c>
+      <c r="D125" s="1">
+        <v>40000170</v>
+      </c>
+      <c r="E125" s="1">
+        <v>4</v>
+      </c>
+      <c r="F125" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="G125" s="1">
+        <v>2007</v>
+      </c>
+      <c r="H125" s="1">
+        <v>7</v>
+      </c>
+      <c r="I125" s="1">
+        <v>7</v>
+      </c>
+      <c r="J125" s="1">
+        <v>4</v>
+      </c>
+      <c r="K125" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="126" customHeight="1" spans="3:11">
+      <c r="C126" s="1">
+        <v>40000171</v>
+      </c>
+      <c r="D126" s="1">
+        <v>40000171</v>
+      </c>
+      <c r="E126" s="1">
+        <v>4</v>
+      </c>
+      <c r="F126" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="G126" s="1">
+        <v>2008</v>
+      </c>
+      <c r="H126" s="1">
+        <v>7</v>
+      </c>
+      <c r="I126" s="1">
+        <v>7</v>
+      </c>
+      <c r="J126" s="1">
+        <v>4</v>
+      </c>
+      <c r="K126" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="127" customHeight="1" spans="3:11">
+      <c r="C127" s="1">
+        <v>40000172</v>
+      </c>
+      <c r="D127" s="1">
+        <v>40000172</v>
+      </c>
+      <c r="E127" s="1">
+        <v>4</v>
+      </c>
+      <c r="F127" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="G127" s="1">
+        <v>2009</v>
+      </c>
+      <c r="H127" s="1">
+        <v>25</v>
+      </c>
+      <c r="I127" s="1">
+        <v>25</v>
+      </c>
+      <c r="J127" s="1">
+        <v>4</v>
+      </c>
+      <c r="K127" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="128" customHeight="1" spans="3:11">
+      <c r="C128" s="1">
+        <v>40000173</v>
+      </c>
+      <c r="D128" s="1">
+        <v>40000173</v>
+      </c>
+      <c r="E128" s="1">
+        <v>4</v>
+      </c>
+      <c r="F128" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="G128" s="1">
+        <v>2012</v>
+      </c>
+      <c r="H128" s="1">
+        <v>7</v>
+      </c>
+      <c r="I128" s="1">
+        <v>7</v>
+      </c>
+      <c r="J128" s="1">
+        <v>4</v>
+      </c>
+      <c r="K128" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="129" customHeight="1" spans="3:11">
+      <c r="C129" s="1">
+        <v>40000174</v>
+      </c>
+      <c r="D129" s="1">
+        <v>40000174</v>
+      </c>
+      <c r="E129" s="1">
+        <v>4</v>
+      </c>
+      <c r="F129" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="G129" s="1">
+        <v>2011</v>
+      </c>
+      <c r="H129" s="1">
+        <v>40</v>
+      </c>
+      <c r="I129" s="1">
+        <v>40</v>
+      </c>
+      <c r="J129" s="1">
+        <v>4</v>
+      </c>
+      <c r="K129" s="1" t="s">
+        <v>93</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3 E4 E5 F3:F5 C3:D5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:F5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/HalidomConfig.xlsx
+++ b/Excel/HalidomConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="162">
   <si>
     <t>Id</t>
   </si>
@@ -56,9 +56,6 @@
     <t>Des</t>
   </si>
   <si>
-    <t>Level</t>
-  </si>
-  <si>
     <t>int</t>
   </si>
   <si>
@@ -414,6 +411,9 @@
   </si>
   <si>
     <t>深渊花朵</t>
+  </si>
+  <si>
+    <t>#</t>
   </si>
   <si>
     <t>深渊冰晶</t>
@@ -1477,7 +1477,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:K129"/>
+  <dimension ref="A3:K129"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="5" width="9" style="1"/>
@@ -1525,7 +1525,7 @@
         <v>1</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>3</v>
@@ -1548,31 +1548,31 @@
     </row>
     <row r="5" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="G5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K5" s="3" t="s">
         <v>10</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -1586,7 +1586,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G6" s="1">
         <v>1</v>
@@ -1601,7 +1601,7 @@
         <v>4</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -1615,7 +1615,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G7" s="1">
         <v>15</v>
@@ -1630,7 +1630,7 @@
         <v>4</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -1644,7 +1644,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G8" s="1">
         <v>2003</v>
@@ -1659,7 +1659,7 @@
         <v>4</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -1673,7 +1673,7 @@
         <v>1</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G9" s="1">
         <v>5</v>
@@ -1688,7 +1688,7 @@
         <v>4</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -1702,7 +1702,7 @@
         <v>1</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G10" s="1">
         <v>16</v>
@@ -1717,7 +1717,7 @@
         <v>4</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -1731,7 +1731,7 @@
         <v>1</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G11" s="1">
         <v>2</v>
@@ -1746,7 +1746,7 @@
         <v>4</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -1760,7 +1760,7 @@
         <v>1</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G12" s="1">
         <v>3</v>
@@ -1775,7 +1775,7 @@
         <v>4</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="3:11">
@@ -1789,7 +1789,7 @@
         <v>1</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G13" s="1">
         <v>4</v>
@@ -1804,7 +1804,7 @@
         <v>4</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="3:11">
@@ -1818,7 +1818,7 @@
         <v>1</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G14" s="1">
         <v>5</v>
@@ -1833,7 +1833,7 @@
         <v>4</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="3:11">
@@ -1847,7 +1847,7 @@
         <v>1</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G15" s="1">
         <v>1</v>
@@ -1862,7 +1862,7 @@
         <v>4</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="3:11">
@@ -1876,7 +1876,7 @@
         <v>1</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G16" s="1">
         <v>15</v>
@@ -1891,7 +1891,7 @@
         <v>4</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="3:11">
@@ -1905,7 +1905,7 @@
         <v>1</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G17" s="1">
         <v>2003</v>
@@ -1920,7 +1920,7 @@
         <v>4</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="3:11">
@@ -1934,7 +1934,7 @@
         <v>1</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G18" s="1">
         <v>33</v>
@@ -1949,7 +1949,7 @@
         <v>4</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="3:11">
@@ -1963,7 +1963,7 @@
         <v>1</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G19" s="1">
         <v>34</v>
@@ -1978,7 +1978,7 @@
         <v>4</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="3:11">
@@ -1992,7 +1992,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G20" s="1">
         <v>35</v>
@@ -2007,7 +2007,7 @@
         <v>4</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="3:11">
@@ -2021,7 +2021,7 @@
         <v>1</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G21" s="1">
         <v>1</v>
@@ -2036,7 +2036,7 @@
         <v>4</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="3:11">
@@ -2050,7 +2050,7 @@
         <v>1</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G22" s="1">
         <v>2003</v>
@@ -2065,7 +2065,7 @@
         <v>4</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="3:11">
@@ -2079,7 +2079,7 @@
         <v>1</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G23" s="1">
         <v>2011</v>
@@ -2094,7 +2094,7 @@
         <v>4</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="3:11">
@@ -2108,7 +2108,7 @@
         <v>1</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G24" s="1">
         <v>2004</v>
@@ -2123,7 +2123,7 @@
         <v>4</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="3:11">
@@ -2137,7 +2137,7 @@
         <v>2</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G25" s="1">
         <v>2005</v>
@@ -2152,7 +2152,7 @@
         <v>4</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="3:11">
@@ -2166,7 +2166,7 @@
         <v>2</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G26" s="1">
         <v>2006</v>
@@ -2181,7 +2181,7 @@
         <v>4</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="3:11">
@@ -2195,7 +2195,7 @@
         <v>2</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G27" s="1">
         <v>2003</v>
@@ -2210,7 +2210,7 @@
         <v>4</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="3:11">
@@ -2224,7 +2224,7 @@
         <v>2</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G28" s="1">
         <v>2002</v>
@@ -2239,7 +2239,7 @@
         <v>4</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="3:11">
@@ -2253,7 +2253,7 @@
         <v>2</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G29" s="1">
         <v>2001</v>
@@ -2268,7 +2268,7 @@
         <v>4</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="3:11">
@@ -2282,7 +2282,7 @@
         <v>2</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G30" s="1">
         <v>1</v>
@@ -2297,7 +2297,7 @@
         <v>4</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="3:11">
@@ -2311,7 +2311,7 @@
         <v>2</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G31" s="1">
         <v>15</v>
@@ -2326,7 +2326,7 @@
         <v>4</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="3:11">
@@ -2340,7 +2340,7 @@
         <v>2</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G32" s="1">
         <v>2003</v>
@@ -2355,7 +2355,7 @@
         <v>4</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="3:11">
@@ -2369,7 +2369,7 @@
         <v>2</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G33" s="1">
         <v>5</v>
@@ -2384,7 +2384,7 @@
         <v>4</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="3:11">
@@ -2398,7 +2398,7 @@
         <v>2</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G34" s="1">
         <v>16</v>
@@ -2413,7 +2413,7 @@
         <v>4</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="3:11">
@@ -2427,7 +2427,7 @@
         <v>2</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G35" s="1">
         <v>12</v>
@@ -2442,7 +2442,7 @@
         <v>4</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="3:11">
@@ -2456,7 +2456,7 @@
         <v>2</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G36" s="1">
         <v>14</v>
@@ -2471,7 +2471,7 @@
         <v>4</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="3:11">
@@ -2485,7 +2485,7 @@
         <v>2</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G37" s="1">
         <v>2004</v>
@@ -2500,7 +2500,7 @@
         <v>4</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="3:11">
@@ -2514,7 +2514,7 @@
         <v>2</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G38" s="1">
         <v>2005</v>
@@ -2529,7 +2529,7 @@
         <v>4</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="3:11">
@@ -2543,7 +2543,7 @@
         <v>2</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G39" s="1">
         <v>2006</v>
@@ -2558,7 +2558,7 @@
         <v>4</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="3:11">
@@ -2572,7 +2572,7 @@
         <v>2</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G40" s="1">
         <v>15</v>
@@ -2587,7 +2587,7 @@
         <v>4</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="3:11">
@@ -2601,7 +2601,7 @@
         <v>2</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G41" s="1">
         <v>16</v>
@@ -2616,7 +2616,7 @@
         <v>4</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="3:11">
@@ -2630,7 +2630,7 @@
         <v>2</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G42" s="1">
         <v>2002</v>
@@ -2645,7 +2645,7 @@
         <v>4</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="3:11">
@@ -2659,7 +2659,7 @@
         <v>2</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G43" s="1">
         <v>2003</v>
@@ -2674,7 +2674,7 @@
         <v>4</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="3:11">
@@ -2688,7 +2688,7 @@
         <v>2</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G44" s="1">
         <v>2011</v>
@@ -2703,7 +2703,7 @@
         <v>4</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="3:11">
@@ -2717,7 +2717,7 @@
         <v>2</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G45" s="1">
         <v>2004</v>
@@ -2732,7 +2732,7 @@
         <v>4</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="3:11">
@@ -2746,7 +2746,7 @@
         <v>2</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G46" s="1">
         <v>2005</v>
@@ -2761,7 +2761,7 @@
         <v>4</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="3:11">
@@ -2775,7 +2775,7 @@
         <v>2</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G47" s="1">
         <v>2006</v>
@@ -2790,7 +2790,7 @@
         <v>4</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="3:11">
@@ -2804,7 +2804,7 @@
         <v>2</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G48" s="1">
         <v>2002</v>
@@ -2819,7 +2819,7 @@
         <v>4</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="49" customHeight="1" spans="3:11">
@@ -2833,7 +2833,7 @@
         <v>2</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G49" s="1">
         <v>2003</v>
@@ -2848,7 +2848,7 @@
         <v>4</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="50" customHeight="1" spans="3:11">
@@ -2862,7 +2862,7 @@
         <v>2</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G50" s="1">
         <v>15</v>
@@ -2877,7 +2877,7 @@
         <v>4</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="3:11">
@@ -2891,7 +2891,7 @@
         <v>2</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G51" s="1">
         <v>16</v>
@@ -2906,7 +2906,7 @@
         <v>4</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="3:11">
@@ -2920,7 +2920,7 @@
         <v>2</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G52" s="1">
         <v>2002</v>
@@ -2935,7 +2935,7 @@
         <v>4</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="3:11">
@@ -2949,7 +2949,7 @@
         <v>2</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G53" s="1">
         <v>2003</v>
@@ -2964,7 +2964,7 @@
         <v>4</v>
       </c>
       <c r="K53" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="54" customHeight="1" spans="3:11">
@@ -2978,7 +2978,7 @@
         <v>2</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G54" s="1">
         <v>2001</v>
@@ -2993,7 +2993,7 @@
         <v>4</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="3:11">
@@ -3007,7 +3007,7 @@
         <v>2</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G55" s="1">
         <v>2004</v>
@@ -3022,7 +3022,7 @@
         <v>4</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="3:11">
@@ -3036,7 +3036,7 @@
         <v>2</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G56" s="1">
         <v>2003</v>
@@ -3051,7 +3051,7 @@
         <v>4</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="3:11">
@@ -3065,7 +3065,7 @@
         <v>2</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G57" s="1">
         <v>2002</v>
@@ -3080,7 +3080,7 @@
         <v>4</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="3:11">
@@ -3094,7 +3094,7 @@
         <v>2</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G58" s="1">
         <v>2011</v>
@@ -3109,7 +3109,7 @@
         <v>4</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="3:11">
@@ -3123,7 +3123,7 @@
         <v>2</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G59" s="1">
         <v>2001</v>
@@ -3138,7 +3138,7 @@
         <v>4</v>
       </c>
       <c r="K59" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="3:11">
@@ -3152,7 +3152,7 @@
         <v>3</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G60" s="1">
         <v>2004</v>
@@ -3167,7 +3167,7 @@
         <v>4</v>
       </c>
       <c r="K60" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="3:11">
@@ -3181,7 +3181,7 @@
         <v>3</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G61" s="1">
         <v>2005</v>
@@ -3196,7 +3196,7 @@
         <v>4</v>
       </c>
       <c r="K61" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="3:11">
@@ -3210,7 +3210,7 @@
         <v>3</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G62" s="1">
         <v>2006</v>
@@ -3225,7 +3225,7 @@
         <v>4</v>
       </c>
       <c r="K62" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="3:11">
@@ -3239,7 +3239,7 @@
         <v>3</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G63" s="1">
         <v>2003</v>
@@ -3254,7 +3254,7 @@
         <v>4</v>
       </c>
       <c r="K63" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="3:11">
@@ -3268,7 +3268,7 @@
         <v>3</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G64" s="1">
         <v>2002</v>
@@ -3283,7 +3283,7 @@
         <v>4</v>
       </c>
       <c r="K64" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="3:11">
@@ -3297,7 +3297,7 @@
         <v>3</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G65" s="1">
         <v>2001</v>
@@ -3312,7 +3312,7 @@
         <v>4</v>
       </c>
       <c r="K65" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="3:11">
@@ -3326,7 +3326,7 @@
         <v>3</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G66" s="1">
         <v>2010</v>
@@ -3341,7 +3341,7 @@
         <v>4</v>
       </c>
       <c r="K66" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="3:11">
@@ -3355,7 +3355,7 @@
         <v>3</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G67" s="1">
         <v>2011</v>
@@ -3370,7 +3370,7 @@
         <v>4</v>
       </c>
       <c r="K67" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="68" customHeight="1" spans="3:11">
@@ -3384,7 +3384,7 @@
         <v>3</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G68" s="1">
         <v>2002</v>
@@ -3399,7 +3399,7 @@
         <v>4</v>
       </c>
       <c r="K68" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="69" customHeight="1" spans="3:11">
@@ -3413,7 +3413,7 @@
         <v>3</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G69" s="1">
         <v>2003</v>
@@ -3428,7 +3428,7 @@
         <v>4</v>
       </c>
       <c r="K69" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="70" customHeight="1" spans="3:11">
@@ -3442,7 +3442,7 @@
         <v>3</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G70" s="1">
         <v>2004</v>
@@ -3457,7 +3457,7 @@
         <v>4</v>
       </c>
       <c r="K70" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="3:11">
@@ -3471,7 +3471,7 @@
         <v>3</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G71" s="1">
         <v>2005</v>
@@ -3486,7 +3486,7 @@
         <v>4</v>
       </c>
       <c r="K71" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="3:11">
@@ -3500,7 +3500,7 @@
         <v>3</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G72" s="1">
         <v>2006</v>
@@ -3515,7 +3515,7 @@
         <v>4</v>
       </c>
       <c r="K72" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="3:11">
@@ -3529,7 +3529,7 @@
         <v>3</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G73" s="1">
         <v>2002</v>
@@ -3544,7 +3544,7 @@
         <v>4</v>
       </c>
       <c r="K73" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="3:11">
@@ -3558,7 +3558,7 @@
         <v>3</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G74" s="1">
         <v>2003</v>
@@ -3573,7 +3573,7 @@
         <v>4</v>
       </c>
       <c r="K74" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="3:11">
@@ -3587,7 +3587,7 @@
         <v>3</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G75" s="1">
         <v>2001</v>
@@ -3602,7 +3602,7 @@
         <v>4</v>
       </c>
       <c r="K75" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="3:11">
@@ -3616,7 +3616,7 @@
         <v>3</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G76" s="1">
         <v>2010</v>
@@ -3631,7 +3631,7 @@
         <v>4</v>
       </c>
       <c r="K76" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="3:11">
@@ -3645,7 +3645,7 @@
         <v>3</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G77" s="1">
         <v>2011</v>
@@ -3660,7 +3660,7 @@
         <v>4</v>
       </c>
       <c r="K77" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="78" customHeight="1" spans="3:11">
@@ -3674,7 +3674,7 @@
         <v>3</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G78" s="1">
         <v>2003</v>
@@ -3689,7 +3689,7 @@
         <v>4</v>
       </c>
       <c r="K78" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="79" customHeight="1" spans="3:11">
@@ -3703,7 +3703,7 @@
         <v>3</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G79" s="1">
         <v>2002</v>
@@ -3718,7 +3718,7 @@
         <v>4</v>
       </c>
       <c r="K79" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="80" customHeight="1" spans="3:11">
@@ -3732,7 +3732,7 @@
         <v>3</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G80" s="1">
         <v>2004</v>
@@ -3747,7 +3747,7 @@
         <v>4</v>
       </c>
       <c r="K80" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="81" customHeight="1" spans="3:11">
@@ -3761,7 +3761,7 @@
         <v>3</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G81" s="1">
         <v>2005</v>
@@ -3776,7 +3776,7 @@
         <v>4</v>
       </c>
       <c r="K81" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="82" customHeight="1" spans="3:11">
@@ -3790,7 +3790,7 @@
         <v>3</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G82" s="1">
         <v>2006</v>
@@ -3805,7 +3805,7 @@
         <v>4</v>
       </c>
       <c r="K82" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="83" customHeight="1" spans="3:11">
@@ -3819,7 +3819,7 @@
         <v>3</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G83" s="1">
         <v>2002</v>
@@ -3834,7 +3834,7 @@
         <v>4</v>
       </c>
       <c r="K83" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="84" customHeight="1" spans="3:11">
@@ -3848,7 +3848,7 @@
         <v>3</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G84" s="1">
         <v>2003</v>
@@ -3863,7 +3863,7 @@
         <v>4</v>
       </c>
       <c r="K84" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="85" customHeight="1" spans="3:11">
@@ -3877,7 +3877,7 @@
         <v>3</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G85" s="1">
         <v>2001</v>
@@ -3892,7 +3892,7 @@
         <v>4</v>
       </c>
       <c r="K85" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="86" customHeight="1" spans="3:11">
@@ -3906,7 +3906,7 @@
         <v>3</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G86" s="1">
         <v>2002</v>
@@ -3921,7 +3921,7 @@
         <v>4</v>
       </c>
       <c r="K86" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="87" customHeight="1" spans="3:11">
@@ -3935,7 +3935,7 @@
         <v>3</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G87" s="1">
         <v>2011</v>
@@ -3950,7 +3950,7 @@
         <v>4</v>
       </c>
       <c r="K87" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="88" customHeight="1" spans="3:11">
@@ -3964,7 +3964,7 @@
         <v>3</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G88" s="1">
         <v>2003</v>
@@ -3979,7 +3979,7 @@
         <v>4</v>
       </c>
       <c r="K88" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="89" customHeight="1" spans="3:11">
@@ -3993,7 +3993,7 @@
         <v>3</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G89" s="1">
         <v>2002</v>
@@ -4008,7 +4008,7 @@
         <v>4</v>
       </c>
       <c r="K89" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="90" customHeight="1" spans="3:11">
@@ -4022,7 +4022,7 @@
         <v>3</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G90" s="1">
         <v>2004</v>
@@ -4037,7 +4037,7 @@
         <v>4</v>
       </c>
       <c r="K90" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="91" customHeight="1" spans="3:11">
@@ -4051,7 +4051,7 @@
         <v>3</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G91" s="1">
         <v>2005</v>
@@ -4066,7 +4066,7 @@
         <v>4</v>
       </c>
       <c r="K91" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="92" customHeight="1" spans="3:11">
@@ -4080,7 +4080,7 @@
         <v>3</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G92" s="1">
         <v>2006</v>
@@ -4095,7 +4095,7 @@
         <v>4</v>
       </c>
       <c r="K92" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="93" customHeight="1" spans="3:11">
@@ -4109,7 +4109,7 @@
         <v>3</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G93" s="1">
         <v>2002</v>
@@ -4124,7 +4124,7 @@
         <v>4</v>
       </c>
       <c r="K93" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="94" customHeight="1" spans="3:11">
@@ -4138,7 +4138,7 @@
         <v>3</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G94" s="1">
         <v>2003</v>
@@ -4153,7 +4153,7 @@
         <v>4</v>
       </c>
       <c r="K94" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="95" s="2" customFormat="1" customHeight="1" spans="3:11">
@@ -4167,7 +4167,7 @@
         <v>4</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G95" s="2">
         <v>2004</v>
@@ -4182,7 +4182,7 @@
         <v>4</v>
       </c>
       <c r="K95" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="96" customHeight="1" spans="3:11">
@@ -4196,7 +4196,7 @@
         <v>4</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G96" s="1">
         <v>2005</v>
@@ -4211,7 +4211,7 @@
         <v>4</v>
       </c>
       <c r="K96" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="97" customHeight="1" spans="3:11">
@@ -4225,7 +4225,7 @@
         <v>4</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G97" s="1">
         <v>2006</v>
@@ -4240,7 +4240,7 @@
         <v>4</v>
       </c>
       <c r="K97" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="98" customHeight="1" spans="3:11">
@@ -4254,7 +4254,7 @@
         <v>4</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G98" s="1">
         <v>2012</v>
@@ -4269,7 +4269,7 @@
         <v>4</v>
       </c>
       <c r="K98" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="99" customHeight="1" spans="3:11">
@@ -4283,7 +4283,7 @@
         <v>4</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G99" s="1">
         <v>2001</v>
@@ -4298,10 +4298,16 @@
         <v>4</v>
       </c>
       <c r="K99" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="100" customHeight="1" spans="3:11">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="100" customHeight="1" spans="1:11">
+      <c r="A100" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>128</v>
+      </c>
       <c r="C100" s="1">
         <v>40000145</v>
       </c>
@@ -4327,10 +4333,16 @@
         <v>4</v>
       </c>
       <c r="K100" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="101" customHeight="1" spans="3:11">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="101" customHeight="1" spans="1:11">
+      <c r="A101" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>128</v>
+      </c>
       <c r="C101" s="1">
         <v>40000146</v>
       </c>
@@ -4359,7 +4371,13 @@
         <v>131</v>
       </c>
     </row>
-    <row r="102" customHeight="1" spans="3:11">
+    <row r="102" customHeight="1" spans="1:11">
+      <c r="A102" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>128</v>
+      </c>
       <c r="C102" s="1">
         <v>40000147</v>
       </c>
@@ -4388,7 +4406,13 @@
         <v>133</v>
       </c>
     </row>
-    <row r="103" customHeight="1" spans="3:11">
+    <row r="103" customHeight="1" spans="1:11">
+      <c r="A103" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>128</v>
+      </c>
       <c r="C103" s="1">
         <v>40000148</v>
       </c>
@@ -4417,7 +4441,13 @@
         <v>135</v>
       </c>
     </row>
-    <row r="104" customHeight="1" spans="3:11">
+    <row r="104" customHeight="1" spans="1:11">
+      <c r="A104" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>128</v>
+      </c>
       <c r="C104" s="1">
         <v>40000149</v>
       </c>
@@ -4443,10 +4473,16 @@
         <v>4</v>
       </c>
       <c r="K104" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="105" customHeight="1" spans="3:11">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="105" customHeight="1" spans="1:11">
+      <c r="A105" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>128</v>
+      </c>
       <c r="C105" s="1">
         <v>40000150</v>
       </c>
@@ -4472,10 +4508,16 @@
         <v>4</v>
       </c>
       <c r="K105" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="106" customHeight="1" spans="3:11">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="106" customHeight="1" spans="1:11">
+      <c r="A106" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>128</v>
+      </c>
       <c r="C106" s="1">
         <v>40000151</v>
       </c>
@@ -4501,10 +4543,16 @@
         <v>4</v>
       </c>
       <c r="K106" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="107" customHeight="1" spans="3:11">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="107" customHeight="1" spans="1:11">
+      <c r="A107" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>128</v>
+      </c>
       <c r="C107" s="1">
         <v>40000152</v>
       </c>
@@ -4530,10 +4578,16 @@
         <v>4</v>
       </c>
       <c r="K107" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="108" customHeight="1" spans="3:11">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="108" customHeight="1" spans="1:11">
+      <c r="A108" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>128</v>
+      </c>
       <c r="C108" s="1">
         <v>40000153</v>
       </c>
@@ -4559,10 +4613,16 @@
         <v>4</v>
       </c>
       <c r="K108" s="1" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="109" customHeight="1" spans="3:11">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="109" customHeight="1" spans="1:11">
+      <c r="A109" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>128</v>
+      </c>
       <c r="C109" s="1">
         <v>40000154</v>
       </c>
@@ -4588,10 +4648,16 @@
         <v>4</v>
       </c>
       <c r="K109" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="110" customHeight="1" spans="3:11">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="110" customHeight="1" spans="1:11">
+      <c r="A110" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>128</v>
+      </c>
       <c r="C110" s="1">
         <v>40000155</v>
       </c>
@@ -4617,10 +4683,16 @@
         <v>4</v>
       </c>
       <c r="K110" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="111" customHeight="1" spans="3:11">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="111" customHeight="1" spans="1:11">
+      <c r="A111" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>128</v>
+      </c>
       <c r="C111" s="1">
         <v>40000156</v>
       </c>
@@ -4646,10 +4718,16 @@
         <v>4</v>
       </c>
       <c r="K111" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="112" customHeight="1" spans="3:11">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="112" customHeight="1" spans="1:11">
+      <c r="A112" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>128</v>
+      </c>
       <c r="C112" s="1">
         <v>40000157</v>
       </c>
@@ -4675,10 +4753,16 @@
         <v>4</v>
       </c>
       <c r="K112" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="113" customHeight="1" spans="3:11">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="113" customHeight="1" spans="1:11">
+      <c r="A113" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>128</v>
+      </c>
       <c r="C113" s="1">
         <v>40000158</v>
       </c>
@@ -4707,7 +4791,13 @@
         <v>131</v>
       </c>
     </row>
-    <row r="114" customHeight="1" spans="3:11">
+    <row r="114" customHeight="1" spans="1:11">
+      <c r="A114" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>128</v>
+      </c>
       <c r="C114" s="1">
         <v>40000159</v>
       </c>
@@ -4736,7 +4826,13 @@
         <v>133</v>
       </c>
     </row>
-    <row r="115" customHeight="1" spans="3:11">
+    <row r="115" customHeight="1" spans="1:11">
+      <c r="A115" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>128</v>
+      </c>
       <c r="C115" s="1">
         <v>40000160</v>
       </c>
@@ -4765,7 +4861,13 @@
         <v>135</v>
       </c>
     </row>
-    <row r="116" customHeight="1" spans="3:11">
+    <row r="116" customHeight="1" spans="1:11">
+      <c r="A116" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>128</v>
+      </c>
       <c r="C116" s="1">
         <v>40000161</v>
       </c>
@@ -4791,10 +4893,16 @@
         <v>4</v>
       </c>
       <c r="K116" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="117" customHeight="1" spans="3:11">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="117" customHeight="1" spans="1:11">
+      <c r="A117" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>128</v>
+      </c>
       <c r="C117" s="1">
         <v>40000162</v>
       </c>
@@ -4820,10 +4928,16 @@
         <v>4</v>
       </c>
       <c r="K117" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="118" customHeight="1" spans="3:11">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="118" customHeight="1" spans="1:11">
+      <c r="A118" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>128</v>
+      </c>
       <c r="C118" s="1">
         <v>40000163</v>
       </c>
@@ -4849,10 +4963,16 @@
         <v>4</v>
       </c>
       <c r="K118" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="119" customHeight="1" spans="3:11">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="119" customHeight="1" spans="1:11">
+      <c r="A119" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>128</v>
+      </c>
       <c r="C119" s="1">
         <v>40000164</v>
       </c>
@@ -4878,10 +4998,16 @@
         <v>4</v>
       </c>
       <c r="K119" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="120" customHeight="1" spans="3:11">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="120" customHeight="1" spans="1:11">
+      <c r="A120" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>128</v>
+      </c>
       <c r="C120" s="1">
         <v>40000165</v>
       </c>
@@ -4907,10 +5033,16 @@
         <v>4</v>
       </c>
       <c r="K120" s="1" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="121" customHeight="1" spans="3:11">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="121" customHeight="1" spans="1:11">
+      <c r="A121" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>128</v>
+      </c>
       <c r="C121" s="1">
         <v>40000166</v>
       </c>
@@ -4936,10 +5068,16 @@
         <v>4</v>
       </c>
       <c r="K121" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="122" customHeight="1" spans="3:11">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="122" customHeight="1" spans="1:11">
+      <c r="A122" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>128</v>
+      </c>
       <c r="C122" s="1">
         <v>40000167</v>
       </c>
@@ -4965,10 +5103,16 @@
         <v>4</v>
       </c>
       <c r="K122" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="123" customHeight="1" spans="3:11">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="123" customHeight="1" spans="1:11">
+      <c r="A123" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>128</v>
+      </c>
       <c r="C123" s="1">
         <v>40000168</v>
       </c>
@@ -4994,10 +5138,16 @@
         <v>4</v>
       </c>
       <c r="K123" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="124" customHeight="1" spans="3:11">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="124" customHeight="1" spans="1:11">
+      <c r="A124" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>128</v>
+      </c>
       <c r="C124" s="1">
         <v>40000169</v>
       </c>
@@ -5023,10 +5173,16 @@
         <v>4</v>
       </c>
       <c r="K124" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="125" customHeight="1" spans="3:11">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="125" customHeight="1" spans="1:11">
+      <c r="A125" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>128</v>
+      </c>
       <c r="C125" s="1">
         <v>40000170</v>
       </c>
@@ -5055,7 +5211,13 @@
         <v>131</v>
       </c>
     </row>
-    <row r="126" customHeight="1" spans="3:11">
+    <row r="126" customHeight="1" spans="1:11">
+      <c r="A126" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>128</v>
+      </c>
       <c r="C126" s="1">
         <v>40000171</v>
       </c>
@@ -5084,7 +5246,13 @@
         <v>133</v>
       </c>
     </row>
-    <row r="127" customHeight="1" spans="3:11">
+    <row r="127" customHeight="1" spans="1:11">
+      <c r="A127" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>128</v>
+      </c>
       <c r="C127" s="1">
         <v>40000172</v>
       </c>
@@ -5113,7 +5281,13 @@
         <v>135</v>
       </c>
     </row>
-    <row r="128" customHeight="1" spans="3:11">
+    <row r="128" customHeight="1" spans="1:11">
+      <c r="A128" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>128</v>
+      </c>
       <c r="C128" s="1">
         <v>40000173</v>
       </c>
@@ -5139,10 +5313,16 @@
         <v>4</v>
       </c>
       <c r="K128" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="129" customHeight="1" spans="3:11">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="129" customHeight="1" spans="1:11">
+      <c r="A129" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>128</v>
+      </c>
       <c r="C129" s="1">
         <v>40000174</v>
       </c>
@@ -5168,12 +5348,12 @@
         <v>4</v>
       </c>
       <c r="K129" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:F5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:F3 C4:F4 C5:F5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/HalidomConfig.xlsx
+++ b/Excel/HalidomConfig.xlsx
@@ -407,12 +407,12 @@
     <t>深渊猫爪</t>
   </si>
   <si>
+    <t>深渊花朵</t>
+  </si>
+  <si>
     <t>韧性倍率</t>
   </si>
   <si>
-    <t>深渊花朵</t>
-  </si>
-  <si>
     <t>#</t>
   </si>
   <si>
@@ -422,25 +422,25 @@
     <t>深渊蝠翼</t>
   </si>
   <si>
+    <t>深渊魂火</t>
+  </si>
+  <si>
+    <t>深渊腐肉</t>
+  </si>
+  <si>
     <t>物伤倍率</t>
   </si>
   <si>
-    <t>深渊魂火</t>
+    <t>深渊蛇胆</t>
   </si>
   <si>
     <t>法伤倍率</t>
   </si>
   <si>
-    <t>深渊腐肉</t>
+    <t>深渊狼爪</t>
   </si>
   <si>
     <t>道伤倍率</t>
-  </si>
-  <si>
-    <t>深渊蛇胆</t>
-  </si>
-  <si>
-    <t>深渊狼爪</t>
   </si>
   <si>
     <t>深渊虫皮</t>
@@ -4257,19 +4257,19 @@
         <v>125</v>
       </c>
       <c r="G98" s="1">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="H98" s="1">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="I98" s="1">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="J98" s="1">
         <v>4</v>
       </c>
       <c r="K98" s="1" t="s">
-        <v>126</v>
+        <v>92</v>
       </c>
     </row>
     <row r="99" customHeight="1" spans="3:11">
@@ -4283,22 +4283,22 @@
         <v>4</v>
       </c>
       <c r="F99" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="G99" s="1">
+        <v>2012</v>
+      </c>
+      <c r="H99" s="1">
+        <v>25</v>
+      </c>
+      <c r="I99" s="1">
+        <v>25</v>
+      </c>
+      <c r="J99" s="1">
+        <v>4</v>
+      </c>
+      <c r="K99" s="1" t="s">
         <v>127</v>
-      </c>
-      <c r="G99" s="1">
-        <v>2001</v>
-      </c>
-      <c r="H99" s="1">
-        <v>7</v>
-      </c>
-      <c r="I99" s="1">
-        <v>7</v>
-      </c>
-      <c r="J99" s="1">
-        <v>4</v>
-      </c>
-      <c r="K99" s="1" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="100" customHeight="1" spans="1:11">
@@ -4321,19 +4321,19 @@
         <v>129</v>
       </c>
       <c r="G100" s="1">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="H100" s="1">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="I100" s="1">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="J100" s="1">
         <v>4</v>
       </c>
       <c r="K100" s="1" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
     </row>
     <row r="101" customHeight="1" spans="1:11">
@@ -4356,19 +4356,19 @@
         <v>130</v>
       </c>
       <c r="G101" s="1">
-        <v>2007</v>
+        <v>2003</v>
       </c>
       <c r="H101" s="1">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="I101" s="1">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="J101" s="1">
         <v>4</v>
       </c>
       <c r="K101" s="1" t="s">
-        <v>131</v>
+        <v>17</v>
       </c>
     </row>
     <row r="102" customHeight="1" spans="1:11">
@@ -4388,10 +4388,10 @@
         <v>4</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G102" s="1">
-        <v>2008</v>
+        <v>2001</v>
       </c>
       <c r="H102" s="1">
         <v>7</v>
@@ -4403,7 +4403,7 @@
         <v>4</v>
       </c>
       <c r="K102" s="1" t="s">
-        <v>133</v>
+        <v>52</v>
       </c>
     </row>
     <row r="103" customHeight="1" spans="1:11">
@@ -4423,10 +4423,10 @@
         <v>4</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="G103" s="1">
-        <v>2009</v>
+        <v>2007</v>
       </c>
       <c r="H103" s="1">
         <v>7</v>
@@ -4438,7 +4438,7 @@
         <v>4</v>
       </c>
       <c r="K103" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="104" customHeight="1" spans="1:11">
@@ -4458,22 +4458,22 @@
         <v>4</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G104" s="1">
-        <v>2012</v>
+        <v>2008</v>
       </c>
       <c r="H104" s="1">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="I104" s="1">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="J104" s="1">
         <v>4</v>
       </c>
       <c r="K104" s="1" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
     </row>
     <row r="105" customHeight="1" spans="1:11">
@@ -4493,22 +4493,22 @@
         <v>4</v>
       </c>
       <c r="F105" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="G105" s="1">
+        <v>2009</v>
+      </c>
+      <c r="H105" s="1">
+        <v>7</v>
+      </c>
+      <c r="I105" s="1">
+        <v>7</v>
+      </c>
+      <c r="J105" s="1">
+        <v>4</v>
+      </c>
+      <c r="K105" s="1" t="s">
         <v>137</v>
-      </c>
-      <c r="G105" s="1">
-        <v>2011</v>
-      </c>
-      <c r="H105" s="1">
-        <v>7</v>
-      </c>
-      <c r="I105" s="1">
-        <v>7</v>
-      </c>
-      <c r="J105" s="1">
-        <v>4</v>
-      </c>
-      <c r="K105" s="1" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="106" customHeight="1" spans="1:11">
@@ -4531,19 +4531,19 @@
         <v>138</v>
       </c>
       <c r="G106" s="1">
-        <v>2003</v>
+        <v>2012</v>
       </c>
       <c r="H106" s="1">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="I106" s="1">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="J106" s="1">
         <v>4</v>
       </c>
       <c r="K106" s="1" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
     </row>
     <row r="107" customHeight="1" spans="1:11">
@@ -4566,19 +4566,19 @@
         <v>139</v>
       </c>
       <c r="G107" s="1">
-        <v>2004</v>
+        <v>2002</v>
       </c>
       <c r="H107" s="1">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c r="I107" s="1">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c r="J107" s="1">
         <v>4</v>
       </c>
       <c r="K107" s="1" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
     </row>
     <row r="108" customHeight="1" spans="1:11">
@@ -4601,19 +4601,19 @@
         <v>140</v>
       </c>
       <c r="G108" s="1">
-        <v>2005</v>
+        <v>2003</v>
       </c>
       <c r="H108" s="1">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="I108" s="1">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="J108" s="1">
         <v>4</v>
       </c>
       <c r="K108" s="1" t="s">
-        <v>123</v>
+        <v>17</v>
       </c>
     </row>
     <row r="109" customHeight="1" spans="1:11">
@@ -4635,20 +4635,20 @@
       <c r="F109" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="G109" s="1">
-        <v>2006</v>
-      </c>
-      <c r="H109" s="1">
-        <v>25</v>
-      </c>
-      <c r="I109" s="1">
-        <v>25</v>
-      </c>
-      <c r="J109" s="1">
-        <v>4</v>
-      </c>
-      <c r="K109" s="1" t="s">
-        <v>47</v>
+      <c r="G109" s="2">
+        <v>2004</v>
+      </c>
+      <c r="H109" s="2">
+        <v>7</v>
+      </c>
+      <c r="I109" s="2">
+        <v>7</v>
+      </c>
+      <c r="J109" s="2">
+        <v>4</v>
+      </c>
+      <c r="K109" s="2" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="110" customHeight="1" spans="1:11">
@@ -4671,7 +4671,7 @@
         <v>142</v>
       </c>
       <c r="G110" s="1">
-        <v>2012</v>
+        <v>2005</v>
       </c>
       <c r="H110" s="1">
         <v>7</v>
@@ -4683,7 +4683,7 @@
         <v>4</v>
       </c>
       <c r="K110" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="111" customHeight="1" spans="1:11">
@@ -4706,19 +4706,19 @@
         <v>143</v>
       </c>
       <c r="G111" s="1">
-        <v>2001</v>
+        <v>2006</v>
       </c>
       <c r="H111" s="1">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="I111" s="1">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="J111" s="1">
         <v>4</v>
       </c>
       <c r="K111" s="1" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="112" customHeight="1" spans="1:11">
@@ -4741,7 +4741,7 @@
         <v>144</v>
       </c>
       <c r="G112" s="1">
-        <v>2003</v>
+        <v>2011</v>
       </c>
       <c r="H112" s="1">
         <v>7</v>
@@ -4753,7 +4753,7 @@
         <v>4</v>
       </c>
       <c r="K112" s="1" t="s">
-        <v>17</v>
+        <v>92</v>
       </c>
     </row>
     <row r="113" customHeight="1" spans="1:11">
@@ -4776,19 +4776,19 @@
         <v>145</v>
       </c>
       <c r="G113" s="1">
-        <v>2007</v>
+        <v>2012</v>
       </c>
       <c r="H113" s="1">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="I113" s="1">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="J113" s="1">
         <v>4</v>
       </c>
       <c r="K113" s="1" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
     </row>
     <row r="114" customHeight="1" spans="1:11">
@@ -4811,19 +4811,19 @@
         <v>146</v>
       </c>
       <c r="G114" s="1">
-        <v>2008</v>
+        <v>2002</v>
       </c>
       <c r="H114" s="1">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c r="I114" s="1">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c r="J114" s="1">
         <v>4</v>
       </c>
       <c r="K114" s="1" t="s">
-        <v>133</v>
+        <v>50</v>
       </c>
     </row>
     <row r="115" customHeight="1" spans="1:11">
@@ -4846,19 +4846,19 @@
         <v>147</v>
       </c>
       <c r="G115" s="1">
-        <v>2009</v>
+        <v>2003</v>
       </c>
       <c r="H115" s="1">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="I115" s="1">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="J115" s="1">
         <v>4</v>
       </c>
       <c r="K115" s="1" t="s">
-        <v>135</v>
+        <v>17</v>
       </c>
     </row>
     <row r="116" customHeight="1" spans="1:11">
@@ -4881,7 +4881,7 @@
         <v>148</v>
       </c>
       <c r="G116" s="1">
-        <v>2012</v>
+        <v>2001</v>
       </c>
       <c r="H116" s="1">
         <v>7</v>
@@ -4893,7 +4893,7 @@
         <v>4</v>
       </c>
       <c r="K116" s="1" t="s">
-        <v>126</v>
+        <v>52</v>
       </c>
     </row>
     <row r="117" customHeight="1" spans="1:11">
@@ -4916,19 +4916,19 @@
         <v>149</v>
       </c>
       <c r="G117" s="1">
-        <v>2011</v>
+        <v>2007</v>
       </c>
       <c r="H117" s="1">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="I117" s="1">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="J117" s="1">
         <v>4</v>
       </c>
       <c r="K117" s="1" t="s">
-        <v>92</v>
+        <v>133</v>
       </c>
     </row>
     <row r="118" customHeight="1" spans="1:11">
@@ -4951,19 +4951,19 @@
         <v>150</v>
       </c>
       <c r="G118" s="1">
-        <v>2003</v>
+        <v>2008</v>
       </c>
       <c r="H118" s="1">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="I118" s="1">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="J118" s="1">
         <v>4</v>
       </c>
       <c r="K118" s="1" t="s">
-        <v>17</v>
+        <v>135</v>
       </c>
     </row>
     <row r="119" customHeight="1" spans="1:11">
@@ -4986,7 +4986,7 @@
         <v>151</v>
       </c>
       <c r="G119" s="1">
-        <v>2004</v>
+        <v>2009</v>
       </c>
       <c r="H119" s="1">
         <v>7</v>
@@ -4998,7 +4998,7 @@
         <v>4</v>
       </c>
       <c r="K119" s="1" t="s">
-        <v>43</v>
+        <v>137</v>
       </c>
     </row>
     <row r="120" customHeight="1" spans="1:11">
@@ -5021,19 +5021,19 @@
         <v>152</v>
       </c>
       <c r="G120" s="1">
-        <v>2005</v>
+        <v>2012</v>
       </c>
       <c r="H120" s="1">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="I120" s="1">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="J120" s="1">
         <v>4</v>
       </c>
       <c r="K120" s="1" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
     </row>
     <row r="121" customHeight="1" spans="1:11">
@@ -5056,19 +5056,19 @@
         <v>153</v>
       </c>
       <c r="G121" s="1">
-        <v>2006</v>
+        <v>2002</v>
       </c>
       <c r="H121" s="1">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="I121" s="1">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="J121" s="1">
         <v>4</v>
       </c>
       <c r="K121" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="122" customHeight="1" spans="1:11">
@@ -5091,19 +5091,19 @@
         <v>154</v>
       </c>
       <c r="G122" s="1">
-        <v>2012</v>
+        <v>2003</v>
       </c>
       <c r="H122" s="1">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="I122" s="1">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="J122" s="1">
         <v>4</v>
       </c>
       <c r="K122" s="1" t="s">
-        <v>126</v>
+        <v>17</v>
       </c>
     </row>
     <row r="123" customHeight="1" spans="1:11">
@@ -5125,20 +5125,20 @@
       <c r="F123" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="G123" s="1">
-        <v>2001</v>
-      </c>
-      <c r="H123" s="1">
-        <v>40</v>
-      </c>
-      <c r="I123" s="1">
-        <v>40</v>
-      </c>
-      <c r="J123" s="1">
-        <v>4</v>
-      </c>
-      <c r="K123" s="1" t="s">
-        <v>52</v>
+      <c r="G123" s="2">
+        <v>2004</v>
+      </c>
+      <c r="H123" s="2">
+        <v>7</v>
+      </c>
+      <c r="I123" s="2">
+        <v>7</v>
+      </c>
+      <c r="J123" s="2">
+        <v>4</v>
+      </c>
+      <c r="K123" s="2" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="124" customHeight="1" spans="1:11">
@@ -5161,7 +5161,7 @@
         <v>156</v>
       </c>
       <c r="G124" s="1">
-        <v>2003</v>
+        <v>2005</v>
       </c>
       <c r="H124" s="1">
         <v>7</v>
@@ -5173,7 +5173,7 @@
         <v>4</v>
       </c>
       <c r="K124" s="1" t="s">
-        <v>17</v>
+        <v>123</v>
       </c>
     </row>
     <row r="125" customHeight="1" spans="1:11">
@@ -5196,7 +5196,7 @@
         <v>157</v>
       </c>
       <c r="G125" s="1">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="H125" s="1">
         <v>7</v>
@@ -5208,7 +5208,7 @@
         <v>4</v>
       </c>
       <c r="K125" s="1" t="s">
-        <v>131</v>
+        <v>47</v>
       </c>
     </row>
     <row r="126" customHeight="1" spans="1:11">
@@ -5231,7 +5231,7 @@
         <v>158</v>
       </c>
       <c r="G126" s="1">
-        <v>2008</v>
+        <v>2011</v>
       </c>
       <c r="H126" s="1">
         <v>7</v>
@@ -5243,7 +5243,7 @@
         <v>4</v>
       </c>
       <c r="K126" s="1" t="s">
-        <v>133</v>
+        <v>92</v>
       </c>
     </row>
     <row r="127" customHeight="1" spans="1:11">
@@ -5266,7 +5266,7 @@
         <v>159</v>
       </c>
       <c r="G127" s="1">
-        <v>2009</v>
+        <v>2012</v>
       </c>
       <c r="H127" s="1">
         <v>25</v>
@@ -5278,7 +5278,7 @@
         <v>4</v>
       </c>
       <c r="K127" s="1" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
     </row>
     <row r="128" customHeight="1" spans="1:11">
@@ -5301,19 +5301,19 @@
         <v>160</v>
       </c>
       <c r="G128" s="1">
-        <v>2012</v>
+        <v>2002</v>
       </c>
       <c r="H128" s="1">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c r="I128" s="1">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c r="J128" s="1">
         <v>4</v>
       </c>
       <c r="K128" s="1" t="s">
-        <v>126</v>
+        <v>50</v>
       </c>
     </row>
     <row r="129" customHeight="1" spans="1:11">
@@ -5336,7 +5336,7 @@
         <v>161</v>
       </c>
       <c r="G129" s="1">
-        <v>2011</v>
+        <v>2003</v>
       </c>
       <c r="H129" s="1">
         <v>40</v>
@@ -5348,12 +5348,12 @@
         <v>4</v>
       </c>
       <c r="K129" s="1" t="s">
-        <v>92</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:F3 C4:F4 C5:F5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:F5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/HalidomConfig.xlsx
+++ b/Excel/HalidomConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -4257,7 +4257,7 @@
         <v>125</v>
       </c>
       <c r="G98" s="1">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="H98" s="1">
         <v>7</v>
@@ -4741,7 +4741,7 @@
         <v>144</v>
       </c>
       <c r="G112" s="1">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="H112" s="1">
         <v>7</v>
@@ -5231,7 +5231,7 @@
         <v>158</v>
       </c>
       <c r="G126" s="1">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="H126" s="1">
         <v>7</v>

--- a/Excel/HalidomConfig.xlsx
+++ b/Excel/HalidomConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="162">
   <si>
     <t>Id</t>
   </si>
@@ -413,28 +413,28 @@
     <t>韧性倍率</t>
   </si>
   <si>
+    <t>深渊冰晶</t>
+  </si>
+  <si>
+    <t>深渊蝠翼</t>
+  </si>
+  <si>
+    <t>深渊魂火</t>
+  </si>
+  <si>
+    <t>深渊腐肉</t>
+  </si>
+  <si>
+    <t>物伤倍率</t>
+  </si>
+  <si>
+    <t>深渊蛇胆</t>
+  </si>
+  <si>
+    <t>法伤倍率</t>
+  </si>
+  <si>
     <t>#</t>
-  </si>
-  <si>
-    <t>深渊冰晶</t>
-  </si>
-  <si>
-    <t>深渊蝠翼</t>
-  </si>
-  <si>
-    <t>深渊魂火</t>
-  </si>
-  <si>
-    <t>深渊腐肉</t>
-  </si>
-  <si>
-    <t>物伤倍率</t>
-  </si>
-  <si>
-    <t>深渊蛇胆</t>
-  </si>
-  <si>
-    <t>法伤倍率</t>
   </si>
   <si>
     <t>深渊狼爪</t>
@@ -4301,13 +4301,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="100" customHeight="1" spans="1:11">
-      <c r="A100" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="B100" s="1" t="s">
-        <v>128</v>
-      </c>
+    <row r="100" customHeight="1" spans="3:11">
       <c r="C100" s="1">
         <v>40000145</v>
       </c>
@@ -4318,7 +4312,7 @@
         <v>4</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G100" s="1">
         <v>2002</v>
@@ -4336,13 +4330,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="101" customHeight="1" spans="1:11">
-      <c r="A101" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="B101" s="1" t="s">
-        <v>128</v>
-      </c>
+    <row r="101" customHeight="1" spans="3:11">
       <c r="C101" s="1">
         <v>40000146</v>
       </c>
@@ -4353,7 +4341,7 @@
         <v>4</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G101" s="1">
         <v>2003</v>
@@ -4371,13 +4359,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="102" customHeight="1" spans="1:11">
-      <c r="A102" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="B102" s="1" t="s">
-        <v>128</v>
-      </c>
+    <row r="102" customHeight="1" spans="3:11">
       <c r="C102" s="1">
         <v>40000147</v>
       </c>
@@ -4388,7 +4370,7 @@
         <v>4</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G102" s="1">
         <v>2001</v>
@@ -4406,13 +4388,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="103" customHeight="1" spans="1:11">
-      <c r="A103" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="B103" s="1" t="s">
-        <v>128</v>
-      </c>
+    <row r="103" customHeight="1" spans="3:11">
       <c r="C103" s="1">
         <v>40000148</v>
       </c>
@@ -4423,7 +4399,7 @@
         <v>4</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G103" s="1">
         <v>2007</v>
@@ -4438,16 +4414,10 @@
         <v>4</v>
       </c>
       <c r="K103" s="1" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="104" customHeight="1" spans="1:11">
-      <c r="A104" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="B104" s="1" t="s">
-        <v>128</v>
-      </c>
+        <v>132</v>
+      </c>
+    </row>
+    <row r="104" customHeight="1" spans="3:11">
       <c r="C104" s="1">
         <v>40000149</v>
       </c>
@@ -4458,7 +4428,7 @@
         <v>4</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G104" s="1">
         <v>2008</v>
@@ -4473,15 +4443,15 @@
         <v>4</v>
       </c>
       <c r="K104" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="105" customHeight="1" spans="1:11">
       <c r="A105" s="1" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="C105" s="1">
         <v>40000150</v>
@@ -4513,10 +4483,10 @@
     </row>
     <row r="106" customHeight="1" spans="1:11">
       <c r="A106" s="1" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="C106" s="1">
         <v>40000151</v>
@@ -4548,10 +4518,10 @@
     </row>
     <row r="107" customHeight="1" spans="1:11">
       <c r="A107" s="1" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="C107" s="1">
         <v>40000152</v>
@@ -4583,10 +4553,10 @@
     </row>
     <row r="108" customHeight="1" spans="1:11">
       <c r="A108" s="1" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="C108" s="1">
         <v>40000153</v>
@@ -4618,10 +4588,10 @@
     </row>
     <row r="109" customHeight="1" spans="1:11">
       <c r="A109" s="1" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="C109" s="1">
         <v>40000154</v>
@@ -4653,10 +4623,10 @@
     </row>
     <row r="110" customHeight="1" spans="1:11">
       <c r="A110" s="1" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="C110" s="1">
         <v>40000155</v>
@@ -4688,10 +4658,10 @@
     </row>
     <row r="111" customHeight="1" spans="1:11">
       <c r="A111" s="1" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="C111" s="1">
         <v>40000156</v>
@@ -4723,10 +4693,10 @@
     </row>
     <row r="112" customHeight="1" spans="1:11">
       <c r="A112" s="1" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="C112" s="1">
         <v>40000157</v>
@@ -4758,10 +4728,10 @@
     </row>
     <row r="113" customHeight="1" spans="1:11">
       <c r="A113" s="1" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="C113" s="1">
         <v>40000158</v>
@@ -4793,10 +4763,10 @@
     </row>
     <row r="114" customHeight="1" spans="1:11">
       <c r="A114" s="1" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="C114" s="1">
         <v>40000159</v>
@@ -4828,10 +4798,10 @@
     </row>
     <row r="115" customHeight="1" spans="1:11">
       <c r="A115" s="1" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="C115" s="1">
         <v>40000160</v>
@@ -4863,10 +4833,10 @@
     </row>
     <row r="116" customHeight="1" spans="1:11">
       <c r="A116" s="1" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="C116" s="1">
         <v>40000161</v>
@@ -4898,10 +4868,10 @@
     </row>
     <row r="117" customHeight="1" spans="1:11">
       <c r="A117" s="1" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="C117" s="1">
         <v>40000162</v>
@@ -4928,15 +4898,15 @@
         <v>4</v>
       </c>
       <c r="K117" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="118" customHeight="1" spans="1:11">
       <c r="A118" s="1" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="C118" s="1">
         <v>40000163</v>
@@ -4963,15 +4933,15 @@
         <v>4</v>
       </c>
       <c r="K118" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="119" customHeight="1" spans="1:11">
       <c r="A119" s="1" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="C119" s="1">
         <v>40000164</v>
@@ -5003,10 +4973,10 @@
     </row>
     <row r="120" customHeight="1" spans="1:11">
       <c r="A120" s="1" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="C120" s="1">
         <v>40000165</v>
@@ -5038,10 +5008,10 @@
     </row>
     <row r="121" customHeight="1" spans="1:11">
       <c r="A121" s="1" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="C121" s="1">
         <v>40000166</v>
@@ -5073,10 +5043,10 @@
     </row>
     <row r="122" customHeight="1" spans="1:11">
       <c r="A122" s="1" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="C122" s="1">
         <v>40000167</v>
@@ -5108,10 +5078,10 @@
     </row>
     <row r="123" customHeight="1" spans="1:11">
       <c r="A123" s="1" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="C123" s="1">
         <v>40000168</v>
@@ -5143,10 +5113,10 @@
     </row>
     <row r="124" customHeight="1" spans="1:11">
       <c r="A124" s="1" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="C124" s="1">
         <v>40000169</v>
@@ -5178,10 +5148,10 @@
     </row>
     <row r="125" customHeight="1" spans="1:11">
       <c r="A125" s="1" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="C125" s="1">
         <v>40000170</v>
@@ -5213,10 +5183,10 @@
     </row>
     <row r="126" customHeight="1" spans="1:11">
       <c r="A126" s="1" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="C126" s="1">
         <v>40000171</v>
@@ -5248,10 +5218,10 @@
     </row>
     <row r="127" customHeight="1" spans="1:11">
       <c r="A127" s="1" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="C127" s="1">
         <v>40000172</v>
@@ -5283,10 +5253,10 @@
     </row>
     <row r="128" customHeight="1" spans="1:11">
       <c r="A128" s="1" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="C128" s="1">
         <v>40000173</v>
@@ -5318,10 +5288,10 @@
     </row>
     <row r="129" customHeight="1" spans="1:11">
       <c r="A129" s="1" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="C129" s="1">
         <v>40000174</v>

--- a/Excel/HalidomConfig.xlsx
+++ b/Excel/HalidomConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="162">
   <si>
     <t>Id</t>
   </si>
@@ -434,25 +434,25 @@
     <t>法伤倍率</t>
   </si>
   <si>
+    <t>深渊狼爪</t>
+  </si>
+  <si>
+    <t>道伤倍率</t>
+  </si>
+  <si>
+    <t>深渊虫皮</t>
+  </si>
+  <si>
+    <t>深渊鹰羽</t>
+  </si>
+  <si>
+    <t>深渊虫角</t>
+  </si>
+  <si>
+    <t>深渊蜈膏</t>
+  </si>
+  <si>
     <t>#</t>
-  </si>
-  <si>
-    <t>深渊狼爪</t>
-  </si>
-  <si>
-    <t>道伤倍率</t>
-  </si>
-  <si>
-    <t>深渊虫皮</t>
-  </si>
-  <si>
-    <t>深渊鹰羽</t>
-  </si>
-  <si>
-    <t>深渊虫角</t>
-  </si>
-  <si>
-    <t>深渊蜈膏</t>
   </si>
   <si>
     <t>深渊虫心</t>
@@ -4446,13 +4446,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="105" customHeight="1" spans="1:11">
-      <c r="A105" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="B105" s="1" t="s">
-        <v>135</v>
-      </c>
+    <row r="105" customHeight="1" spans="3:11">
       <c r="C105" s="1">
         <v>40000150</v>
       </c>
@@ -4463,7 +4457,7 @@
         <v>4</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G105" s="1">
         <v>2009</v>
@@ -4478,16 +4472,10 @@
         <v>4</v>
       </c>
       <c r="K105" s="1" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="106" customHeight="1" spans="1:11">
-      <c r="A106" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="B106" s="1" t="s">
-        <v>135</v>
-      </c>
+        <v>136</v>
+      </c>
+    </row>
+    <row r="106" customHeight="1" spans="3:11">
       <c r="C106" s="1">
         <v>40000151</v>
       </c>
@@ -4498,7 +4486,7 @@
         <v>4</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G106" s="1">
         <v>2012</v>
@@ -4516,13 +4504,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="107" customHeight="1" spans="1:11">
-      <c r="A107" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="B107" s="1" t="s">
-        <v>135</v>
-      </c>
+    <row r="107" customHeight="1" spans="3:11">
       <c r="C107" s="1">
         <v>40000152</v>
       </c>
@@ -4533,7 +4515,7 @@
         <v>4</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G107" s="1">
         <v>2002</v>
@@ -4551,13 +4533,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="108" customHeight="1" spans="1:11">
-      <c r="A108" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="B108" s="1" t="s">
-        <v>135</v>
-      </c>
+    <row r="108" customHeight="1" spans="3:11">
       <c r="C108" s="1">
         <v>40000153</v>
       </c>
@@ -4568,7 +4544,7 @@
         <v>4</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G108" s="1">
         <v>2003</v>
@@ -4586,13 +4562,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="109" customHeight="1" spans="1:11">
-      <c r="A109" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="B109" s="1" t="s">
-        <v>135</v>
-      </c>
+    <row r="109" customHeight="1" spans="3:11">
       <c r="C109" s="1">
         <v>40000154</v>
       </c>
@@ -4603,7 +4573,7 @@
         <v>4</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G109" s="2">
         <v>2004</v>
@@ -4623,10 +4593,10 @@
     </row>
     <row r="110" customHeight="1" spans="1:11">
       <c r="A110" s="1" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="C110" s="1">
         <v>40000155</v>
@@ -4658,10 +4628,10 @@
     </row>
     <row r="111" customHeight="1" spans="1:11">
       <c r="A111" s="1" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="C111" s="1">
         <v>40000156</v>
@@ -4693,10 +4663,10 @@
     </row>
     <row r="112" customHeight="1" spans="1:11">
       <c r="A112" s="1" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="C112" s="1">
         <v>40000157</v>
@@ -4728,10 +4698,10 @@
     </row>
     <row r="113" customHeight="1" spans="1:11">
       <c r="A113" s="1" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="C113" s="1">
         <v>40000158</v>
@@ -4763,10 +4733,10 @@
     </row>
     <row r="114" customHeight="1" spans="1:11">
       <c r="A114" s="1" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="C114" s="1">
         <v>40000159</v>
@@ -4798,10 +4768,10 @@
     </row>
     <row r="115" customHeight="1" spans="1:11">
       <c r="A115" s="1" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="C115" s="1">
         <v>40000160</v>
@@ -4833,10 +4803,10 @@
     </row>
     <row r="116" customHeight="1" spans="1:11">
       <c r="A116" s="1" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="C116" s="1">
         <v>40000161</v>
@@ -4868,10 +4838,10 @@
     </row>
     <row r="117" customHeight="1" spans="1:11">
       <c r="A117" s="1" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="C117" s="1">
         <v>40000162</v>
@@ -4903,10 +4873,10 @@
     </row>
     <row r="118" customHeight="1" spans="1:11">
       <c r="A118" s="1" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="C118" s="1">
         <v>40000163</v>
@@ -4938,10 +4908,10 @@
     </row>
     <row r="119" customHeight="1" spans="1:11">
       <c r="A119" s="1" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="C119" s="1">
         <v>40000164</v>
@@ -4968,15 +4938,15 @@
         <v>4</v>
       </c>
       <c r="K119" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="120" customHeight="1" spans="1:11">
       <c r="A120" s="1" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="C120" s="1">
         <v>40000165</v>
@@ -5008,10 +4978,10 @@
     </row>
     <row r="121" customHeight="1" spans="1:11">
       <c r="A121" s="1" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="C121" s="1">
         <v>40000166</v>
@@ -5043,10 +5013,10 @@
     </row>
     <row r="122" customHeight="1" spans="1:11">
       <c r="A122" s="1" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="C122" s="1">
         <v>40000167</v>
@@ -5078,10 +5048,10 @@
     </row>
     <row r="123" customHeight="1" spans="1:11">
       <c r="A123" s="1" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="C123" s="1">
         <v>40000168</v>
@@ -5113,10 +5083,10 @@
     </row>
     <row r="124" customHeight="1" spans="1:11">
       <c r="A124" s="1" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="C124" s="1">
         <v>40000169</v>
@@ -5148,10 +5118,10 @@
     </row>
     <row r="125" customHeight="1" spans="1:11">
       <c r="A125" s="1" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="C125" s="1">
         <v>40000170</v>
@@ -5183,10 +5153,10 @@
     </row>
     <row r="126" customHeight="1" spans="1:11">
       <c r="A126" s="1" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="C126" s="1">
         <v>40000171</v>
@@ -5218,10 +5188,10 @@
     </row>
     <row r="127" customHeight="1" spans="1:11">
       <c r="A127" s="1" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="C127" s="1">
         <v>40000172</v>
@@ -5253,10 +5223,10 @@
     </row>
     <row r="128" customHeight="1" spans="1:11">
       <c r="A128" s="1" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="C128" s="1">
         <v>40000173</v>
@@ -5288,10 +5258,10 @@
     </row>
     <row r="129" customHeight="1" spans="1:11">
       <c r="A129" s="1" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="C129" s="1">
         <v>40000174</v>

--- a/Excel/HalidomConfig.xlsx
+++ b/Excel/HalidomConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27952" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="162">
   <si>
     <t>Id</t>
   </si>
@@ -452,22 +452,22 @@
     <t>深渊蜈膏</t>
   </si>
   <si>
+    <t>深渊虫心</t>
+  </si>
+  <si>
+    <t>深渊龙皮</t>
+  </si>
+  <si>
+    <t>深渊猪皮</t>
+  </si>
+  <si>
+    <t>深渊猪心</t>
+  </si>
+  <si>
+    <t>深渊蝎皮</t>
+  </si>
+  <si>
     <t>#</t>
-  </si>
-  <si>
-    <t>深渊虫心</t>
-  </si>
-  <si>
-    <t>深渊龙皮</t>
-  </si>
-  <si>
-    <t>深渊猪皮</t>
-  </si>
-  <si>
-    <t>深渊猪心</t>
-  </si>
-  <si>
-    <t>深渊蝎皮</t>
   </si>
   <si>
     <t>深渊宝甲</t>
@@ -1481,10 +1481,10 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="5" width="9" style="1"/>
-    <col min="6" max="6" width="12.625" style="1" customWidth="1"/>
-    <col min="7" max="9" width="12.25" style="1" customWidth="1"/>
-    <col min="10" max="10" width="11.125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="26.75" style="1" customWidth="1"/>
+    <col min="6" max="6" width="12.6283185840708" style="1" customWidth="1"/>
+    <col min="7" max="9" width="12.2477876106195" style="1" customWidth="1"/>
+    <col min="10" max="10" width="11.1238938053097" style="1" customWidth="1"/>
+    <col min="11" max="11" width="26.7522123893805" style="1" customWidth="1"/>
     <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -4591,13 +4591,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="110" customHeight="1" spans="1:11">
-      <c r="A110" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="B110" s="1" t="s">
-        <v>141</v>
-      </c>
+    <row r="110" customHeight="1" spans="3:11">
       <c r="C110" s="1">
         <v>40000155</v>
       </c>
@@ -4608,7 +4602,7 @@
         <v>4</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G110" s="1">
         <v>2005</v>
@@ -4626,13 +4620,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="111" customHeight="1" spans="1:11">
-      <c r="A111" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="B111" s="1" t="s">
-        <v>141</v>
-      </c>
+    <row r="111" customHeight="1" spans="3:11">
       <c r="C111" s="1">
         <v>40000156</v>
       </c>
@@ -4643,7 +4631,7 @@
         <v>4</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G111" s="1">
         <v>2006</v>
@@ -4661,13 +4649,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="112" customHeight="1" spans="1:11">
-      <c r="A112" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="B112" s="1" t="s">
-        <v>141</v>
-      </c>
+    <row r="112" customHeight="1" spans="3:11">
       <c r="C112" s="1">
         <v>40000157</v>
       </c>
@@ -4678,7 +4660,7 @@
         <v>4</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G112" s="1">
         <v>2010</v>
@@ -4696,13 +4678,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="113" customHeight="1" spans="1:11">
-      <c r="A113" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="B113" s="1" t="s">
-        <v>141</v>
-      </c>
+    <row r="113" customHeight="1" spans="3:11">
       <c r="C113" s="1">
         <v>40000158</v>
       </c>
@@ -4713,7 +4689,7 @@
         <v>4</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G113" s="1">
         <v>2012</v>
@@ -4731,13 +4707,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="114" customHeight="1" spans="1:11">
-      <c r="A114" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="B114" s="1" t="s">
-        <v>141</v>
-      </c>
+    <row r="114" customHeight="1" spans="3:11">
       <c r="C114" s="1">
         <v>40000159</v>
       </c>
@@ -4748,7 +4718,7 @@
         <v>4</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G114" s="1">
         <v>2002</v>
@@ -4768,10 +4738,10 @@
     </row>
     <row r="115" customHeight="1" spans="1:11">
       <c r="A115" s="1" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="C115" s="1">
         <v>40000160</v>
@@ -4803,10 +4773,10 @@
     </row>
     <row r="116" customHeight="1" spans="1:11">
       <c r="A116" s="1" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="C116" s="1">
         <v>40000161</v>
@@ -4838,10 +4808,10 @@
     </row>
     <row r="117" customHeight="1" spans="1:11">
       <c r="A117" s="1" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="C117" s="1">
         <v>40000162</v>
@@ -4873,10 +4843,10 @@
     </row>
     <row r="118" customHeight="1" spans="1:11">
       <c r="A118" s="1" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="C118" s="1">
         <v>40000163</v>
@@ -4908,10 +4878,10 @@
     </row>
     <row r="119" customHeight="1" spans="1:11">
       <c r="A119" s="1" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="C119" s="1">
         <v>40000164</v>
@@ -4943,10 +4913,10 @@
     </row>
     <row r="120" customHeight="1" spans="1:11">
       <c r="A120" s="1" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="C120" s="1">
         <v>40000165</v>
@@ -4978,10 +4948,10 @@
     </row>
     <row r="121" customHeight="1" spans="1:11">
       <c r="A121" s="1" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="C121" s="1">
         <v>40000166</v>
@@ -5013,10 +4983,10 @@
     </row>
     <row r="122" customHeight="1" spans="1:11">
       <c r="A122" s="1" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="C122" s="1">
         <v>40000167</v>
@@ -5048,10 +5018,10 @@
     </row>
     <row r="123" customHeight="1" spans="1:11">
       <c r="A123" s="1" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="C123" s="1">
         <v>40000168</v>
@@ -5083,10 +5053,10 @@
     </row>
     <row r="124" customHeight="1" spans="1:11">
       <c r="A124" s="1" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="C124" s="1">
         <v>40000169</v>
@@ -5118,10 +5088,10 @@
     </row>
     <row r="125" customHeight="1" spans="1:11">
       <c r="A125" s="1" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="C125" s="1">
         <v>40000170</v>
@@ -5153,10 +5123,10 @@
     </row>
     <row r="126" customHeight="1" spans="1:11">
       <c r="A126" s="1" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="C126" s="1">
         <v>40000171</v>
@@ -5188,10 +5158,10 @@
     </row>
     <row r="127" customHeight="1" spans="1:11">
       <c r="A127" s="1" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="C127" s="1">
         <v>40000172</v>
@@ -5223,10 +5193,10 @@
     </row>
     <row r="128" customHeight="1" spans="1:11">
       <c r="A128" s="1" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="C128" s="1">
         <v>40000173</v>
@@ -5258,10 +5228,10 @@
     </row>
     <row r="129" customHeight="1" spans="1:11">
       <c r="A129" s="1" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="C129" s="1">
         <v>40000174</v>

--- a/Excel/HalidomConfig.xlsx
+++ b/Excel/HalidomConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="162">
   <si>
     <t>Id</t>
   </si>
@@ -467,22 +467,22 @@
     <t>深渊蝎皮</t>
   </si>
   <si>
+    <t>深渊宝甲</t>
+  </si>
+  <si>
+    <t>深渊号角</t>
+  </si>
+  <si>
+    <t>深渊雕像</t>
+  </si>
+  <si>
+    <t>深渊神像</t>
+  </si>
+  <si>
+    <t>深渊獠牙</t>
+  </si>
+  <si>
     <t>#</t>
-  </si>
-  <si>
-    <t>深渊宝甲</t>
-  </si>
-  <si>
-    <t>深渊号角</t>
-  </si>
-  <si>
-    <t>深渊雕像</t>
-  </si>
-  <si>
-    <t>深渊神像</t>
-  </si>
-  <si>
-    <t>深渊獠牙</t>
   </si>
   <si>
     <t>深渊树心</t>
@@ -4736,13 +4736,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="115" customHeight="1" spans="1:11">
-      <c r="A115" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="B115" s="1" t="s">
-        <v>146</v>
-      </c>
+    <row r="115" customHeight="1" spans="3:11">
       <c r="C115" s="1">
         <v>40000160</v>
       </c>
@@ -4753,7 +4747,7 @@
         <v>4</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G115" s="1">
         <v>2003</v>
@@ -4771,13 +4765,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="116" customHeight="1" spans="1:11">
-      <c r="A116" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="B116" s="1" t="s">
-        <v>146</v>
-      </c>
+    <row r="116" customHeight="1" spans="3:11">
       <c r="C116" s="1">
         <v>40000161</v>
       </c>
@@ -4788,7 +4776,7 @@
         <v>4</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G116" s="1">
         <v>2001</v>
@@ -4806,13 +4794,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="117" customHeight="1" spans="1:11">
-      <c r="A117" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="B117" s="1" t="s">
-        <v>146</v>
-      </c>
+    <row r="117" customHeight="1" spans="3:11">
       <c r="C117" s="1">
         <v>40000162</v>
       </c>
@@ -4823,7 +4805,7 @@
         <v>4</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G117" s="1">
         <v>2007</v>
@@ -4841,13 +4823,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="118" customHeight="1" spans="1:11">
-      <c r="A118" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="B118" s="1" t="s">
-        <v>146</v>
-      </c>
+    <row r="118" customHeight="1" spans="3:11">
       <c r="C118" s="1">
         <v>40000163</v>
       </c>
@@ -4858,7 +4834,7 @@
         <v>4</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G118" s="1">
         <v>2008</v>
@@ -4876,13 +4852,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="119" customHeight="1" spans="1:11">
-      <c r="A119" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="B119" s="1" t="s">
-        <v>146</v>
-      </c>
+    <row r="119" customHeight="1" spans="3:11">
       <c r="C119" s="1">
         <v>40000164</v>
       </c>
@@ -4893,7 +4863,7 @@
         <v>4</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G119" s="1">
         <v>2009</v>
@@ -4913,10 +4883,10 @@
     </row>
     <row r="120" customHeight="1" spans="1:11">
       <c r="A120" s="1" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="C120" s="1">
         <v>40000165</v>
@@ -4948,10 +4918,10 @@
     </row>
     <row r="121" customHeight="1" spans="1:11">
       <c r="A121" s="1" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="C121" s="1">
         <v>40000166</v>
@@ -4983,10 +4953,10 @@
     </row>
     <row r="122" customHeight="1" spans="1:11">
       <c r="A122" s="1" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="C122" s="1">
         <v>40000167</v>
@@ -5018,10 +4988,10 @@
     </row>
     <row r="123" customHeight="1" spans="1:11">
       <c r="A123" s="1" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="C123" s="1">
         <v>40000168</v>
@@ -5053,10 +5023,10 @@
     </row>
     <row r="124" customHeight="1" spans="1:11">
       <c r="A124" s="1" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="C124" s="1">
         <v>40000169</v>
@@ -5088,10 +5058,10 @@
     </row>
     <row r="125" customHeight="1" spans="1:11">
       <c r="A125" s="1" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="C125" s="1">
         <v>40000170</v>
@@ -5123,10 +5093,10 @@
     </row>
     <row r="126" customHeight="1" spans="1:11">
       <c r="A126" s="1" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="C126" s="1">
         <v>40000171</v>
@@ -5158,10 +5128,10 @@
     </row>
     <row r="127" customHeight="1" spans="1:11">
       <c r="A127" s="1" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="C127" s="1">
         <v>40000172</v>
@@ -5193,10 +5163,10 @@
     </row>
     <row r="128" customHeight="1" spans="1:11">
       <c r="A128" s="1" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="C128" s="1">
         <v>40000173</v>
@@ -5228,10 +5198,10 @@
     </row>
     <row r="129" customHeight="1" spans="1:11">
       <c r="A129" s="1" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="C129" s="1">
         <v>40000174</v>

--- a/Excel/HalidomConfig.xlsx
+++ b/Excel/HalidomConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="162">
   <si>
     <t>Id</t>
   </si>
@@ -482,22 +482,22 @@
     <t>深渊獠牙</t>
   </si>
   <si>
+    <t>深渊树心</t>
+  </si>
+  <si>
+    <t>深渊魔心</t>
+  </si>
+  <si>
+    <t>深渊尸心</t>
+  </si>
+  <si>
+    <t>深渊法杖</t>
+  </si>
+  <si>
+    <t>深渊权杖</t>
+  </si>
+  <si>
     <t>#</t>
-  </si>
-  <si>
-    <t>深渊树心</t>
-  </si>
-  <si>
-    <t>深渊魔心</t>
-  </si>
-  <si>
-    <t>深渊尸心</t>
-  </si>
-  <si>
-    <t>深渊法杖</t>
-  </si>
-  <si>
-    <t>深渊权杖</t>
   </si>
   <si>
     <t>深渊战锤</t>
@@ -4881,13 +4881,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="120" customHeight="1" spans="1:11">
-      <c r="A120" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="B120" s="1" t="s">
-        <v>151</v>
-      </c>
+    <row r="120" customHeight="1" spans="3:11">
       <c r="C120" s="1">
         <v>40000165</v>
       </c>
@@ -4898,7 +4892,7 @@
         <v>4</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G120" s="1">
         <v>2012</v>
@@ -4916,13 +4910,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="121" customHeight="1" spans="1:11">
-      <c r="A121" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="B121" s="1" t="s">
-        <v>151</v>
-      </c>
+    <row r="121" customHeight="1" spans="3:11">
       <c r="C121" s="1">
         <v>40000166</v>
       </c>
@@ -4933,7 +4921,7 @@
         <v>4</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G121" s="1">
         <v>2002</v>
@@ -4951,13 +4939,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="122" customHeight="1" spans="1:11">
-      <c r="A122" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="B122" s="1" t="s">
-        <v>151</v>
-      </c>
+    <row r="122" customHeight="1" spans="3:11">
       <c r="C122" s="1">
         <v>40000167</v>
       </c>
@@ -4968,7 +4950,7 @@
         <v>4</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G122" s="1">
         <v>2003</v>
@@ -4986,13 +4968,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="123" customHeight="1" spans="1:11">
-      <c r="A123" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="B123" s="1" t="s">
-        <v>151</v>
-      </c>
+    <row r="123" customHeight="1" spans="3:11">
       <c r="C123" s="1">
         <v>40000168</v>
       </c>
@@ -5003,7 +4979,7 @@
         <v>4</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G123" s="2">
         <v>2004</v>
@@ -5021,13 +4997,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="124" customHeight="1" spans="1:11">
-      <c r="A124" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="B124" s="1" t="s">
-        <v>151</v>
-      </c>
+    <row r="124" customHeight="1" spans="3:11">
       <c r="C124" s="1">
         <v>40000169</v>
       </c>
@@ -5038,7 +5008,7 @@
         <v>4</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G124" s="1">
         <v>2005</v>
@@ -5058,10 +5028,10 @@
     </row>
     <row r="125" customHeight="1" spans="1:11">
       <c r="A125" s="1" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="C125" s="1">
         <v>40000170</v>
@@ -5093,10 +5063,10 @@
     </row>
     <row r="126" customHeight="1" spans="1:11">
       <c r="A126" s="1" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="C126" s="1">
         <v>40000171</v>
@@ -5128,10 +5098,10 @@
     </row>
     <row r="127" customHeight="1" spans="1:11">
       <c r="A127" s="1" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="C127" s="1">
         <v>40000172</v>
@@ -5163,10 +5133,10 @@
     </row>
     <row r="128" customHeight="1" spans="1:11">
       <c r="A128" s="1" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="C128" s="1">
         <v>40000173</v>
@@ -5198,10 +5168,10 @@
     </row>
     <row r="129" customHeight="1" spans="1:11">
       <c r="A129" s="1" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="C129" s="1">
         <v>40000174</v>

--- a/Excel/HalidomConfig.xlsx
+++ b/Excel/HalidomConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27952" windowHeight="12255"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="161">
   <si>
     <t>Id</t>
   </si>
@@ -495,9 +495,6 @@
   </si>
   <si>
     <t>深渊权杖</t>
-  </si>
-  <si>
-    <t>#</t>
   </si>
   <si>
     <t>深渊战锤</t>
@@ -1477,14 +1474,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:K129"/>
+  <dimension ref="C3:K129"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="5" width="9" style="1"/>
-    <col min="6" max="6" width="12.6283185840708" style="1" customWidth="1"/>
-    <col min="7" max="9" width="12.2477876106195" style="1" customWidth="1"/>
-    <col min="10" max="10" width="11.1238938053097" style="1" customWidth="1"/>
-    <col min="11" max="11" width="26.7522123893805" style="1" customWidth="1"/>
+    <col min="6" max="6" width="12.625" style="1" customWidth="1"/>
+    <col min="7" max="9" width="12.25" style="1" customWidth="1"/>
+    <col min="10" max="10" width="11.125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="26.75" style="1" customWidth="1"/>
     <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -5026,13 +5023,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="125" customHeight="1" spans="1:11">
-      <c r="A125" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="B125" s="1" t="s">
-        <v>156</v>
-      </c>
+    <row r="125" customHeight="1" spans="3:11">
       <c r="C125" s="1">
         <v>40000170</v>
       </c>
@@ -5043,7 +5034,7 @@
         <v>4</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G125" s="1">
         <v>2006</v>
@@ -5061,13 +5052,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="126" customHeight="1" spans="1:11">
-      <c r="A126" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="B126" s="1" t="s">
-        <v>156</v>
-      </c>
+    <row r="126" customHeight="1" spans="3:11">
       <c r="C126" s="1">
         <v>40000171</v>
       </c>
@@ -5078,7 +5063,7 @@
         <v>4</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G126" s="1">
         <v>2010</v>
@@ -5096,13 +5081,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="127" customHeight="1" spans="1:11">
-      <c r="A127" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="B127" s="1" t="s">
-        <v>156</v>
-      </c>
+    <row r="127" customHeight="1" spans="3:11">
       <c r="C127" s="1">
         <v>40000172</v>
       </c>
@@ -5113,7 +5092,7 @@
         <v>4</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G127" s="1">
         <v>2012</v>
@@ -5131,13 +5110,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="128" customHeight="1" spans="1:11">
-      <c r="A128" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="B128" s="1" t="s">
-        <v>156</v>
-      </c>
+    <row r="128" customHeight="1" spans="3:11">
       <c r="C128" s="1">
         <v>40000173</v>
       </c>
@@ -5148,7 +5121,7 @@
         <v>4</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G128" s="1">
         <v>2002</v>
@@ -5166,13 +5139,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="129" customHeight="1" spans="1:11">
-      <c r="A129" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="B129" s="1" t="s">
-        <v>156</v>
-      </c>
+    <row r="129" customHeight="1" spans="3:11">
       <c r="C129" s="1">
         <v>40000174</v>
       </c>
@@ -5183,7 +5150,7 @@
         <v>4</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G129" s="1">
         <v>2003</v>

--- a/Excel/HalidomConfig.xlsx
+++ b/Excel/HalidomConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="197">
   <si>
     <t>Id</t>
   </si>
@@ -510,6 +510,114 @@
   </si>
   <si>
     <t>深渊龙爪</t>
+  </si>
+  <si>
+    <t>混沌鸡爪</t>
+  </si>
+  <si>
+    <t>混沌鹿茸</t>
+  </si>
+  <si>
+    <t>混沌草帽</t>
+  </si>
+  <si>
+    <t>混沌猫爪</t>
+  </si>
+  <si>
+    <t>混沌花朵</t>
+  </si>
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>混沌冰晶</t>
+  </si>
+  <si>
+    <t>混沌蝠翼</t>
+  </si>
+  <si>
+    <t>混沌魂火</t>
+  </si>
+  <si>
+    <t>混沌腐肉</t>
+  </si>
+  <si>
+    <t>混沌蛇胆</t>
+  </si>
+  <si>
+    <t>混沌狼爪</t>
+  </si>
+  <si>
+    <t>混沌虫皮</t>
+  </si>
+  <si>
+    <t>混沌鹰羽</t>
+  </si>
+  <si>
+    <t>混沌虫角</t>
+  </si>
+  <si>
+    <t>混沌蜈膏</t>
+  </si>
+  <si>
+    <t>混沌虫心</t>
+  </si>
+  <si>
+    <t>混沌龙皮</t>
+  </si>
+  <si>
+    <t>混沌猪皮</t>
+  </si>
+  <si>
+    <t>混沌猪心</t>
+  </si>
+  <si>
+    <t>混沌蝎皮</t>
+  </si>
+  <si>
+    <t>混沌宝甲</t>
+  </si>
+  <si>
+    <t>混沌号角</t>
+  </si>
+  <si>
+    <t>混沌雕像</t>
+  </si>
+  <si>
+    <t>混沌神像</t>
+  </si>
+  <si>
+    <t>混沌獠牙</t>
+  </si>
+  <si>
+    <t>混沌树心</t>
+  </si>
+  <si>
+    <t>混沌魔心</t>
+  </si>
+  <si>
+    <t>混沌尸心</t>
+  </si>
+  <si>
+    <t>混沌法杖</t>
+  </si>
+  <si>
+    <t>混沌权杖</t>
+  </si>
+  <si>
+    <t>混沌战锤</t>
+  </si>
+  <si>
+    <t>混沌血核</t>
+  </si>
+  <si>
+    <t>混沌魔核</t>
+  </si>
+  <si>
+    <t>混沌龙甲</t>
+  </si>
+  <si>
+    <t>混沌龙爪</t>
   </si>
 </sst>
 </file>
@@ -1474,7 +1582,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:K129"/>
+  <dimension ref="A3:K164"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="5" width="9" style="1"/>
@@ -5168,6 +5276,1201 @@
         <v>17</v>
       </c>
     </row>
+    <row r="130" s="2" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C130" s="2">
+        <v>40000175</v>
+      </c>
+      <c r="D130" s="2">
+        <v>40000175</v>
+      </c>
+      <c r="E130" s="2">
+        <v>5</v>
+      </c>
+      <c r="F130" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="G130" s="2">
+        <v>2004</v>
+      </c>
+      <c r="H130" s="2">
+        <v>7</v>
+      </c>
+      <c r="I130" s="2">
+        <v>7</v>
+      </c>
+      <c r="J130" s="2">
+        <v>4</v>
+      </c>
+      <c r="K130" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="131" customHeight="1" spans="3:11">
+      <c r="C131" s="1">
+        <v>40000176</v>
+      </c>
+      <c r="D131" s="1">
+        <v>40000176</v>
+      </c>
+      <c r="E131" s="1">
+        <v>5</v>
+      </c>
+      <c r="F131" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="G131" s="1">
+        <v>2005</v>
+      </c>
+      <c r="H131" s="1">
+        <v>7</v>
+      </c>
+      <c r="I131" s="1">
+        <v>7</v>
+      </c>
+      <c r="J131" s="1">
+        <v>4</v>
+      </c>
+      <c r="K131" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="132" customHeight="1" spans="3:11">
+      <c r="C132" s="1">
+        <v>40000177</v>
+      </c>
+      <c r="D132" s="1">
+        <v>40000177</v>
+      </c>
+      <c r="E132" s="1">
+        <v>5</v>
+      </c>
+      <c r="F132" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="G132" s="1">
+        <v>2006</v>
+      </c>
+      <c r="H132" s="1">
+        <v>7</v>
+      </c>
+      <c r="I132" s="1">
+        <v>7</v>
+      </c>
+      <c r="J132" s="1">
+        <v>4</v>
+      </c>
+      <c r="K132" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="133" customHeight="1" spans="3:11">
+      <c r="C133" s="1">
+        <v>40000178</v>
+      </c>
+      <c r="D133" s="1">
+        <v>40000178</v>
+      </c>
+      <c r="E133" s="1">
+        <v>5</v>
+      </c>
+      <c r="F133" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="G133" s="1">
+        <v>2010</v>
+      </c>
+      <c r="H133" s="1">
+        <v>7</v>
+      </c>
+      <c r="I133" s="1">
+        <v>7</v>
+      </c>
+      <c r="J133" s="1">
+        <v>4</v>
+      </c>
+      <c r="K133" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="134" customHeight="1" spans="3:11">
+      <c r="C134" s="1">
+        <v>40000179</v>
+      </c>
+      <c r="D134" s="1">
+        <v>40000179</v>
+      </c>
+      <c r="E134" s="1">
+        <v>5</v>
+      </c>
+      <c r="F134" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="G134" s="1">
+        <v>2012</v>
+      </c>
+      <c r="H134" s="1">
+        <v>25</v>
+      </c>
+      <c r="I134" s="1">
+        <v>25</v>
+      </c>
+      <c r="J134" s="1">
+        <v>4</v>
+      </c>
+      <c r="K134" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="135" customHeight="1" spans="1:11">
+      <c r="A135" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B135" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C135" s="1">
+        <v>40000180</v>
+      </c>
+      <c r="D135" s="1">
+        <v>40000180</v>
+      </c>
+      <c r="E135" s="1">
+        <v>5</v>
+      </c>
+      <c r="F135" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="G135" s="1">
+        <v>2002</v>
+      </c>
+      <c r="H135" s="1">
+        <v>50</v>
+      </c>
+      <c r="I135" s="1">
+        <v>50</v>
+      </c>
+      <c r="J135" s="1">
+        <v>4</v>
+      </c>
+      <c r="K135" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="136" customHeight="1" spans="1:11">
+      <c r="A136" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C136" s="1">
+        <v>40000181</v>
+      </c>
+      <c r="D136" s="1">
+        <v>40000181</v>
+      </c>
+      <c r="E136" s="1">
+        <v>5</v>
+      </c>
+      <c r="F136" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="G136" s="1">
+        <v>2003</v>
+      </c>
+      <c r="H136" s="1">
+        <v>40</v>
+      </c>
+      <c r="I136" s="1">
+        <v>40</v>
+      </c>
+      <c r="J136" s="1">
+        <v>4</v>
+      </c>
+      <c r="K136" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="137" customHeight="1" spans="1:11">
+      <c r="A137" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C137" s="1">
+        <v>40000182</v>
+      </c>
+      <c r="D137" s="1">
+        <v>40000182</v>
+      </c>
+      <c r="E137" s="1">
+        <v>5</v>
+      </c>
+      <c r="F137" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="G137" s="1">
+        <v>2001</v>
+      </c>
+      <c r="H137" s="1">
+        <v>7</v>
+      </c>
+      <c r="I137" s="1">
+        <v>7</v>
+      </c>
+      <c r="J137" s="1">
+        <v>4</v>
+      </c>
+      <c r="K137" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="138" customHeight="1" spans="1:11">
+      <c r="A138" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C138" s="1">
+        <v>40000183</v>
+      </c>
+      <c r="D138" s="1">
+        <v>40000183</v>
+      </c>
+      <c r="E138" s="1">
+        <v>5</v>
+      </c>
+      <c r="F138" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="G138" s="1">
+        <v>2007</v>
+      </c>
+      <c r="H138" s="1">
+        <v>7</v>
+      </c>
+      <c r="I138" s="1">
+        <v>7</v>
+      </c>
+      <c r="J138" s="1">
+        <v>4</v>
+      </c>
+      <c r="K138" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="139" customHeight="1" spans="1:11">
+      <c r="A139" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C139" s="1">
+        <v>40000184</v>
+      </c>
+      <c r="D139" s="1">
+        <v>40000184</v>
+      </c>
+      <c r="E139" s="1">
+        <v>5</v>
+      </c>
+      <c r="F139" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="G139" s="1">
+        <v>2008</v>
+      </c>
+      <c r="H139" s="1">
+        <v>7</v>
+      </c>
+      <c r="I139" s="1">
+        <v>7</v>
+      </c>
+      <c r="J139" s="1">
+        <v>4</v>
+      </c>
+      <c r="K139" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="140" customHeight="1" spans="1:11">
+      <c r="A140" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C140" s="1">
+        <v>40000185</v>
+      </c>
+      <c r="D140" s="1">
+        <v>40000185</v>
+      </c>
+      <c r="E140" s="1">
+        <v>5</v>
+      </c>
+      <c r="F140" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="G140" s="1">
+        <v>2009</v>
+      </c>
+      <c r="H140" s="1">
+        <v>7</v>
+      </c>
+      <c r="I140" s="1">
+        <v>7</v>
+      </c>
+      <c r="J140" s="1">
+        <v>4</v>
+      </c>
+      <c r="K140" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="141" customHeight="1" spans="1:11">
+      <c r="A141" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C141" s="1">
+        <v>40000186</v>
+      </c>
+      <c r="D141" s="1">
+        <v>40000186</v>
+      </c>
+      <c r="E141" s="1">
+        <v>5</v>
+      </c>
+      <c r="F141" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="G141" s="1">
+        <v>2012</v>
+      </c>
+      <c r="H141" s="1">
+        <v>25</v>
+      </c>
+      <c r="I141" s="1">
+        <v>25</v>
+      </c>
+      <c r="J141" s="1">
+        <v>4</v>
+      </c>
+      <c r="K141" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="142" customHeight="1" spans="1:11">
+      <c r="A142" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B142" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C142" s="1">
+        <v>40000187</v>
+      </c>
+      <c r="D142" s="1">
+        <v>40000187</v>
+      </c>
+      <c r="E142" s="1">
+        <v>5</v>
+      </c>
+      <c r="F142" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="G142" s="1">
+        <v>2002</v>
+      </c>
+      <c r="H142" s="1">
+        <v>50</v>
+      </c>
+      <c r="I142" s="1">
+        <v>50</v>
+      </c>
+      <c r="J142" s="1">
+        <v>4</v>
+      </c>
+      <c r="K142" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="143" customHeight="1" spans="1:11">
+      <c r="A143" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C143" s="1">
+        <v>40000188</v>
+      </c>
+      <c r="D143" s="1">
+        <v>40000188</v>
+      </c>
+      <c r="E143" s="1">
+        <v>5</v>
+      </c>
+      <c r="F143" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="G143" s="1">
+        <v>2003</v>
+      </c>
+      <c r="H143" s="1">
+        <v>40</v>
+      </c>
+      <c r="I143" s="1">
+        <v>40</v>
+      </c>
+      <c r="J143" s="1">
+        <v>4</v>
+      </c>
+      <c r="K143" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="144" customHeight="1" spans="1:11">
+      <c r="A144" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C144" s="1">
+        <v>40000189</v>
+      </c>
+      <c r="D144" s="1">
+        <v>40000189</v>
+      </c>
+      <c r="E144" s="1">
+        <v>5</v>
+      </c>
+      <c r="F144" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="G144" s="2">
+        <v>2004</v>
+      </c>
+      <c r="H144" s="2">
+        <v>7</v>
+      </c>
+      <c r="I144" s="2">
+        <v>7</v>
+      </c>
+      <c r="J144" s="2">
+        <v>4</v>
+      </c>
+      <c r="K144" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="145" customHeight="1" spans="1:11">
+      <c r="A145" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C145" s="1">
+        <v>40000190</v>
+      </c>
+      <c r="D145" s="1">
+        <v>40000190</v>
+      </c>
+      <c r="E145" s="1">
+        <v>5</v>
+      </c>
+      <c r="F145" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="G145" s="1">
+        <v>2005</v>
+      </c>
+      <c r="H145" s="1">
+        <v>7</v>
+      </c>
+      <c r="I145" s="1">
+        <v>7</v>
+      </c>
+      <c r="J145" s="1">
+        <v>4</v>
+      </c>
+      <c r="K145" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="146" customHeight="1" spans="1:11">
+      <c r="A146" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B146" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C146" s="1">
+        <v>40000191</v>
+      </c>
+      <c r="D146" s="1">
+        <v>40000191</v>
+      </c>
+      <c r="E146" s="1">
+        <v>5</v>
+      </c>
+      <c r="F146" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="G146" s="1">
+        <v>2006</v>
+      </c>
+      <c r="H146" s="1">
+        <v>7</v>
+      </c>
+      <c r="I146" s="1">
+        <v>7</v>
+      </c>
+      <c r="J146" s="1">
+        <v>4</v>
+      </c>
+      <c r="K146" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="147" customHeight="1" spans="1:11">
+      <c r="A147" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C147" s="1">
+        <v>40000192</v>
+      </c>
+      <c r="D147" s="1">
+        <v>40000192</v>
+      </c>
+      <c r="E147" s="1">
+        <v>5</v>
+      </c>
+      <c r="F147" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="G147" s="1">
+        <v>2010</v>
+      </c>
+      <c r="H147" s="1">
+        <v>7</v>
+      </c>
+      <c r="I147" s="1">
+        <v>7</v>
+      </c>
+      <c r="J147" s="1">
+        <v>4</v>
+      </c>
+      <c r="K147" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="148" customHeight="1" spans="1:11">
+      <c r="A148" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C148" s="1">
+        <v>40000193</v>
+      </c>
+      <c r="D148" s="1">
+        <v>40000193</v>
+      </c>
+      <c r="E148" s="1">
+        <v>5</v>
+      </c>
+      <c r="F148" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="G148" s="1">
+        <v>2012</v>
+      </c>
+      <c r="H148" s="1">
+        <v>25</v>
+      </c>
+      <c r="I148" s="1">
+        <v>25</v>
+      </c>
+      <c r="J148" s="1">
+        <v>4</v>
+      </c>
+      <c r="K148" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="149" customHeight="1" spans="1:11">
+      <c r="A149" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B149" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C149" s="1">
+        <v>40000194</v>
+      </c>
+      <c r="D149" s="1">
+        <v>40000194</v>
+      </c>
+      <c r="E149" s="1">
+        <v>5</v>
+      </c>
+      <c r="F149" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="G149" s="1">
+        <v>2002</v>
+      </c>
+      <c r="H149" s="1">
+        <v>50</v>
+      </c>
+      <c r="I149" s="1">
+        <v>50</v>
+      </c>
+      <c r="J149" s="1">
+        <v>4</v>
+      </c>
+      <c r="K149" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="150" customHeight="1" spans="1:11">
+      <c r="A150" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B150" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C150" s="1">
+        <v>40000195</v>
+      </c>
+      <c r="D150" s="1">
+        <v>40000195</v>
+      </c>
+      <c r="E150" s="1">
+        <v>5</v>
+      </c>
+      <c r="F150" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="G150" s="1">
+        <v>2003</v>
+      </c>
+      <c r="H150" s="1">
+        <v>40</v>
+      </c>
+      <c r="I150" s="1">
+        <v>40</v>
+      </c>
+      <c r="J150" s="1">
+        <v>4</v>
+      </c>
+      <c r="K150" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="151" customHeight="1" spans="1:11">
+      <c r="A151" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C151" s="1">
+        <v>40000196</v>
+      </c>
+      <c r="D151" s="1">
+        <v>40000196</v>
+      </c>
+      <c r="E151" s="1">
+        <v>5</v>
+      </c>
+      <c r="F151" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="G151" s="1">
+        <v>2001</v>
+      </c>
+      <c r="H151" s="1">
+        <v>7</v>
+      </c>
+      <c r="I151" s="1">
+        <v>7</v>
+      </c>
+      <c r="J151" s="1">
+        <v>4</v>
+      </c>
+      <c r="K151" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="152" customHeight="1" spans="1:11">
+      <c r="A152" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B152" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C152" s="1">
+        <v>40000197</v>
+      </c>
+      <c r="D152" s="1">
+        <v>40000197</v>
+      </c>
+      <c r="E152" s="1">
+        <v>5</v>
+      </c>
+      <c r="F152" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="G152" s="1">
+        <v>2007</v>
+      </c>
+      <c r="H152" s="1">
+        <v>7</v>
+      </c>
+      <c r="I152" s="1">
+        <v>7</v>
+      </c>
+      <c r="J152" s="1">
+        <v>4</v>
+      </c>
+      <c r="K152" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="153" customHeight="1" spans="1:11">
+      <c r="A153" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B153" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C153" s="1">
+        <v>40000198</v>
+      </c>
+      <c r="D153" s="1">
+        <v>40000198</v>
+      </c>
+      <c r="E153" s="1">
+        <v>5</v>
+      </c>
+      <c r="F153" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="G153" s="1">
+        <v>2008</v>
+      </c>
+      <c r="H153" s="1">
+        <v>7</v>
+      </c>
+      <c r="I153" s="1">
+        <v>7</v>
+      </c>
+      <c r="J153" s="1">
+        <v>4</v>
+      </c>
+      <c r="K153" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="154" customHeight="1" spans="1:11">
+      <c r="A154" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C154" s="1">
+        <v>40000199</v>
+      </c>
+      <c r="D154" s="1">
+        <v>40000199</v>
+      </c>
+      <c r="E154" s="1">
+        <v>5</v>
+      </c>
+      <c r="F154" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="G154" s="1">
+        <v>2009</v>
+      </c>
+      <c r="H154" s="1">
+        <v>7</v>
+      </c>
+      <c r="I154" s="1">
+        <v>7</v>
+      </c>
+      <c r="J154" s="1">
+        <v>4</v>
+      </c>
+      <c r="K154" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="155" customHeight="1" spans="1:11">
+      <c r="A155" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B155" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C155" s="1">
+        <v>40000200</v>
+      </c>
+      <c r="D155" s="1">
+        <v>40000200</v>
+      </c>
+      <c r="E155" s="1">
+        <v>5</v>
+      </c>
+      <c r="F155" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G155" s="1">
+        <v>2012</v>
+      </c>
+      <c r="H155" s="1">
+        <v>25</v>
+      </c>
+      <c r="I155" s="1">
+        <v>25</v>
+      </c>
+      <c r="J155" s="1">
+        <v>4</v>
+      </c>
+      <c r="K155" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="156" customHeight="1" spans="1:11">
+      <c r="A156" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B156" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C156" s="1">
+        <v>40000201</v>
+      </c>
+      <c r="D156" s="1">
+        <v>40000201</v>
+      </c>
+      <c r="E156" s="1">
+        <v>5</v>
+      </c>
+      <c r="F156" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="G156" s="1">
+        <v>2002</v>
+      </c>
+      <c r="H156" s="1">
+        <v>50</v>
+      </c>
+      <c r="I156" s="1">
+        <v>50</v>
+      </c>
+      <c r="J156" s="1">
+        <v>4</v>
+      </c>
+      <c r="K156" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="157" customHeight="1" spans="1:11">
+      <c r="A157" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B157" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C157" s="1">
+        <v>40000202</v>
+      </c>
+      <c r="D157" s="1">
+        <v>40000202</v>
+      </c>
+      <c r="E157" s="1">
+        <v>5</v>
+      </c>
+      <c r="F157" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="G157" s="1">
+        <v>2003</v>
+      </c>
+      <c r="H157" s="1">
+        <v>40</v>
+      </c>
+      <c r="I157" s="1">
+        <v>40</v>
+      </c>
+      <c r="J157" s="1">
+        <v>4</v>
+      </c>
+      <c r="K157" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="158" customHeight="1" spans="1:11">
+      <c r="A158" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B158" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C158" s="1">
+        <v>40000203</v>
+      </c>
+      <c r="D158" s="1">
+        <v>40000203</v>
+      </c>
+      <c r="E158" s="1">
+        <v>5</v>
+      </c>
+      <c r="F158" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="G158" s="2">
+        <v>2004</v>
+      </c>
+      <c r="H158" s="2">
+        <v>7</v>
+      </c>
+      <c r="I158" s="2">
+        <v>7</v>
+      </c>
+      <c r="J158" s="2">
+        <v>4</v>
+      </c>
+      <c r="K158" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="159" customHeight="1" spans="1:11">
+      <c r="A159" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B159" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C159" s="1">
+        <v>40000204</v>
+      </c>
+      <c r="D159" s="1">
+        <v>40000204</v>
+      </c>
+      <c r="E159" s="1">
+        <v>5</v>
+      </c>
+      <c r="F159" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="G159" s="1">
+        <v>2005</v>
+      </c>
+      <c r="H159" s="1">
+        <v>7</v>
+      </c>
+      <c r="I159" s="1">
+        <v>7</v>
+      </c>
+      <c r="J159" s="1">
+        <v>4</v>
+      </c>
+      <c r="K159" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="160" customHeight="1" spans="1:11">
+      <c r="A160" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B160" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C160" s="1">
+        <v>40000205</v>
+      </c>
+      <c r="D160" s="1">
+        <v>40000205</v>
+      </c>
+      <c r="E160" s="1">
+        <v>5</v>
+      </c>
+      <c r="F160" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="G160" s="1">
+        <v>2006</v>
+      </c>
+      <c r="H160" s="1">
+        <v>7</v>
+      </c>
+      <c r="I160" s="1">
+        <v>7</v>
+      </c>
+      <c r="J160" s="1">
+        <v>4</v>
+      </c>
+      <c r="K160" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="161" customHeight="1" spans="1:11">
+      <c r="A161" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B161" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C161" s="1">
+        <v>40000206</v>
+      </c>
+      <c r="D161" s="1">
+        <v>40000206</v>
+      </c>
+      <c r="E161" s="1">
+        <v>5</v>
+      </c>
+      <c r="F161" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="G161" s="1">
+        <v>2010</v>
+      </c>
+      <c r="H161" s="1">
+        <v>7</v>
+      </c>
+      <c r="I161" s="1">
+        <v>7</v>
+      </c>
+      <c r="J161" s="1">
+        <v>4</v>
+      </c>
+      <c r="K161" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="162" customHeight="1" spans="1:11">
+      <c r="A162" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B162" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C162" s="1">
+        <v>40000207</v>
+      </c>
+      <c r="D162" s="1">
+        <v>40000207</v>
+      </c>
+      <c r="E162" s="1">
+        <v>5</v>
+      </c>
+      <c r="F162" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="G162" s="1">
+        <v>2012</v>
+      </c>
+      <c r="H162" s="1">
+        <v>25</v>
+      </c>
+      <c r="I162" s="1">
+        <v>25</v>
+      </c>
+      <c r="J162" s="1">
+        <v>4</v>
+      </c>
+      <c r="K162" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="163" customHeight="1" spans="1:11">
+      <c r="A163" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B163" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C163" s="1">
+        <v>40000208</v>
+      </c>
+      <c r="D163" s="1">
+        <v>40000208</v>
+      </c>
+      <c r="E163" s="1">
+        <v>5</v>
+      </c>
+      <c r="F163" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="G163" s="1">
+        <v>2002</v>
+      </c>
+      <c r="H163" s="1">
+        <v>50</v>
+      </c>
+      <c r="I163" s="1">
+        <v>50</v>
+      </c>
+      <c r="J163" s="1">
+        <v>4</v>
+      </c>
+      <c r="K163" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="164" customHeight="1" spans="1:11">
+      <c r="A164" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B164" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C164" s="1">
+        <v>40000209</v>
+      </c>
+      <c r="D164" s="1">
+        <v>40000209</v>
+      </c>
+      <c r="E164" s="1">
+        <v>5</v>
+      </c>
+      <c r="F164" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="G164" s="1">
+        <v>2003</v>
+      </c>
+      <c r="H164" s="1">
+        <v>40</v>
+      </c>
+      <c r="I164" s="1">
+        <v>40</v>
+      </c>
+      <c r="J164" s="1">
+        <v>4</v>
+      </c>
+      <c r="K164" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:F5" errorStyle="warning">

--- a/Excel/HalidomConfig.xlsx
+++ b/Excel/HalidomConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="197">
   <si>
     <t>Id</t>
   </si>
@@ -527,22 +527,22 @@
     <t>混沌花朵</t>
   </si>
   <si>
+    <t>混沌冰晶</t>
+  </si>
+  <si>
+    <t>混沌蝠翼</t>
+  </si>
+  <si>
+    <t>混沌魂火</t>
+  </si>
+  <si>
+    <t>混沌腐肉</t>
+  </si>
+  <si>
+    <t>混沌蛇胆</t>
+  </si>
+  <si>
     <t>#</t>
-  </si>
-  <si>
-    <t>混沌冰晶</t>
-  </si>
-  <si>
-    <t>混沌蝠翼</t>
-  </si>
-  <si>
-    <t>混沌魂火</t>
-  </si>
-  <si>
-    <t>混沌腐肉</t>
-  </si>
-  <si>
-    <t>混沌蛇胆</t>
   </si>
   <si>
     <t>混沌狼爪</t>
@@ -5421,13 +5421,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="135" customHeight="1" spans="1:11">
-      <c r="A135" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="B135" s="1" t="s">
-        <v>166</v>
-      </c>
+    <row r="135" customHeight="1" spans="3:11">
       <c r="C135" s="1">
         <v>40000180</v>
       </c>
@@ -5438,7 +5432,7 @@
         <v>5</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G135" s="1">
         <v>2002</v>
@@ -5456,13 +5450,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="136" customHeight="1" spans="1:11">
-      <c r="A136" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="B136" s="1" t="s">
-        <v>166</v>
-      </c>
+    <row r="136" customHeight="1" spans="3:11">
       <c r="C136" s="1">
         <v>40000181</v>
       </c>
@@ -5473,7 +5461,7 @@
         <v>5</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G136" s="1">
         <v>2003</v>
@@ -5491,13 +5479,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="137" customHeight="1" spans="1:11">
-      <c r="A137" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="B137" s="1" t="s">
-        <v>166</v>
-      </c>
+    <row r="137" customHeight="1" spans="3:11">
       <c r="C137" s="1">
         <v>40000182</v>
       </c>
@@ -5508,7 +5490,7 @@
         <v>5</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G137" s="1">
         <v>2001</v>
@@ -5526,13 +5508,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="138" customHeight="1" spans="1:11">
-      <c r="A138" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="B138" s="1" t="s">
-        <v>166</v>
-      </c>
+    <row r="138" customHeight="1" spans="3:11">
       <c r="C138" s="1">
         <v>40000183</v>
       </c>
@@ -5543,7 +5519,7 @@
         <v>5</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G138" s="1">
         <v>2007</v>
@@ -5561,13 +5537,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="139" customHeight="1" spans="1:11">
-      <c r="A139" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="B139" s="1" t="s">
-        <v>166</v>
-      </c>
+    <row r="139" customHeight="1" spans="3:11">
       <c r="C139" s="1">
         <v>40000184</v>
       </c>
@@ -5578,7 +5548,7 @@
         <v>5</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G139" s="1">
         <v>2008</v>
@@ -5598,10 +5568,10 @@
     </row>
     <row r="140" customHeight="1" spans="1:11">
       <c r="A140" s="1" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="C140" s="1">
         <v>40000185</v>
@@ -5633,10 +5603,10 @@
     </row>
     <row r="141" customHeight="1" spans="1:11">
       <c r="A141" s="1" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="C141" s="1">
         <v>40000186</v>
@@ -5668,10 +5638,10 @@
     </row>
     <row r="142" customHeight="1" spans="1:11">
       <c r="A142" s="1" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="C142" s="1">
         <v>40000187</v>
@@ -5703,10 +5673,10 @@
     </row>
     <row r="143" customHeight="1" spans="1:11">
       <c r="A143" s="1" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="C143" s="1">
         <v>40000188</v>
@@ -5738,10 +5708,10 @@
     </row>
     <row r="144" customHeight="1" spans="1:11">
       <c r="A144" s="1" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="C144" s="1">
         <v>40000189</v>
@@ -5773,10 +5743,10 @@
     </row>
     <row r="145" customHeight="1" spans="1:11">
       <c r="A145" s="1" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="C145" s="1">
         <v>40000190</v>
@@ -5808,10 +5778,10 @@
     </row>
     <row r="146" customHeight="1" spans="1:11">
       <c r="A146" s="1" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="C146" s="1">
         <v>40000191</v>
@@ -5843,10 +5813,10 @@
     </row>
     <row r="147" customHeight="1" spans="1:11">
       <c r="A147" s="1" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="C147" s="1">
         <v>40000192</v>
@@ -5878,10 +5848,10 @@
     </row>
     <row r="148" customHeight="1" spans="1:11">
       <c r="A148" s="1" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="C148" s="1">
         <v>40000193</v>
@@ -5913,10 +5883,10 @@
     </row>
     <row r="149" customHeight="1" spans="1:11">
       <c r="A149" s="1" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="C149" s="1">
         <v>40000194</v>
@@ -5948,10 +5918,10 @@
     </row>
     <row r="150" customHeight="1" spans="1:11">
       <c r="A150" s="1" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="C150" s="1">
         <v>40000195</v>
@@ -5983,10 +5953,10 @@
     </row>
     <row r="151" customHeight="1" spans="1:11">
       <c r="A151" s="1" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="C151" s="1">
         <v>40000196</v>
@@ -6018,10 +5988,10 @@
     </row>
     <row r="152" customHeight="1" spans="1:11">
       <c r="A152" s="1" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="C152" s="1">
         <v>40000197</v>
@@ -6053,10 +6023,10 @@
     </row>
     <row r="153" customHeight="1" spans="1:11">
       <c r="A153" s="1" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="C153" s="1">
         <v>40000198</v>
@@ -6088,10 +6058,10 @@
     </row>
     <row r="154" customHeight="1" spans="1:11">
       <c r="A154" s="1" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="C154" s="1">
         <v>40000199</v>
@@ -6123,10 +6093,10 @@
     </row>
     <row r="155" customHeight="1" spans="1:11">
       <c r="A155" s="1" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="C155" s="1">
         <v>40000200</v>
@@ -6158,10 +6128,10 @@
     </row>
     <row r="156" customHeight="1" spans="1:11">
       <c r="A156" s="1" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="C156" s="1">
         <v>40000201</v>
@@ -6193,10 +6163,10 @@
     </row>
     <row r="157" customHeight="1" spans="1:11">
       <c r="A157" s="1" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="C157" s="1">
         <v>40000202</v>
@@ -6228,10 +6198,10 @@
     </row>
     <row r="158" customHeight="1" spans="1:11">
       <c r="A158" s="1" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="C158" s="1">
         <v>40000203</v>
@@ -6263,10 +6233,10 @@
     </row>
     <row r="159" customHeight="1" spans="1:11">
       <c r="A159" s="1" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="C159" s="1">
         <v>40000204</v>
@@ -6298,10 +6268,10 @@
     </row>
     <row r="160" customHeight="1" spans="1:11">
       <c r="A160" s="1" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="C160" s="1">
         <v>40000205</v>
@@ -6333,10 +6303,10 @@
     </row>
     <row r="161" customHeight="1" spans="1:11">
       <c r="A161" s="1" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="C161" s="1">
         <v>40000206</v>
@@ -6368,10 +6338,10 @@
     </row>
     <row r="162" customHeight="1" spans="1:11">
       <c r="A162" s="1" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="C162" s="1">
         <v>40000207</v>
@@ -6403,10 +6373,10 @@
     </row>
     <row r="163" customHeight="1" spans="1:11">
       <c r="A163" s="1" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="C163" s="1">
         <v>40000208</v>
@@ -6438,10 +6408,10 @@
     </row>
     <row r="164" customHeight="1" spans="1:11">
       <c r="A164" s="1" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="C164" s="1">
         <v>40000209</v>

--- a/Excel/HalidomConfig.xlsx
+++ b/Excel/HalidomConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="197">
   <si>
     <t>Id</t>
   </si>
@@ -542,22 +542,22 @@
     <t>混沌蛇胆</t>
   </si>
   <si>
+    <t>混沌狼爪</t>
+  </si>
+  <si>
+    <t>混沌虫皮</t>
+  </si>
+  <si>
+    <t>混沌鹰羽</t>
+  </si>
+  <si>
+    <t>混沌虫角</t>
+  </si>
+  <si>
+    <t>混沌蜈膏</t>
+  </si>
+  <si>
     <t>#</t>
-  </si>
-  <si>
-    <t>混沌狼爪</t>
-  </si>
-  <si>
-    <t>混沌虫皮</t>
-  </si>
-  <si>
-    <t>混沌鹰羽</t>
-  </si>
-  <si>
-    <t>混沌虫角</t>
-  </si>
-  <si>
-    <t>混沌蜈膏</t>
   </si>
   <si>
     <t>混沌虫心</t>
@@ -5566,13 +5566,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="140" customHeight="1" spans="1:11">
-      <c r="A140" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="B140" s="1" t="s">
-        <v>171</v>
-      </c>
+    <row r="140" customHeight="1" spans="3:11">
       <c r="C140" s="1">
         <v>40000185</v>
       </c>
@@ -5583,7 +5577,7 @@
         <v>5</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G140" s="1">
         <v>2009</v>
@@ -5601,13 +5595,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="141" customHeight="1" spans="1:11">
-      <c r="A141" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="B141" s="1" t="s">
-        <v>171</v>
-      </c>
+    <row r="141" customHeight="1" spans="3:11">
       <c r="C141" s="1">
         <v>40000186</v>
       </c>
@@ -5618,7 +5606,7 @@
         <v>5</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="G141" s="1">
         <v>2012</v>
@@ -5636,13 +5624,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="142" customHeight="1" spans="1:11">
-      <c r="A142" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="B142" s="1" t="s">
-        <v>171</v>
-      </c>
+    <row r="142" customHeight="1" spans="3:11">
       <c r="C142" s="1">
         <v>40000187</v>
       </c>
@@ -5653,7 +5635,7 @@
         <v>5</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G142" s="1">
         <v>2002</v>
@@ -5671,13 +5653,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="143" customHeight="1" spans="1:11">
-      <c r="A143" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="B143" s="1" t="s">
-        <v>171</v>
-      </c>
+    <row r="143" customHeight="1" spans="3:11">
       <c r="C143" s="1">
         <v>40000188</v>
       </c>
@@ -5688,7 +5664,7 @@
         <v>5</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G143" s="1">
         <v>2003</v>
@@ -5706,13 +5682,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="144" customHeight="1" spans="1:11">
-      <c r="A144" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="B144" s="1" t="s">
-        <v>171</v>
-      </c>
+    <row r="144" customHeight="1" spans="3:11">
       <c r="C144" s="1">
         <v>40000189</v>
       </c>
@@ -5723,7 +5693,7 @@
         <v>5</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G144" s="2">
         <v>2004</v>
@@ -5743,10 +5713,10 @@
     </row>
     <row r="145" customHeight="1" spans="1:11">
       <c r="A145" s="1" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="C145" s="1">
         <v>40000190</v>
@@ -5778,10 +5748,10 @@
     </row>
     <row r="146" customHeight="1" spans="1:11">
       <c r="A146" s="1" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="C146" s="1">
         <v>40000191</v>
@@ -5813,10 +5783,10 @@
     </row>
     <row r="147" customHeight="1" spans="1:11">
       <c r="A147" s="1" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="C147" s="1">
         <v>40000192</v>
@@ -5848,10 +5818,10 @@
     </row>
     <row r="148" customHeight="1" spans="1:11">
       <c r="A148" s="1" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="C148" s="1">
         <v>40000193</v>
@@ -5883,10 +5853,10 @@
     </row>
     <row r="149" customHeight="1" spans="1:11">
       <c r="A149" s="1" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="C149" s="1">
         <v>40000194</v>
@@ -5918,10 +5888,10 @@
     </row>
     <row r="150" customHeight="1" spans="1:11">
       <c r="A150" s="1" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="C150" s="1">
         <v>40000195</v>
@@ -5953,10 +5923,10 @@
     </row>
     <row r="151" customHeight="1" spans="1:11">
       <c r="A151" s="1" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="C151" s="1">
         <v>40000196</v>
@@ -5988,10 +5958,10 @@
     </row>
     <row r="152" customHeight="1" spans="1:11">
       <c r="A152" s="1" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="C152" s="1">
         <v>40000197</v>
@@ -6023,10 +5993,10 @@
     </row>
     <row r="153" customHeight="1" spans="1:11">
       <c r="A153" s="1" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="C153" s="1">
         <v>40000198</v>
@@ -6058,10 +6028,10 @@
     </row>
     <row r="154" customHeight="1" spans="1:11">
       <c r="A154" s="1" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="C154" s="1">
         <v>40000199</v>
@@ -6093,10 +6063,10 @@
     </row>
     <row r="155" customHeight="1" spans="1:11">
       <c r="A155" s="1" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="C155" s="1">
         <v>40000200</v>
@@ -6128,10 +6098,10 @@
     </row>
     <row r="156" customHeight="1" spans="1:11">
       <c r="A156" s="1" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="C156" s="1">
         <v>40000201</v>
@@ -6163,10 +6133,10 @@
     </row>
     <row r="157" customHeight="1" spans="1:11">
       <c r="A157" s="1" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="C157" s="1">
         <v>40000202</v>
@@ -6198,10 +6168,10 @@
     </row>
     <row r="158" customHeight="1" spans="1:11">
       <c r="A158" s="1" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="C158" s="1">
         <v>40000203</v>
@@ -6233,10 +6203,10 @@
     </row>
     <row r="159" customHeight="1" spans="1:11">
       <c r="A159" s="1" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="C159" s="1">
         <v>40000204</v>
@@ -6268,10 +6238,10 @@
     </row>
     <row r="160" customHeight="1" spans="1:11">
       <c r="A160" s="1" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="C160" s="1">
         <v>40000205</v>
@@ -6303,10 +6273,10 @@
     </row>
     <row r="161" customHeight="1" spans="1:11">
       <c r="A161" s="1" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="C161" s="1">
         <v>40000206</v>
@@ -6338,10 +6308,10 @@
     </row>
     <row r="162" customHeight="1" spans="1:11">
       <c r="A162" s="1" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="C162" s="1">
         <v>40000207</v>
@@ -6373,10 +6343,10 @@
     </row>
     <row r="163" customHeight="1" spans="1:11">
       <c r="A163" s="1" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="C163" s="1">
         <v>40000208</v>
@@ -6408,10 +6378,10 @@
     </row>
     <row r="164" customHeight="1" spans="1:11">
       <c r="A164" s="1" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="C164" s="1">
         <v>40000209</v>

--- a/Excel/HalidomConfig.xlsx
+++ b/Excel/HalidomConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="198">
   <si>
     <t>Id</t>
   </si>
@@ -557,22 +557,25 @@
     <t>混沌蜈膏</t>
   </si>
   <si>
+    <t>混沌虫心</t>
+  </si>
+  <si>
+    <t>混沌龙皮</t>
+  </si>
+  <si>
+    <t>混沌猪皮</t>
+  </si>
+  <si>
+    <t>混沌猪心</t>
+  </si>
+  <si>
+    <t>破韧倍率</t>
+  </si>
+  <si>
+    <t>混沌蝎皮</t>
+  </si>
+  <si>
     <t>#</t>
-  </si>
-  <si>
-    <t>混沌虫心</t>
-  </si>
-  <si>
-    <t>混沌龙皮</t>
-  </si>
-  <si>
-    <t>混沌猪皮</t>
-  </si>
-  <si>
-    <t>混沌猪心</t>
-  </si>
-  <si>
-    <t>混沌蝎皮</t>
   </si>
   <si>
     <t>混沌宝甲</t>
@@ -1256,13 +1259,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -5712,12 +5716,6 @@
       </c>
     </row>
     <row r="145" customHeight="1" spans="1:11">
-      <c r="A145" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="B145" s="1" t="s">
-        <v>176</v>
-      </c>
       <c r="C145" s="1">
         <v>40000190</v>
       </c>
@@ -5728,7 +5726,7 @@
         <v>5</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G145" s="1">
         <v>2005</v>
@@ -5747,12 +5745,6 @@
       </c>
     </row>
     <row r="146" customHeight="1" spans="1:11">
-      <c r="A146" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="B146" s="1" t="s">
-        <v>176</v>
-      </c>
       <c r="C146" s="1">
         <v>40000191</v>
       </c>
@@ -5763,7 +5755,7 @@
         <v>5</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G146" s="1">
         <v>2006</v>
@@ -5782,12 +5774,6 @@
       </c>
     </row>
     <row r="147" customHeight="1" spans="1:11">
-      <c r="A147" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="B147" s="1" t="s">
-        <v>176</v>
-      </c>
       <c r="C147" s="1">
         <v>40000192</v>
       </c>
@@ -5798,7 +5784,7 @@
         <v>5</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G147" s="1">
         <v>2010</v>
@@ -5817,12 +5803,6 @@
       </c>
     </row>
     <row r="148" customHeight="1" spans="1:11">
-      <c r="A148" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="B148" s="1" t="s">
-        <v>176</v>
-      </c>
       <c r="C148" s="1">
         <v>40000193</v>
       </c>
@@ -5833,31 +5813,25 @@
         <v>5</v>
       </c>
       <c r="F148" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="G148" s="1">
+        <v>2013</v>
+      </c>
+      <c r="H148" s="1">
+        <v>15</v>
+      </c>
+      <c r="I148" s="1">
+        <v>15</v>
+      </c>
+      <c r="J148" s="1">
+        <v>4</v>
+      </c>
+      <c r="K148" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="G148" s="1">
-        <v>2012</v>
-      </c>
-      <c r="H148" s="1">
-        <v>25</v>
-      </c>
-      <c r="I148" s="1">
-        <v>25</v>
-      </c>
-      <c r="J148" s="1">
-        <v>4</v>
-      </c>
-      <c r="K148" s="1" t="s">
-        <v>127</v>
-      </c>
     </row>
     <row r="149" customHeight="1" spans="1:11">
-      <c r="A149" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="B149" s="1" t="s">
-        <v>176</v>
-      </c>
       <c r="C149" s="1">
         <v>40000194</v>
       </c>
@@ -5871,27 +5845,27 @@
         <v>181</v>
       </c>
       <c r="G149" s="1">
-        <v>2002</v>
+        <v>2007</v>
       </c>
       <c r="H149" s="1">
-        <v>50</v>
+        <v>7</v>
       </c>
       <c r="I149" s="1">
-        <v>50</v>
+        <v>7</v>
       </c>
       <c r="J149" s="1">
         <v>4</v>
       </c>
       <c r="K149" s="1" t="s">
-        <v>50</v>
+        <v>132</v>
       </c>
     </row>
     <row r="150" customHeight="1" spans="1:11">
       <c r="A150" s="1" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="C150" s="1">
         <v>40000195</v>
@@ -5903,30 +5877,30 @@
         <v>5</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G150" s="1">
-        <v>2003</v>
+        <v>2008</v>
       </c>
       <c r="H150" s="1">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="I150" s="1">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="J150" s="1">
         <v>4</v>
       </c>
       <c r="K150" s="1" t="s">
-        <v>17</v>
+        <v>134</v>
       </c>
     </row>
     <row r="151" customHeight="1" spans="1:11">
       <c r="A151" s="1" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="C151" s="1">
         <v>40000196</v>
@@ -5938,10 +5912,10 @@
         <v>5</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G151" s="1">
-        <v>2001</v>
+        <v>2009</v>
       </c>
       <c r="H151" s="1">
         <v>7</v>
@@ -5953,15 +5927,15 @@
         <v>4</v>
       </c>
       <c r="K151" s="1" t="s">
-        <v>52</v>
+        <v>136</v>
       </c>
     </row>
     <row r="152" customHeight="1" spans="1:11">
       <c r="A152" s="1" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="C152" s="1">
         <v>40000197</v>
@@ -5973,7 +5947,7 @@
         <v>5</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G152" s="1">
         <v>2007</v>
@@ -5993,10 +5967,10 @@
     </row>
     <row r="153" customHeight="1" spans="1:11">
       <c r="A153" s="1" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="C153" s="1">
         <v>40000198</v>
@@ -6008,7 +5982,7 @@
         <v>5</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G153" s="1">
         <v>2008</v>
@@ -6028,10 +6002,10 @@
     </row>
     <row r="154" customHeight="1" spans="1:11">
       <c r="A154" s="1" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="C154" s="1">
         <v>40000199</v>
@@ -6043,7 +6017,7 @@
         <v>5</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G154" s="1">
         <v>2009</v>
@@ -6063,10 +6037,10 @@
     </row>
     <row r="155" customHeight="1" spans="1:11">
       <c r="A155" s="1" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="C155" s="1">
         <v>40000200</v>
@@ -6078,30 +6052,30 @@
         <v>5</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="G155" s="1">
-        <v>2012</v>
-      </c>
-      <c r="H155" s="1">
-        <v>25</v>
-      </c>
-      <c r="I155" s="1">
-        <v>25</v>
-      </c>
-      <c r="J155" s="1">
-        <v>4</v>
-      </c>
-      <c r="K155" s="1" t="s">
-        <v>127</v>
+        <v>188</v>
+      </c>
+      <c r="G155" s="2">
+        <v>2001</v>
+      </c>
+      <c r="H155" s="2">
+        <v>7</v>
+      </c>
+      <c r="I155" s="2">
+        <v>7</v>
+      </c>
+      <c r="J155" s="2">
+        <v>4</v>
+      </c>
+      <c r="K155" s="2" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="156" customHeight="1" spans="1:11">
       <c r="A156" s="1" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="C156" s="1">
         <v>40000201</v>
@@ -6113,30 +6087,30 @@
         <v>5</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="G156" s="1">
-        <v>2002</v>
-      </c>
-      <c r="H156" s="1">
-        <v>50</v>
-      </c>
-      <c r="I156" s="1">
-        <v>50</v>
-      </c>
-      <c r="J156" s="1">
-        <v>4</v>
-      </c>
-      <c r="K156" s="1" t="s">
-        <v>50</v>
+        <v>189</v>
+      </c>
+      <c r="G156" s="4">
+        <v>2004</v>
+      </c>
+      <c r="H156" s="4">
+        <v>7</v>
+      </c>
+      <c r="I156" s="4">
+        <v>7</v>
+      </c>
+      <c r="J156" s="4">
+        <v>4</v>
+      </c>
+      <c r="K156" s="4" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="157" customHeight="1" spans="1:11">
       <c r="A157" s="1" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="C157" s="1">
         <v>40000202</v>
@@ -6148,30 +6122,30 @@
         <v>5</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="G157" s="1">
-        <v>2003</v>
+        <v>2005</v>
       </c>
       <c r="H157" s="1">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="I157" s="1">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="J157" s="1">
         <v>4</v>
       </c>
       <c r="K157" s="1" t="s">
-        <v>17</v>
+        <v>123</v>
       </c>
     </row>
     <row r="158" customHeight="1" spans="1:11">
       <c r="A158" s="1" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="C158" s="1">
         <v>40000203</v>
@@ -6183,30 +6157,30 @@
         <v>5</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="G158" s="2">
-        <v>2004</v>
-      </c>
-      <c r="H158" s="2">
-        <v>7</v>
-      </c>
-      <c r="I158" s="2">
-        <v>7</v>
-      </c>
-      <c r="J158" s="2">
-        <v>4</v>
-      </c>
-      <c r="K158" s="2" t="s">
-        <v>43</v>
+        <v>191</v>
+      </c>
+      <c r="G158" s="1">
+        <v>2006</v>
+      </c>
+      <c r="H158" s="1">
+        <v>7</v>
+      </c>
+      <c r="I158" s="1">
+        <v>7</v>
+      </c>
+      <c r="J158" s="1">
+        <v>4</v>
+      </c>
+      <c r="K158" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="159" customHeight="1" spans="1:11">
       <c r="A159" s="1" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="C159" s="1">
         <v>40000204</v>
@@ -6218,10 +6192,10 @@
         <v>5</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G159" s="1">
-        <v>2005</v>
+        <v>2010</v>
       </c>
       <c r="H159" s="1">
         <v>7</v>
@@ -6233,15 +6207,15 @@
         <v>4</v>
       </c>
       <c r="K159" s="1" t="s">
-        <v>123</v>
+        <v>92</v>
       </c>
     </row>
     <row r="160" customHeight="1" spans="1:11">
       <c r="A160" s="1" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="C160" s="1">
         <v>40000205</v>
@@ -6253,10 +6227,10 @@
         <v>5</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G160" s="1">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="H160" s="1">
         <v>7</v>
@@ -6268,15 +6242,15 @@
         <v>4</v>
       </c>
       <c r="K160" s="1" t="s">
-        <v>47</v>
+        <v>132</v>
       </c>
     </row>
     <row r="161" customHeight="1" spans="1:11">
       <c r="A161" s="1" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="C161" s="1">
         <v>40000206</v>
@@ -6288,10 +6262,10 @@
         <v>5</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G161" s="1">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="H161" s="1">
         <v>7</v>
@@ -6303,15 +6277,15 @@
         <v>4</v>
       </c>
       <c r="K161" s="1" t="s">
-        <v>92</v>
+        <v>134</v>
       </c>
     </row>
     <row r="162" customHeight="1" spans="1:11">
       <c r="A162" s="1" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="C162" s="1">
         <v>40000207</v>
@@ -6323,30 +6297,30 @@
         <v>5</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G162" s="1">
-        <v>2012</v>
+        <v>2009</v>
       </c>
       <c r="H162" s="1">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="I162" s="1">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="J162" s="1">
         <v>4</v>
       </c>
       <c r="K162" s="1" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
     </row>
     <row r="163" customHeight="1" spans="1:11">
       <c r="A163" s="1" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="C163" s="1">
         <v>40000208</v>
@@ -6358,30 +6332,30 @@
         <v>5</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G163" s="1">
-        <v>2002</v>
+        <v>2013</v>
       </c>
       <c r="H163" s="1">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="I163" s="1">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="J163" s="1">
         <v>4</v>
       </c>
       <c r="K163" s="1" t="s">
-        <v>50</v>
+        <v>180</v>
       </c>
     </row>
     <row r="164" customHeight="1" spans="1:11">
       <c r="A164" s="1" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="C164" s="1">
         <v>40000209</v>
@@ -6393,7 +6367,7 @@
         <v>5</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G164" s="1">
         <v>2003</v>

--- a/Excel/HalidomConfig.xlsx
+++ b/Excel/HalidomConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="198">
   <si>
     <t>Id</t>
   </si>
@@ -575,22 +575,22 @@
     <t>混沌蝎皮</t>
   </si>
   <si>
+    <t>混沌宝甲</t>
+  </si>
+  <si>
+    <t>混沌号角</t>
+  </si>
+  <si>
+    <t>混沌雕像</t>
+  </si>
+  <si>
+    <t>混沌神像</t>
+  </si>
+  <si>
+    <t>混沌獠牙</t>
+  </si>
+  <si>
     <t>#</t>
-  </si>
-  <si>
-    <t>混沌宝甲</t>
-  </si>
-  <si>
-    <t>混沌号角</t>
-  </si>
-  <si>
-    <t>混沌雕像</t>
-  </si>
-  <si>
-    <t>混沌神像</t>
-  </si>
-  <si>
-    <t>混沌獠牙</t>
   </si>
   <si>
     <t>混沌树心</t>
@@ -5861,12 +5861,6 @@
       </c>
     </row>
     <row r="150" customHeight="1" spans="1:11">
-      <c r="A150" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="B150" s="1" t="s">
-        <v>182</v>
-      </c>
       <c r="C150" s="1">
         <v>40000195</v>
       </c>
@@ -5877,7 +5871,7 @@
         <v>5</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G150" s="1">
         <v>2008</v>
@@ -5896,12 +5890,6 @@
       </c>
     </row>
     <row r="151" customHeight="1" spans="1:11">
-      <c r="A151" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="B151" s="1" t="s">
-        <v>182</v>
-      </c>
       <c r="C151" s="1">
         <v>40000196</v>
       </c>
@@ -5912,7 +5900,7 @@
         <v>5</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G151" s="1">
         <v>2009</v>
@@ -5931,12 +5919,6 @@
       </c>
     </row>
     <row r="152" customHeight="1" spans="1:11">
-      <c r="A152" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="B152" s="1" t="s">
-        <v>182</v>
-      </c>
       <c r="C152" s="1">
         <v>40000197</v>
       </c>
@@ -5947,7 +5929,7 @@
         <v>5</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G152" s="1">
         <v>2007</v>
@@ -5966,12 +5948,6 @@
       </c>
     </row>
     <row r="153" customHeight="1" spans="1:11">
-      <c r="A153" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="B153" s="1" t="s">
-        <v>182</v>
-      </c>
       <c r="C153" s="1">
         <v>40000198</v>
       </c>
@@ -5982,7 +5958,7 @@
         <v>5</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G153" s="1">
         <v>2008</v>
@@ -6001,12 +5977,6 @@
       </c>
     </row>
     <row r="154" customHeight="1" spans="1:11">
-      <c r="A154" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="B154" s="1" t="s">
-        <v>182</v>
-      </c>
       <c r="C154" s="1">
         <v>40000199</v>
       </c>
@@ -6017,7 +5987,7 @@
         <v>5</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G154" s="1">
         <v>2009</v>
@@ -6037,10 +6007,10 @@
     </row>
     <row r="155" customHeight="1" spans="1:11">
       <c r="A155" s="1" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="C155" s="1">
         <v>40000200</v>
@@ -6072,10 +6042,10 @@
     </row>
     <row r="156" customHeight="1" spans="1:11">
       <c r="A156" s="1" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="C156" s="1">
         <v>40000201</v>
@@ -6107,10 +6077,10 @@
     </row>
     <row r="157" customHeight="1" spans="1:11">
       <c r="A157" s="1" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="C157" s="1">
         <v>40000202</v>
@@ -6142,10 +6112,10 @@
     </row>
     <row r="158" customHeight="1" spans="1:11">
       <c r="A158" s="1" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="C158" s="1">
         <v>40000203</v>
@@ -6177,10 +6147,10 @@
     </row>
     <row r="159" customHeight="1" spans="1:11">
       <c r="A159" s="1" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="C159" s="1">
         <v>40000204</v>
@@ -6212,10 +6182,10 @@
     </row>
     <row r="160" customHeight="1" spans="1:11">
       <c r="A160" s="1" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="C160" s="1">
         <v>40000205</v>
@@ -6247,10 +6217,10 @@
     </row>
     <row r="161" customHeight="1" spans="1:11">
       <c r="A161" s="1" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="C161" s="1">
         <v>40000206</v>
@@ -6282,10 +6252,10 @@
     </row>
     <row r="162" customHeight="1" spans="1:11">
       <c r="A162" s="1" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="C162" s="1">
         <v>40000207</v>
@@ -6317,10 +6287,10 @@
     </row>
     <row r="163" customHeight="1" spans="1:11">
       <c r="A163" s="1" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="C163" s="1">
         <v>40000208</v>
@@ -6352,10 +6322,10 @@
     </row>
     <row r="164" customHeight="1" spans="1:11">
       <c r="A164" s="1" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="C164" s="1">
         <v>40000209</v>

--- a/Excel/HalidomConfig.xlsx
+++ b/Excel/HalidomConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="198">
   <si>
     <t>Id</t>
   </si>
@@ -590,22 +590,22 @@
     <t>混沌獠牙</t>
   </si>
   <si>
+    <t>混沌树心</t>
+  </si>
+  <si>
+    <t>混沌魔心</t>
+  </si>
+  <si>
+    <t>混沌尸心</t>
+  </si>
+  <si>
+    <t>混沌法杖</t>
+  </si>
+  <si>
+    <t>混沌权杖</t>
+  </si>
+  <si>
     <t>#</t>
-  </si>
-  <si>
-    <t>混沌树心</t>
-  </si>
-  <si>
-    <t>混沌魔心</t>
-  </si>
-  <si>
-    <t>混沌尸心</t>
-  </si>
-  <si>
-    <t>混沌法杖</t>
-  </si>
-  <si>
-    <t>混沌权杖</t>
   </si>
   <si>
     <t>混沌战锤</t>
@@ -6006,12 +6006,6 @@
       </c>
     </row>
     <row r="155" customHeight="1" spans="1:11">
-      <c r="A155" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="B155" s="1" t="s">
-        <v>187</v>
-      </c>
       <c r="C155" s="1">
         <v>40000200</v>
       </c>
@@ -6022,7 +6016,7 @@
         <v>5</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G155" s="2">
         <v>2001</v>
@@ -6041,12 +6035,6 @@
       </c>
     </row>
     <row r="156" customHeight="1" spans="1:11">
-      <c r="A156" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="B156" s="1" t="s">
-        <v>187</v>
-      </c>
       <c r="C156" s="1">
         <v>40000201</v>
       </c>
@@ -6057,7 +6045,7 @@
         <v>5</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G156" s="4">
         <v>2004</v>
@@ -6076,12 +6064,6 @@
       </c>
     </row>
     <row r="157" customHeight="1" spans="1:11">
-      <c r="A157" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="B157" s="1" t="s">
-        <v>187</v>
-      </c>
       <c r="C157" s="1">
         <v>40000202</v>
       </c>
@@ -6092,7 +6074,7 @@
         <v>5</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G157" s="1">
         <v>2005</v>
@@ -6111,12 +6093,6 @@
       </c>
     </row>
     <row r="158" customHeight="1" spans="1:11">
-      <c r="A158" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="B158" s="1" t="s">
-        <v>187</v>
-      </c>
       <c r="C158" s="1">
         <v>40000203</v>
       </c>
@@ -6127,7 +6103,7 @@
         <v>5</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G158" s="1">
         <v>2006</v>
@@ -6146,12 +6122,6 @@
       </c>
     </row>
     <row r="159" customHeight="1" spans="1:11">
-      <c r="A159" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="B159" s="1" t="s">
-        <v>187</v>
-      </c>
       <c r="C159" s="1">
         <v>40000204</v>
       </c>
@@ -6162,7 +6132,7 @@
         <v>5</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G159" s="1">
         <v>2010</v>
@@ -6182,10 +6152,10 @@
     </row>
     <row r="160" customHeight="1" spans="1:11">
       <c r="A160" s="1" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="C160" s="1">
         <v>40000205</v>
@@ -6217,10 +6187,10 @@
     </row>
     <row r="161" customHeight="1" spans="1:11">
       <c r="A161" s="1" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="C161" s="1">
         <v>40000206</v>
@@ -6252,10 +6222,10 @@
     </row>
     <row r="162" customHeight="1" spans="1:11">
       <c r="A162" s="1" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="C162" s="1">
         <v>40000207</v>
@@ -6287,10 +6257,10 @@
     </row>
     <row r="163" customHeight="1" spans="1:11">
       <c r="A163" s="1" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="C163" s="1">
         <v>40000208</v>
@@ -6322,10 +6292,10 @@
     </row>
     <row r="164" customHeight="1" spans="1:11">
       <c r="A164" s="1" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="C164" s="1">
         <v>40000209</v>

--- a/Excel/HalidomConfig.xlsx
+++ b/Excel/HalidomConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="197">
   <si>
     <t>Id</t>
   </si>
@@ -603,9 +603,6 @@
   </si>
   <si>
     <t>混沌权杖</t>
-  </si>
-  <si>
-    <t>#</t>
   </si>
   <si>
     <t>混沌战锤</t>
@@ -1586,7 +1583,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:K164"/>
+  <dimension ref="C3:K164"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="5" width="9" style="1"/>
@@ -5715,7 +5712,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="145" customHeight="1" spans="1:11">
+    <row r="145" customHeight="1" spans="3:11">
       <c r="C145" s="1">
         <v>40000190</v>
       </c>
@@ -5744,7 +5741,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="146" customHeight="1" spans="1:11">
+    <row r="146" customHeight="1" spans="3:11">
       <c r="C146" s="1">
         <v>40000191</v>
       </c>
@@ -5773,7 +5770,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="147" customHeight="1" spans="1:11">
+    <row r="147" customHeight="1" spans="3:11">
       <c r="C147" s="1">
         <v>40000192</v>
       </c>
@@ -5802,7 +5799,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="148" customHeight="1" spans="1:11">
+    <row r="148" customHeight="1" spans="3:11">
       <c r="C148" s="1">
         <v>40000193</v>
       </c>
@@ -5831,7 +5828,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="149" customHeight="1" spans="1:11">
+    <row r="149" customHeight="1" spans="3:11">
       <c r="C149" s="1">
         <v>40000194</v>
       </c>
@@ -5860,7 +5857,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="150" customHeight="1" spans="1:11">
+    <row r="150" customHeight="1" spans="3:11">
       <c r="C150" s="1">
         <v>40000195</v>
       </c>
@@ -5889,7 +5886,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="151" customHeight="1" spans="1:11">
+    <row r="151" customHeight="1" spans="3:11">
       <c r="C151" s="1">
         <v>40000196</v>
       </c>
@@ -5918,7 +5915,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="152" customHeight="1" spans="1:11">
+    <row r="152" customHeight="1" spans="3:11">
       <c r="C152" s="1">
         <v>40000197</v>
       </c>
@@ -5947,7 +5944,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="153" customHeight="1" spans="1:11">
+    <row r="153" customHeight="1" spans="3:11">
       <c r="C153" s="1">
         <v>40000198</v>
       </c>
@@ -5976,7 +5973,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="154" customHeight="1" spans="1:11">
+    <row r="154" customHeight="1" spans="3:11">
       <c r="C154" s="1">
         <v>40000199</v>
       </c>
@@ -6005,7 +6002,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="155" customHeight="1" spans="1:11">
+    <row r="155" customHeight="1" spans="3:11">
       <c r="C155" s="1">
         <v>40000200</v>
       </c>
@@ -6034,7 +6031,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="156" customHeight="1" spans="1:11">
+    <row r="156" customHeight="1" spans="3:11">
       <c r="C156" s="1">
         <v>40000201</v>
       </c>
@@ -6063,7 +6060,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="157" customHeight="1" spans="1:11">
+    <row r="157" customHeight="1" spans="3:11">
       <c r="C157" s="1">
         <v>40000202</v>
       </c>
@@ -6092,7 +6089,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="158" customHeight="1" spans="1:11">
+    <row r="158" customHeight="1" spans="3:11">
       <c r="C158" s="1">
         <v>40000203</v>
       </c>
@@ -6121,7 +6118,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="159" customHeight="1" spans="1:11">
+    <row r="159" customHeight="1" spans="3:11">
       <c r="C159" s="1">
         <v>40000204</v>
       </c>
@@ -6150,13 +6147,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="160" customHeight="1" spans="1:11">
-      <c r="A160" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="B160" s="1" t="s">
-        <v>192</v>
-      </c>
+    <row r="160" customHeight="1" spans="3:11">
       <c r="C160" s="1">
         <v>40000205</v>
       </c>
@@ -6167,7 +6158,7 @@
         <v>5</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G160" s="1">
         <v>2007</v>
@@ -6185,13 +6176,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="161" customHeight="1" spans="1:11">
-      <c r="A161" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="B161" s="1" t="s">
-        <v>192</v>
-      </c>
+    <row r="161" customHeight="1" spans="3:11">
       <c r="C161" s="1">
         <v>40000206</v>
       </c>
@@ -6202,7 +6187,7 @@
         <v>5</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G161" s="1">
         <v>2008</v>
@@ -6220,13 +6205,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="162" customHeight="1" spans="1:11">
-      <c r="A162" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="B162" s="1" t="s">
-        <v>192</v>
-      </c>
+    <row r="162" customHeight="1" spans="3:11">
       <c r="C162" s="1">
         <v>40000207</v>
       </c>
@@ -6237,7 +6216,7 @@
         <v>5</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G162" s="1">
         <v>2009</v>
@@ -6255,13 +6234,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="163" customHeight="1" spans="1:11">
-      <c r="A163" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="B163" s="1" t="s">
-        <v>192</v>
-      </c>
+    <row r="163" customHeight="1" spans="3:11">
       <c r="C163" s="1">
         <v>40000208</v>
       </c>
@@ -6272,7 +6245,7 @@
         <v>5</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G163" s="1">
         <v>2013</v>
@@ -6290,13 +6263,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="164" customHeight="1" spans="1:11">
-      <c r="A164" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="B164" s="1" t="s">
-        <v>192</v>
-      </c>
+    <row r="164" customHeight="1" spans="3:11">
       <c r="C164" s="1">
         <v>40000209</v>
       </c>
@@ -6307,7 +6274,7 @@
         <v>5</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G164" s="1">
         <v>2003</v>

--- a/Excel/HalidomConfig.xlsx
+++ b/Excel/HalidomConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="232">
   <si>
     <t>Id</t>
   </si>
@@ -618,6 +618,111 @@
   </si>
   <si>
     <t>混沌龙爪</t>
+  </si>
+  <si>
+    <t>虚无鸡爪</t>
+  </si>
+  <si>
+    <t>虚无鹿茸</t>
+  </si>
+  <si>
+    <t>虚无草帽</t>
+  </si>
+  <si>
+    <t>虚无猫爪</t>
+  </si>
+  <si>
+    <t>虚无花朵</t>
+  </si>
+  <si>
+    <t>虚无冰晶</t>
+  </si>
+  <si>
+    <t>虚无蝠翼</t>
+  </si>
+  <si>
+    <t>虚无魂火</t>
+  </si>
+  <si>
+    <t>虚无腐肉</t>
+  </si>
+  <si>
+    <t>虚无蛇胆</t>
+  </si>
+  <si>
+    <t>虚无狼爪</t>
+  </si>
+  <si>
+    <t>虚无虫皮</t>
+  </si>
+  <si>
+    <t>虚无鹰羽</t>
+  </si>
+  <si>
+    <t>虚无虫角</t>
+  </si>
+  <si>
+    <t>虚无蜈膏</t>
+  </si>
+  <si>
+    <t>虚无虫心</t>
+  </si>
+  <si>
+    <t>虚无龙皮</t>
+  </si>
+  <si>
+    <t>虚无猪皮</t>
+  </si>
+  <si>
+    <t>虚无猪心</t>
+  </si>
+  <si>
+    <t>虚无蝎皮</t>
+  </si>
+  <si>
+    <t>虚无宝甲</t>
+  </si>
+  <si>
+    <t>虚无号角</t>
+  </si>
+  <si>
+    <t>虚无雕像</t>
+  </si>
+  <si>
+    <t>虚无神像</t>
+  </si>
+  <si>
+    <t>虚无獠牙</t>
+  </si>
+  <si>
+    <t>虚无树心</t>
+  </si>
+  <si>
+    <t>虚无魔心</t>
+  </si>
+  <si>
+    <t>虚无尸心</t>
+  </si>
+  <si>
+    <t>虚无法杖</t>
+  </si>
+  <si>
+    <t>虚无权杖</t>
+  </si>
+  <si>
+    <t>虚无战锤</t>
+  </si>
+  <si>
+    <t>虚无血核</t>
+  </si>
+  <si>
+    <t>虚无魔核</t>
+  </si>
+  <si>
+    <t>虚无龙甲</t>
+  </si>
+  <si>
+    <t>虚无龙爪</t>
   </si>
 </sst>
 </file>
@@ -1583,7 +1688,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:K164"/>
+  <dimension ref="C3:K202"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="5" width="9" style="1"/>
@@ -6292,6 +6397,1033 @@
         <v>17</v>
       </c>
     </row>
+    <row r="165" customHeight="1" spans="3:11">
+      <c r="C165" s="1">
+        <v>40000210</v>
+      </c>
+      <c r="D165" s="1">
+        <v>40000210</v>
+      </c>
+      <c r="E165" s="2">
+        <v>6</v>
+      </c>
+      <c r="F165" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="G165" s="2">
+        <v>2001</v>
+      </c>
+      <c r="H165" s="2">
+        <v>8</v>
+      </c>
+      <c r="I165" s="2">
+        <v>8</v>
+      </c>
+      <c r="J165" s="2">
+        <v>4</v>
+      </c>
+      <c r="K165" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="166" customHeight="1" spans="3:11">
+      <c r="C166" s="1">
+        <v>40000211</v>
+      </c>
+      <c r="D166" s="1">
+        <v>40000211</v>
+      </c>
+      <c r="E166" s="1">
+        <v>6</v>
+      </c>
+      <c r="F166" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="G166" s="4">
+        <v>2004</v>
+      </c>
+      <c r="H166" s="4">
+        <v>8</v>
+      </c>
+      <c r="I166" s="4">
+        <v>8</v>
+      </c>
+      <c r="J166" s="4">
+        <v>4</v>
+      </c>
+      <c r="K166" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="167" customHeight="1" spans="3:11">
+      <c r="C167" s="1">
+        <v>40000212</v>
+      </c>
+      <c r="D167" s="1">
+        <v>40000212</v>
+      </c>
+      <c r="E167" s="1">
+        <v>6</v>
+      </c>
+      <c r="F167" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="G167" s="1">
+        <v>2005</v>
+      </c>
+      <c r="H167" s="4">
+        <v>8</v>
+      </c>
+      <c r="I167" s="4">
+        <v>8</v>
+      </c>
+      <c r="J167" s="1">
+        <v>4</v>
+      </c>
+      <c r="K167" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="168" customHeight="1" spans="3:11">
+      <c r="C168" s="1">
+        <v>40000213</v>
+      </c>
+      <c r="D168" s="1">
+        <v>40000213</v>
+      </c>
+      <c r="E168" s="1">
+        <v>6</v>
+      </c>
+      <c r="F168" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="G168" s="1">
+        <v>2006</v>
+      </c>
+      <c r="H168" s="4">
+        <v>8</v>
+      </c>
+      <c r="I168" s="4">
+        <v>8</v>
+      </c>
+      <c r="J168" s="1">
+        <v>4</v>
+      </c>
+      <c r="K168" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="169" customHeight="1" spans="3:11">
+      <c r="C169" s="1">
+        <v>40000214</v>
+      </c>
+      <c r="D169" s="1">
+        <v>40000214</v>
+      </c>
+      <c r="E169" s="1">
+        <v>6</v>
+      </c>
+      <c r="F169" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="G169" s="1">
+        <v>2010</v>
+      </c>
+      <c r="H169" s="4">
+        <v>8</v>
+      </c>
+      <c r="I169" s="4">
+        <v>8</v>
+      </c>
+      <c r="J169" s="1">
+        <v>4</v>
+      </c>
+      <c r="K169" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="170" customHeight="1" spans="3:11">
+      <c r="C170" s="1">
+        <v>40000215</v>
+      </c>
+      <c r="D170" s="1">
+        <v>40000215</v>
+      </c>
+      <c r="E170" s="1">
+        <v>6</v>
+      </c>
+      <c r="F170" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="G170" s="1">
+        <v>2007</v>
+      </c>
+      <c r="H170" s="4">
+        <v>8</v>
+      </c>
+      <c r="I170" s="4">
+        <v>8</v>
+      </c>
+      <c r="J170" s="1">
+        <v>4</v>
+      </c>
+      <c r="K170" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="171" customHeight="1" spans="3:11">
+      <c r="C171" s="1">
+        <v>40000216</v>
+      </c>
+      <c r="D171" s="1">
+        <v>40000216</v>
+      </c>
+      <c r="E171" s="1">
+        <v>6</v>
+      </c>
+      <c r="F171" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="G171" s="1">
+        <v>2008</v>
+      </c>
+      <c r="H171" s="4">
+        <v>8</v>
+      </c>
+      <c r="I171" s="4">
+        <v>8</v>
+      </c>
+      <c r="J171" s="1">
+        <v>4</v>
+      </c>
+      <c r="K171" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="172" customHeight="1" spans="3:11">
+      <c r="C172" s="1">
+        <v>40000217</v>
+      </c>
+      <c r="D172" s="1">
+        <v>40000217</v>
+      </c>
+      <c r="E172" s="1">
+        <v>6</v>
+      </c>
+      <c r="F172" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="G172" s="1">
+        <v>2009</v>
+      </c>
+      <c r="H172" s="4">
+        <v>8</v>
+      </c>
+      <c r="I172" s="4">
+        <v>8</v>
+      </c>
+      <c r="J172" s="1">
+        <v>4</v>
+      </c>
+      <c r="K172" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="173" customHeight="1" spans="3:11">
+      <c r="C173" s="1">
+        <v>40000218</v>
+      </c>
+      <c r="D173" s="1">
+        <v>40000218</v>
+      </c>
+      <c r="E173" s="1">
+        <v>6</v>
+      </c>
+      <c r="F173" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="G173" s="1">
+        <v>2013</v>
+      </c>
+      <c r="H173" s="1">
+        <v>16</v>
+      </c>
+      <c r="I173" s="1">
+        <v>16</v>
+      </c>
+      <c r="J173" s="1">
+        <v>4</v>
+      </c>
+      <c r="K173" s="1" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="174" customHeight="1" spans="3:11">
+      <c r="C174" s="1">
+        <v>40000219</v>
+      </c>
+      <c r="D174" s="1">
+        <v>40000219</v>
+      </c>
+      <c r="E174" s="1">
+        <v>6</v>
+      </c>
+      <c r="F174" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="G174" s="1">
+        <v>2003</v>
+      </c>
+      <c r="H174" s="1">
+        <v>50</v>
+      </c>
+      <c r="I174" s="1">
+        <v>50</v>
+      </c>
+      <c r="J174" s="1">
+        <v>4</v>
+      </c>
+      <c r="K174" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="175" customHeight="1" spans="3:11">
+      <c r="C175" s="1">
+        <v>40000220</v>
+      </c>
+      <c r="D175" s="1">
+        <v>40000220</v>
+      </c>
+      <c r="E175" s="1">
+        <v>6</v>
+      </c>
+      <c r="F175" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="G175" s="2">
+        <v>2001</v>
+      </c>
+      <c r="H175" s="2">
+        <v>8</v>
+      </c>
+      <c r="I175" s="2">
+        <v>8</v>
+      </c>
+      <c r="J175" s="2">
+        <v>4</v>
+      </c>
+      <c r="K175" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="176" customHeight="1" spans="3:11">
+      <c r="C176" s="1">
+        <v>40000221</v>
+      </c>
+      <c r="D176" s="1">
+        <v>40000221</v>
+      </c>
+      <c r="E176" s="1">
+        <v>6</v>
+      </c>
+      <c r="F176" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="G176" s="4">
+        <v>2004</v>
+      </c>
+      <c r="H176" s="4">
+        <v>8</v>
+      </c>
+      <c r="I176" s="4">
+        <v>8</v>
+      </c>
+      <c r="J176" s="4">
+        <v>4</v>
+      </c>
+      <c r="K176" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="177" customHeight="1" spans="3:11">
+      <c r="C177" s="1">
+        <v>40000222</v>
+      </c>
+      <c r="D177" s="1">
+        <v>40000222</v>
+      </c>
+      <c r="E177" s="1">
+        <v>6</v>
+      </c>
+      <c r="F177" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="G177" s="1">
+        <v>2005</v>
+      </c>
+      <c r="H177" s="4">
+        <v>8</v>
+      </c>
+      <c r="I177" s="4">
+        <v>8</v>
+      </c>
+      <c r="J177" s="1">
+        <v>4</v>
+      </c>
+      <c r="K177" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="178" customHeight="1" spans="3:11">
+      <c r="C178" s="1">
+        <v>40000223</v>
+      </c>
+      <c r="D178" s="1">
+        <v>40000223</v>
+      </c>
+      <c r="E178" s="1">
+        <v>6</v>
+      </c>
+      <c r="F178" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="G178" s="1">
+        <v>2006</v>
+      </c>
+      <c r="H178" s="4">
+        <v>8</v>
+      </c>
+      <c r="I178" s="4">
+        <v>8</v>
+      </c>
+      <c r="J178" s="1">
+        <v>4</v>
+      </c>
+      <c r="K178" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="179" customHeight="1" spans="3:11">
+      <c r="C179" s="1">
+        <v>40000224</v>
+      </c>
+      <c r="D179" s="1">
+        <v>40000224</v>
+      </c>
+      <c r="E179" s="1">
+        <v>6</v>
+      </c>
+      <c r="F179" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="G179" s="1">
+        <v>2010</v>
+      </c>
+      <c r="H179" s="4">
+        <v>8</v>
+      </c>
+      <c r="I179" s="4">
+        <v>8</v>
+      </c>
+      <c r="J179" s="1">
+        <v>4</v>
+      </c>
+      <c r="K179" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="180" customHeight="1" spans="3:11">
+      <c r="C180" s="1">
+        <v>40000225</v>
+      </c>
+      <c r="D180" s="1">
+        <v>40000225</v>
+      </c>
+      <c r="E180" s="1">
+        <v>6</v>
+      </c>
+      <c r="F180" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="G180" s="1">
+        <v>2007</v>
+      </c>
+      <c r="H180" s="4">
+        <v>8</v>
+      </c>
+      <c r="I180" s="4">
+        <v>8</v>
+      </c>
+      <c r="J180" s="1">
+        <v>4</v>
+      </c>
+      <c r="K180" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="181" customHeight="1" spans="3:11">
+      <c r="C181" s="1">
+        <v>40000226</v>
+      </c>
+      <c r="D181" s="1">
+        <v>40000226</v>
+      </c>
+      <c r="E181" s="1">
+        <v>6</v>
+      </c>
+      <c r="F181" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="G181" s="1">
+        <v>2008</v>
+      </c>
+      <c r="H181" s="4">
+        <v>8</v>
+      </c>
+      <c r="I181" s="4">
+        <v>8</v>
+      </c>
+      <c r="J181" s="1">
+        <v>4</v>
+      </c>
+      <c r="K181" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="182" customHeight="1" spans="3:11">
+      <c r="C182" s="1">
+        <v>40000227</v>
+      </c>
+      <c r="D182" s="1">
+        <v>40000227</v>
+      </c>
+      <c r="E182" s="1">
+        <v>6</v>
+      </c>
+      <c r="F182" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="G182" s="1">
+        <v>2009</v>
+      </c>
+      <c r="H182" s="4">
+        <v>8</v>
+      </c>
+      <c r="I182" s="4">
+        <v>8</v>
+      </c>
+      <c r="J182" s="1">
+        <v>4</v>
+      </c>
+      <c r="K182" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="183" customHeight="1" spans="3:11">
+      <c r="C183" s="1">
+        <v>40000228</v>
+      </c>
+      <c r="D183" s="1">
+        <v>40000228</v>
+      </c>
+      <c r="E183" s="1">
+        <v>6</v>
+      </c>
+      <c r="F183" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="G183" s="1">
+        <v>2013</v>
+      </c>
+      <c r="H183" s="1">
+        <v>16</v>
+      </c>
+      <c r="I183" s="1">
+        <v>16</v>
+      </c>
+      <c r="J183" s="1">
+        <v>4</v>
+      </c>
+      <c r="K183" s="1" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="184" customHeight="1" spans="3:11">
+      <c r="C184" s="1">
+        <v>40000229</v>
+      </c>
+      <c r="D184" s="1">
+        <v>40000229</v>
+      </c>
+      <c r="E184" s="1">
+        <v>6</v>
+      </c>
+      <c r="F184" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="G184" s="1">
+        <v>2003</v>
+      </c>
+      <c r="H184" s="1">
+        <v>50</v>
+      </c>
+      <c r="I184" s="1">
+        <v>50</v>
+      </c>
+      <c r="J184" s="1">
+        <v>4</v>
+      </c>
+      <c r="K184" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="185" customHeight="1" spans="3:11">
+      <c r="C185" s="1">
+        <v>40000230</v>
+      </c>
+      <c r="D185" s="1">
+        <v>40000230</v>
+      </c>
+      <c r="E185" s="1">
+        <v>6</v>
+      </c>
+      <c r="F185" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="G185" s="2">
+        <v>2001</v>
+      </c>
+      <c r="H185" s="2">
+        <v>8</v>
+      </c>
+      <c r="I185" s="2">
+        <v>8</v>
+      </c>
+      <c r="J185" s="2">
+        <v>4</v>
+      </c>
+      <c r="K185" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="186" customHeight="1" spans="3:11">
+      <c r="C186" s="1">
+        <v>40000231</v>
+      </c>
+      <c r="D186" s="1">
+        <v>40000231</v>
+      </c>
+      <c r="E186" s="1">
+        <v>6</v>
+      </c>
+      <c r="F186" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="G186" s="4">
+        <v>2004</v>
+      </c>
+      <c r="H186" s="4">
+        <v>8</v>
+      </c>
+      <c r="I186" s="4">
+        <v>8</v>
+      </c>
+      <c r="J186" s="4">
+        <v>4</v>
+      </c>
+      <c r="K186" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="187" customHeight="1" spans="3:11">
+      <c r="C187" s="1">
+        <v>40000232</v>
+      </c>
+      <c r="D187" s="1">
+        <v>40000232</v>
+      </c>
+      <c r="E187" s="1">
+        <v>6</v>
+      </c>
+      <c r="F187" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="G187" s="1">
+        <v>2005</v>
+      </c>
+      <c r="H187" s="4">
+        <v>8</v>
+      </c>
+      <c r="I187" s="4">
+        <v>8</v>
+      </c>
+      <c r="J187" s="1">
+        <v>4</v>
+      </c>
+      <c r="K187" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="188" customHeight="1" spans="3:11">
+      <c r="C188" s="1">
+        <v>40000233</v>
+      </c>
+      <c r="D188" s="1">
+        <v>40000233</v>
+      </c>
+      <c r="E188" s="1">
+        <v>6</v>
+      </c>
+      <c r="F188" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="G188" s="1">
+        <v>2006</v>
+      </c>
+      <c r="H188" s="4">
+        <v>8</v>
+      </c>
+      <c r="I188" s="4">
+        <v>8</v>
+      </c>
+      <c r="J188" s="1">
+        <v>4</v>
+      </c>
+      <c r="K188" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="189" customHeight="1" spans="3:11">
+      <c r="C189" s="1">
+        <v>40000234</v>
+      </c>
+      <c r="D189" s="1">
+        <v>40000234</v>
+      </c>
+      <c r="E189" s="1">
+        <v>6</v>
+      </c>
+      <c r="F189" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="G189" s="1">
+        <v>2010</v>
+      </c>
+      <c r="H189" s="4">
+        <v>8</v>
+      </c>
+      <c r="I189" s="4">
+        <v>8</v>
+      </c>
+      <c r="J189" s="1">
+        <v>4</v>
+      </c>
+      <c r="K189" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="190" customHeight="1" spans="3:11">
+      <c r="C190" s="1">
+        <v>40000235</v>
+      </c>
+      <c r="D190" s="1">
+        <v>40000235</v>
+      </c>
+      <c r="E190" s="1">
+        <v>6</v>
+      </c>
+      <c r="F190" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="G190" s="1">
+        <v>2007</v>
+      </c>
+      <c r="H190" s="4">
+        <v>8</v>
+      </c>
+      <c r="I190" s="4">
+        <v>8</v>
+      </c>
+      <c r="J190" s="1">
+        <v>4</v>
+      </c>
+      <c r="K190" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="191" customHeight="1" spans="3:11">
+      <c r="C191" s="1">
+        <v>40000236</v>
+      </c>
+      <c r="D191" s="1">
+        <v>40000236</v>
+      </c>
+      <c r="E191" s="1">
+        <v>6</v>
+      </c>
+      <c r="F191" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="G191" s="1">
+        <v>2008</v>
+      </c>
+      <c r="H191" s="4">
+        <v>8</v>
+      </c>
+      <c r="I191" s="4">
+        <v>8</v>
+      </c>
+      <c r="J191" s="1">
+        <v>4</v>
+      </c>
+      <c r="K191" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="192" customHeight="1" spans="3:11">
+      <c r="C192" s="1">
+        <v>40000237</v>
+      </c>
+      <c r="D192" s="1">
+        <v>40000237</v>
+      </c>
+      <c r="E192" s="1">
+        <v>6</v>
+      </c>
+      <c r="F192" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="G192" s="1">
+        <v>2009</v>
+      </c>
+      <c r="H192" s="4">
+        <v>8</v>
+      </c>
+      <c r="I192" s="4">
+        <v>8</v>
+      </c>
+      <c r="J192" s="1">
+        <v>4</v>
+      </c>
+      <c r="K192" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="193" customHeight="1" spans="3:11">
+      <c r="C193" s="1">
+        <v>40000238</v>
+      </c>
+      <c r="D193" s="1">
+        <v>40000238</v>
+      </c>
+      <c r="E193" s="1">
+        <v>6</v>
+      </c>
+      <c r="F193" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="G193" s="1">
+        <v>2013</v>
+      </c>
+      <c r="H193" s="1">
+        <v>16</v>
+      </c>
+      <c r="I193" s="1">
+        <v>16</v>
+      </c>
+      <c r="J193" s="1">
+        <v>4</v>
+      </c>
+      <c r="K193" s="1" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="194" customHeight="1" spans="3:11">
+      <c r="C194" s="1">
+        <v>40000239</v>
+      </c>
+      <c r="D194" s="1">
+        <v>40000239</v>
+      </c>
+      <c r="E194" s="1">
+        <v>6</v>
+      </c>
+      <c r="F194" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="G194" s="1">
+        <v>2003</v>
+      </c>
+      <c r="H194" s="1">
+        <v>50</v>
+      </c>
+      <c r="I194" s="1">
+        <v>50</v>
+      </c>
+      <c r="J194" s="1">
+        <v>4</v>
+      </c>
+      <c r="K194" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="195" customHeight="1" spans="3:11">
+      <c r="C195" s="1">
+        <v>40000240</v>
+      </c>
+      <c r="D195" s="1">
+        <v>40000240</v>
+      </c>
+      <c r="E195" s="1">
+        <v>6</v>
+      </c>
+      <c r="F195" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="G195" s="2">
+        <v>2001</v>
+      </c>
+      <c r="H195" s="2">
+        <v>8</v>
+      </c>
+      <c r="I195" s="2">
+        <v>8</v>
+      </c>
+      <c r="J195" s="2">
+        <v>4</v>
+      </c>
+      <c r="K195" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="196" customHeight="1" spans="3:11">
+      <c r="C196" s="1">
+        <v>40000241</v>
+      </c>
+      <c r="D196" s="1">
+        <v>40000241</v>
+      </c>
+      <c r="E196" s="1">
+        <v>6</v>
+      </c>
+      <c r="F196" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="G196" s="4">
+        <v>2004</v>
+      </c>
+      <c r="H196" s="4">
+        <v>8</v>
+      </c>
+      <c r="I196" s="4">
+        <v>8</v>
+      </c>
+      <c r="J196" s="4">
+        <v>4</v>
+      </c>
+      <c r="K196" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="197" customHeight="1" spans="3:11">
+      <c r="C197" s="1">
+        <v>40000242</v>
+      </c>
+      <c r="D197" s="1">
+        <v>40000242</v>
+      </c>
+      <c r="E197" s="1">
+        <v>6</v>
+      </c>
+      <c r="F197" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="G197" s="1">
+        <v>2005</v>
+      </c>
+      <c r="H197" s="4">
+        <v>8</v>
+      </c>
+      <c r="I197" s="4">
+        <v>8</v>
+      </c>
+      <c r="J197" s="1">
+        <v>4</v>
+      </c>
+      <c r="K197" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="198" customHeight="1" spans="3:11">
+      <c r="C198" s="1">
+        <v>40000243</v>
+      </c>
+      <c r="D198" s="1">
+        <v>40000243</v>
+      </c>
+      <c r="E198" s="1">
+        <v>6</v>
+      </c>
+      <c r="F198" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="G198" s="1">
+        <v>2006</v>
+      </c>
+      <c r="H198" s="4">
+        <v>8</v>
+      </c>
+      <c r="I198" s="4">
+        <v>8</v>
+      </c>
+      <c r="J198" s="1">
+        <v>4</v>
+      </c>
+      <c r="K198" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="199" customHeight="1" spans="3:11">
+      <c r="C199" s="1">
+        <v>40000244</v>
+      </c>
+      <c r="D199" s="1">
+        <v>40000244</v>
+      </c>
+      <c r="E199" s="1">
+        <v>6</v>
+      </c>
+      <c r="F199" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="G199" s="1">
+        <v>2010</v>
+      </c>
+      <c r="H199" s="4">
+        <v>8</v>
+      </c>
+      <c r="I199" s="4">
+        <v>8</v>
+      </c>
+      <c r="J199" s="1">
+        <v>4</v>
+      </c>
+      <c r="K199" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="200" customHeight="1" spans="3:11">
+      <c r="H200" s="4"/>
+      <c r="I200" s="4"/>
+    </row>
+    <row r="201" customHeight="1" spans="3:11">
+      <c r="H201" s="4"/>
+      <c r="I201" s="4"/>
+    </row>
+    <row r="202" customHeight="1" spans="3:11">
+      <c r="H202" s="4"/>
+      <c r="I202" s="4"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:F5" errorStyle="warning">

--- a/Excel/HalidomConfig.xlsx
+++ b/Excel/HalidomConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="233">
   <si>
     <t>Id</t>
   </si>
@@ -633,6 +633,9 @@
   </si>
   <si>
     <t>虚无花朵</t>
+  </si>
+  <si>
+    <t>#</t>
   </si>
   <si>
     <t>虚无冰晶</t>
@@ -1688,7 +1691,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:K202"/>
+  <dimension ref="A3:K202"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="5" width="9" style="1"/>
@@ -6281,7 +6284,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="161" customHeight="1" spans="3:11">
+    <row r="161" customHeight="1" spans="1:11">
       <c r="C161" s="1">
         <v>40000206</v>
       </c>
@@ -6310,7 +6313,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="162" customHeight="1" spans="3:11">
+    <row r="162" customHeight="1" spans="1:11">
       <c r="C162" s="1">
         <v>40000207</v>
       </c>
@@ -6339,7 +6342,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="163" customHeight="1" spans="3:11">
+    <row r="163" customHeight="1" spans="1:11">
       <c r="C163" s="1">
         <v>40000208</v>
       </c>
@@ -6368,7 +6371,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="164" customHeight="1" spans="3:11">
+    <row r="164" customHeight="1" spans="1:11">
       <c r="C164" s="1">
         <v>40000209</v>
       </c>
@@ -6397,7 +6400,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="165" customHeight="1" spans="3:11">
+    <row r="165" customHeight="1" spans="1:11">
       <c r="C165" s="1">
         <v>40000210</v>
       </c>
@@ -6426,7 +6429,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="166" customHeight="1" spans="3:11">
+    <row r="166" customHeight="1" spans="1:11">
       <c r="C166" s="1">
         <v>40000211</v>
       </c>
@@ -6455,7 +6458,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="167" customHeight="1" spans="3:11">
+    <row r="167" customHeight="1" spans="1:11">
       <c r="C167" s="1">
         <v>40000212</v>
       </c>
@@ -6484,7 +6487,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="168" customHeight="1" spans="3:11">
+    <row r="168" customHeight="1" spans="1:11">
       <c r="C168" s="1">
         <v>40000213</v>
       </c>
@@ -6513,7 +6516,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="169" customHeight="1" spans="3:11">
+    <row r="169" customHeight="1" spans="1:11">
       <c r="C169" s="1">
         <v>40000214</v>
       </c>
@@ -6542,7 +6545,13 @@
         <v>92</v>
       </c>
     </row>
-    <row r="170" customHeight="1" spans="3:11">
+    <row r="170" customHeight="1" spans="1:11">
+      <c r="A170" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B170" s="1" t="s">
+        <v>202</v>
+      </c>
       <c r="C170" s="1">
         <v>40000215</v>
       </c>
@@ -6553,7 +6562,7 @@
         <v>6</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G170" s="1">
         <v>2007</v>
@@ -6571,7 +6580,13 @@
         <v>132</v>
       </c>
     </row>
-    <row r="171" customHeight="1" spans="3:11">
+    <row r="171" customHeight="1" spans="1:11">
+      <c r="A171" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B171" s="1" t="s">
+        <v>202</v>
+      </c>
       <c r="C171" s="1">
         <v>40000216</v>
       </c>
@@ -6582,7 +6597,7 @@
         <v>6</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="G171" s="1">
         <v>2008</v>
@@ -6600,7 +6615,13 @@
         <v>134</v>
       </c>
     </row>
-    <row r="172" customHeight="1" spans="3:11">
+    <row r="172" customHeight="1" spans="1:11">
+      <c r="A172" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B172" s="1" t="s">
+        <v>202</v>
+      </c>
       <c r="C172" s="1">
         <v>40000217</v>
       </c>
@@ -6611,7 +6632,7 @@
         <v>6</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G172" s="1">
         <v>2009</v>
@@ -6629,7 +6650,13 @@
         <v>136</v>
       </c>
     </row>
-    <row r="173" customHeight="1" spans="3:11">
+    <row r="173" customHeight="1" spans="1:11">
+      <c r="A173" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B173" s="1" t="s">
+        <v>202</v>
+      </c>
       <c r="C173" s="1">
         <v>40000218</v>
       </c>
@@ -6640,7 +6667,7 @@
         <v>6</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G173" s="1">
         <v>2013</v>
@@ -6658,7 +6685,13 @@
         <v>180</v>
       </c>
     </row>
-    <row r="174" customHeight="1" spans="3:11">
+    <row r="174" customHeight="1" spans="1:11">
+      <c r="A174" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B174" s="1" t="s">
+        <v>202</v>
+      </c>
       <c r="C174" s="1">
         <v>40000219</v>
       </c>
@@ -6669,7 +6702,7 @@
         <v>6</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="G174" s="1">
         <v>2003</v>
@@ -6687,7 +6720,13 @@
         <v>17</v>
       </c>
     </row>
-    <row r="175" customHeight="1" spans="3:11">
+    <row r="175" customHeight="1" spans="1:11">
+      <c r="A175" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B175" s="1" t="s">
+        <v>202</v>
+      </c>
       <c r="C175" s="1">
         <v>40000220</v>
       </c>
@@ -6698,7 +6737,7 @@
         <v>6</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G175" s="2">
         <v>2001</v>
@@ -6716,7 +6755,13 @@
         <v>52</v>
       </c>
     </row>
-    <row r="176" customHeight="1" spans="3:11">
+    <row r="176" customHeight="1" spans="1:11">
+      <c r="A176" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B176" s="1" t="s">
+        <v>202</v>
+      </c>
       <c r="C176" s="1">
         <v>40000221</v>
       </c>
@@ -6727,7 +6772,7 @@
         <v>6</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G176" s="4">
         <v>2004</v>
@@ -6745,7 +6790,13 @@
         <v>43</v>
       </c>
     </row>
-    <row r="177" customHeight="1" spans="3:11">
+    <row r="177" customHeight="1" spans="1:11">
+      <c r="A177" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B177" s="1" t="s">
+        <v>202</v>
+      </c>
       <c r="C177" s="1">
         <v>40000222</v>
       </c>
@@ -6756,7 +6807,7 @@
         <v>6</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G177" s="1">
         <v>2005</v>
@@ -6774,7 +6825,13 @@
         <v>123</v>
       </c>
     </row>
-    <row r="178" customHeight="1" spans="3:11">
+    <row r="178" customHeight="1" spans="1:11">
+      <c r="A178" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B178" s="1" t="s">
+        <v>202</v>
+      </c>
       <c r="C178" s="1">
         <v>40000223</v>
       </c>
@@ -6785,7 +6842,7 @@
         <v>6</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G178" s="1">
         <v>2006</v>
@@ -6803,7 +6860,13 @@
         <v>47</v>
       </c>
     </row>
-    <row r="179" customHeight="1" spans="3:11">
+    <row r="179" customHeight="1" spans="1:11">
+      <c r="A179" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B179" s="1" t="s">
+        <v>202</v>
+      </c>
       <c r="C179" s="1">
         <v>40000224</v>
       </c>
@@ -6814,7 +6877,7 @@
         <v>6</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G179" s="1">
         <v>2010</v>
@@ -6832,7 +6895,13 @@
         <v>92</v>
       </c>
     </row>
-    <row r="180" customHeight="1" spans="3:11">
+    <row r="180" customHeight="1" spans="1:11">
+      <c r="A180" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B180" s="1" t="s">
+        <v>202</v>
+      </c>
       <c r="C180" s="1">
         <v>40000225</v>
       </c>
@@ -6843,7 +6912,7 @@
         <v>6</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G180" s="1">
         <v>2007</v>
@@ -6861,7 +6930,13 @@
         <v>132</v>
       </c>
     </row>
-    <row r="181" customHeight="1" spans="3:11">
+    <row r="181" customHeight="1" spans="1:11">
+      <c r="A181" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B181" s="1" t="s">
+        <v>202</v>
+      </c>
       <c r="C181" s="1">
         <v>40000226</v>
       </c>
@@ -6872,7 +6947,7 @@
         <v>6</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G181" s="1">
         <v>2008</v>
@@ -6890,7 +6965,13 @@
         <v>134</v>
       </c>
     </row>
-    <row r="182" customHeight="1" spans="3:11">
+    <row r="182" customHeight="1" spans="1:11">
+      <c r="A182" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B182" s="1" t="s">
+        <v>202</v>
+      </c>
       <c r="C182" s="1">
         <v>40000227</v>
       </c>
@@ -6901,7 +6982,7 @@
         <v>6</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G182" s="1">
         <v>2009</v>
@@ -6919,7 +7000,13 @@
         <v>136</v>
       </c>
     </row>
-    <row r="183" customHeight="1" spans="3:11">
+    <row r="183" customHeight="1" spans="1:11">
+      <c r="A183" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B183" s="1" t="s">
+        <v>202</v>
+      </c>
       <c r="C183" s="1">
         <v>40000228</v>
       </c>
@@ -6930,7 +7017,7 @@
         <v>6</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G183" s="1">
         <v>2013</v>
@@ -6948,7 +7035,13 @@
         <v>180</v>
       </c>
     </row>
-    <row r="184" customHeight="1" spans="3:11">
+    <row r="184" customHeight="1" spans="1:11">
+      <c r="A184" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B184" s="1" t="s">
+        <v>202</v>
+      </c>
       <c r="C184" s="1">
         <v>40000229</v>
       </c>
@@ -6959,7 +7052,7 @@
         <v>6</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G184" s="1">
         <v>2003</v>
@@ -6977,7 +7070,13 @@
         <v>17</v>
       </c>
     </row>
-    <row r="185" customHeight="1" spans="3:11">
+    <row r="185" customHeight="1" spans="1:11">
+      <c r="A185" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B185" s="1" t="s">
+        <v>202</v>
+      </c>
       <c r="C185" s="1">
         <v>40000230</v>
       </c>
@@ -6988,7 +7087,7 @@
         <v>6</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="G185" s="2">
         <v>2001</v>
@@ -7006,7 +7105,13 @@
         <v>52</v>
       </c>
     </row>
-    <row r="186" customHeight="1" spans="3:11">
+    <row r="186" customHeight="1" spans="1:11">
+      <c r="A186" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B186" s="1" t="s">
+        <v>202</v>
+      </c>
       <c r="C186" s="1">
         <v>40000231</v>
       </c>
@@ -7017,7 +7122,7 @@
         <v>6</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G186" s="4">
         <v>2004</v>
@@ -7035,7 +7140,13 @@
         <v>43</v>
       </c>
     </row>
-    <row r="187" customHeight="1" spans="3:11">
+    <row r="187" customHeight="1" spans="1:11">
+      <c r="A187" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B187" s="1" t="s">
+        <v>202</v>
+      </c>
       <c r="C187" s="1">
         <v>40000232</v>
       </c>
@@ -7046,7 +7157,7 @@
         <v>6</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G187" s="1">
         <v>2005</v>
@@ -7064,7 +7175,13 @@
         <v>123</v>
       </c>
     </row>
-    <row r="188" customHeight="1" spans="3:11">
+    <row r="188" customHeight="1" spans="1:11">
+      <c r="A188" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B188" s="1" t="s">
+        <v>202</v>
+      </c>
       <c r="C188" s="1">
         <v>40000233</v>
       </c>
@@ -7075,7 +7192,7 @@
         <v>6</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="G188" s="1">
         <v>2006</v>
@@ -7093,7 +7210,13 @@
         <v>47</v>
       </c>
     </row>
-    <row r="189" customHeight="1" spans="3:11">
+    <row r="189" customHeight="1" spans="1:11">
+      <c r="A189" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B189" s="1" t="s">
+        <v>202</v>
+      </c>
       <c r="C189" s="1">
         <v>40000234</v>
       </c>
@@ -7104,7 +7227,7 @@
         <v>6</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="G189" s="1">
         <v>2010</v>
@@ -7122,7 +7245,13 @@
         <v>92</v>
       </c>
     </row>
-    <row r="190" customHeight="1" spans="3:11">
+    <row r="190" customHeight="1" spans="1:11">
+      <c r="A190" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B190" s="1" t="s">
+        <v>202</v>
+      </c>
       <c r="C190" s="1">
         <v>40000235</v>
       </c>
@@ -7133,7 +7262,7 @@
         <v>6</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="G190" s="1">
         <v>2007</v>
@@ -7151,7 +7280,13 @@
         <v>132</v>
       </c>
     </row>
-    <row r="191" customHeight="1" spans="3:11">
+    <row r="191" customHeight="1" spans="1:11">
+      <c r="A191" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B191" s="1" t="s">
+        <v>202</v>
+      </c>
       <c r="C191" s="1">
         <v>40000236</v>
       </c>
@@ -7162,7 +7297,7 @@
         <v>6</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="G191" s="1">
         <v>2008</v>
@@ -7180,7 +7315,13 @@
         <v>134</v>
       </c>
     </row>
-    <row r="192" customHeight="1" spans="3:11">
+    <row r="192" customHeight="1" spans="1:11">
+      <c r="A192" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B192" s="1" t="s">
+        <v>202</v>
+      </c>
       <c r="C192" s="1">
         <v>40000237</v>
       </c>
@@ -7191,7 +7332,7 @@
         <v>6</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G192" s="1">
         <v>2009</v>
@@ -7209,7 +7350,13 @@
         <v>136</v>
       </c>
     </row>
-    <row r="193" customHeight="1" spans="3:11">
+    <row r="193" customHeight="1" spans="1:11">
+      <c r="A193" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B193" s="1" t="s">
+        <v>202</v>
+      </c>
       <c r="C193" s="1">
         <v>40000238</v>
       </c>
@@ -7220,7 +7367,7 @@
         <v>6</v>
       </c>
       <c r="F193" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G193" s="1">
         <v>2013</v>
@@ -7238,7 +7385,13 @@
         <v>180</v>
       </c>
     </row>
-    <row r="194" customHeight="1" spans="3:11">
+    <row r="194" customHeight="1" spans="1:11">
+      <c r="A194" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B194" s="1" t="s">
+        <v>202</v>
+      </c>
       <c r="C194" s="1">
         <v>40000239</v>
       </c>
@@ -7249,7 +7402,7 @@
         <v>6</v>
       </c>
       <c r="F194" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="G194" s="1">
         <v>2003</v>
@@ -7267,7 +7420,13 @@
         <v>17</v>
       </c>
     </row>
-    <row r="195" customHeight="1" spans="3:11">
+    <row r="195" customHeight="1" spans="1:11">
+      <c r="A195" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B195" s="1" t="s">
+        <v>202</v>
+      </c>
       <c r="C195" s="1">
         <v>40000240</v>
       </c>
@@ -7278,7 +7437,7 @@
         <v>6</v>
       </c>
       <c r="F195" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="G195" s="2">
         <v>2001</v>
@@ -7296,7 +7455,13 @@
         <v>52</v>
       </c>
     </row>
-    <row r="196" customHeight="1" spans="3:11">
+    <row r="196" customHeight="1" spans="1:11">
+      <c r="A196" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B196" s="1" t="s">
+        <v>202</v>
+      </c>
       <c r="C196" s="1">
         <v>40000241</v>
       </c>
@@ -7307,7 +7472,7 @@
         <v>6</v>
       </c>
       <c r="F196" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="G196" s="4">
         <v>2004</v>
@@ -7325,7 +7490,13 @@
         <v>43</v>
       </c>
     </row>
-    <row r="197" customHeight="1" spans="3:11">
+    <row r="197" customHeight="1" spans="1:11">
+      <c r="A197" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B197" s="1" t="s">
+        <v>202</v>
+      </c>
       <c r="C197" s="1">
         <v>40000242</v>
       </c>
@@ -7336,7 +7507,7 @@
         <v>6</v>
       </c>
       <c r="F197" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G197" s="1">
         <v>2005</v>
@@ -7354,7 +7525,13 @@
         <v>123</v>
       </c>
     </row>
-    <row r="198" customHeight="1" spans="3:11">
+    <row r="198" customHeight="1" spans="1:11">
+      <c r="A198" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B198" s="1" t="s">
+        <v>202</v>
+      </c>
       <c r="C198" s="1">
         <v>40000243</v>
       </c>
@@ -7365,7 +7542,7 @@
         <v>6</v>
       </c>
       <c r="F198" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G198" s="1">
         <v>2006</v>
@@ -7383,7 +7560,13 @@
         <v>47</v>
       </c>
     </row>
-    <row r="199" customHeight="1" spans="3:11">
+    <row r="199" customHeight="1" spans="1:11">
+      <c r="A199" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B199" s="1" t="s">
+        <v>202</v>
+      </c>
       <c r="C199" s="1">
         <v>40000244</v>
       </c>
@@ -7394,7 +7577,7 @@
         <v>6</v>
       </c>
       <c r="F199" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="G199" s="1">
         <v>2010</v>
@@ -7412,15 +7595,15 @@
         <v>92</v>
       </c>
     </row>
-    <row r="200" customHeight="1" spans="3:11">
+    <row r="200" customHeight="1" spans="1:11">
       <c r="H200" s="4"/>
       <c r="I200" s="4"/>
     </row>
-    <row r="201" customHeight="1" spans="3:11">
+    <row r="201" customHeight="1" spans="1:11">
       <c r="H201" s="4"/>
       <c r="I201" s="4"/>
     </row>
-    <row r="202" customHeight="1" spans="3:11">
+    <row r="202" customHeight="1" spans="1:11">
       <c r="H202" s="4"/>
       <c r="I202" s="4"/>
     </row>

--- a/Excel/HalidomConfig.xlsx
+++ b/Excel/HalidomConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="233">
   <si>
     <t>Id</t>
   </si>
@@ -635,22 +635,22 @@
     <t>虚无花朵</t>
   </si>
   <si>
+    <t>虚无冰晶</t>
+  </si>
+  <si>
+    <t>虚无蝠翼</t>
+  </si>
+  <si>
+    <t>虚无魂火</t>
+  </si>
+  <si>
+    <t>虚无腐肉</t>
+  </si>
+  <si>
+    <t>虚无蛇胆</t>
+  </si>
+  <si>
     <t>#</t>
-  </si>
-  <si>
-    <t>虚无冰晶</t>
-  </si>
-  <si>
-    <t>虚无蝠翼</t>
-  </si>
-  <si>
-    <t>虚无魂火</t>
-  </si>
-  <si>
-    <t>虚无腐肉</t>
-  </si>
-  <si>
-    <t>虚无蛇胆</t>
   </si>
   <si>
     <t>虚无狼爪</t>
@@ -6546,12 +6546,6 @@
       </c>
     </row>
     <row r="170" customHeight="1" spans="1:11">
-      <c r="A170" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="B170" s="1" t="s">
-        <v>202</v>
-      </c>
       <c r="C170" s="1">
         <v>40000215</v>
       </c>
@@ -6562,7 +6556,7 @@
         <v>6</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G170" s="1">
         <v>2007</v>
@@ -6581,12 +6575,6 @@
       </c>
     </row>
     <row r="171" customHeight="1" spans="1:11">
-      <c r="A171" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="B171" s="1" t="s">
-        <v>202</v>
-      </c>
       <c r="C171" s="1">
         <v>40000216</v>
       </c>
@@ -6597,7 +6585,7 @@
         <v>6</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G171" s="1">
         <v>2008</v>
@@ -6616,12 +6604,6 @@
       </c>
     </row>
     <row r="172" customHeight="1" spans="1:11">
-      <c r="A172" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="B172" s="1" t="s">
-        <v>202</v>
-      </c>
       <c r="C172" s="1">
         <v>40000217</v>
       </c>
@@ -6632,7 +6614,7 @@
         <v>6</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G172" s="1">
         <v>2009</v>
@@ -6651,12 +6633,6 @@
       </c>
     </row>
     <row r="173" customHeight="1" spans="1:11">
-      <c r="A173" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="B173" s="1" t="s">
-        <v>202</v>
-      </c>
       <c r="C173" s="1">
         <v>40000218</v>
       </c>
@@ -6667,7 +6643,7 @@
         <v>6</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G173" s="1">
         <v>2013</v>
@@ -6686,12 +6662,6 @@
       </c>
     </row>
     <row r="174" customHeight="1" spans="1:11">
-      <c r="A174" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="B174" s="1" t="s">
-        <v>202</v>
-      </c>
       <c r="C174" s="1">
         <v>40000219</v>
       </c>
@@ -6702,7 +6672,7 @@
         <v>6</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="G174" s="1">
         <v>2003</v>
@@ -6722,10 +6692,10 @@
     </row>
     <row r="175" customHeight="1" spans="1:11">
       <c r="A175" s="1" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="C175" s="1">
         <v>40000220</v>
@@ -6757,10 +6727,10 @@
     </row>
     <row r="176" customHeight="1" spans="1:11">
       <c r="A176" s="1" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="C176" s="1">
         <v>40000221</v>
@@ -6792,10 +6762,10 @@
     </row>
     <row r="177" customHeight="1" spans="1:11">
       <c r="A177" s="1" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="C177" s="1">
         <v>40000222</v>
@@ -6827,10 +6797,10 @@
     </row>
     <row r="178" customHeight="1" spans="1:11">
       <c r="A178" s="1" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="C178" s="1">
         <v>40000223</v>
@@ -6862,10 +6832,10 @@
     </row>
     <row r="179" customHeight="1" spans="1:11">
       <c r="A179" s="1" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="C179" s="1">
         <v>40000224</v>
@@ -6897,10 +6867,10 @@
     </row>
     <row r="180" customHeight="1" spans="1:11">
       <c r="A180" s="1" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="C180" s="1">
         <v>40000225</v>
@@ -6932,10 +6902,10 @@
     </row>
     <row r="181" customHeight="1" spans="1:11">
       <c r="A181" s="1" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="C181" s="1">
         <v>40000226</v>
@@ -6967,10 +6937,10 @@
     </row>
     <row r="182" customHeight="1" spans="1:11">
       <c r="A182" s="1" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="C182" s="1">
         <v>40000227</v>
@@ -7002,10 +6972,10 @@
     </row>
     <row r="183" customHeight="1" spans="1:11">
       <c r="A183" s="1" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="C183" s="1">
         <v>40000228</v>
@@ -7037,10 +7007,10 @@
     </row>
     <row r="184" customHeight="1" spans="1:11">
       <c r="A184" s="1" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="C184" s="1">
         <v>40000229</v>
@@ -7072,10 +7042,10 @@
     </row>
     <row r="185" customHeight="1" spans="1:11">
       <c r="A185" s="1" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="C185" s="1">
         <v>40000230</v>
@@ -7107,10 +7077,10 @@
     </row>
     <row r="186" customHeight="1" spans="1:11">
       <c r="A186" s="1" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="C186" s="1">
         <v>40000231</v>
@@ -7142,10 +7112,10 @@
     </row>
     <row r="187" customHeight="1" spans="1:11">
       <c r="A187" s="1" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="C187" s="1">
         <v>40000232</v>
@@ -7177,10 +7147,10 @@
     </row>
     <row r="188" customHeight="1" spans="1:11">
       <c r="A188" s="1" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="C188" s="1">
         <v>40000233</v>
@@ -7212,10 +7182,10 @@
     </row>
     <row r="189" customHeight="1" spans="1:11">
       <c r="A189" s="1" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="C189" s="1">
         <v>40000234</v>
@@ -7247,10 +7217,10 @@
     </row>
     <row r="190" customHeight="1" spans="1:11">
       <c r="A190" s="1" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="C190" s="1">
         <v>40000235</v>
@@ -7282,10 +7252,10 @@
     </row>
     <row r="191" customHeight="1" spans="1:11">
       <c r="A191" s="1" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="C191" s="1">
         <v>40000236</v>
@@ -7317,10 +7287,10 @@
     </row>
     <row r="192" customHeight="1" spans="1:11">
       <c r="A192" s="1" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="C192" s="1">
         <v>40000237</v>
@@ -7352,10 +7322,10 @@
     </row>
     <row r="193" customHeight="1" spans="1:11">
       <c r="A193" s="1" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="C193" s="1">
         <v>40000238</v>
@@ -7387,10 +7357,10 @@
     </row>
     <row r="194" customHeight="1" spans="1:11">
       <c r="A194" s="1" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="C194" s="1">
         <v>40000239</v>
@@ -7422,10 +7392,10 @@
     </row>
     <row r="195" customHeight="1" spans="1:11">
       <c r="A195" s="1" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="C195" s="1">
         <v>40000240</v>
@@ -7457,10 +7427,10 @@
     </row>
     <row r="196" customHeight="1" spans="1:11">
       <c r="A196" s="1" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="C196" s="1">
         <v>40000241</v>
@@ -7492,10 +7462,10 @@
     </row>
     <row r="197" customHeight="1" spans="1:11">
       <c r="A197" s="1" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="C197" s="1">
         <v>40000242</v>
@@ -7527,10 +7497,10 @@
     </row>
     <row r="198" customHeight="1" spans="1:11">
       <c r="A198" s="1" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="C198" s="1">
         <v>40000243</v>
@@ -7562,10 +7532,10 @@
     </row>
     <row r="199" customHeight="1" spans="1:11">
       <c r="A199" s="1" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="C199" s="1">
         <v>40000244</v>

--- a/Excel/HalidomConfig.xlsx
+++ b/Excel/HalidomConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="233">
   <si>
     <t>Id</t>
   </si>
@@ -650,22 +650,22 @@
     <t>虚无蛇胆</t>
   </si>
   <si>
+    <t>虚无狼爪</t>
+  </si>
+  <si>
+    <t>虚无虫皮</t>
+  </si>
+  <si>
+    <t>虚无鹰羽</t>
+  </si>
+  <si>
+    <t>虚无虫角</t>
+  </si>
+  <si>
+    <t>虚无蜈膏</t>
+  </si>
+  <si>
     <t>#</t>
-  </si>
-  <si>
-    <t>虚无狼爪</t>
-  </si>
-  <si>
-    <t>虚无虫皮</t>
-  </si>
-  <si>
-    <t>虚无鹰羽</t>
-  </si>
-  <si>
-    <t>虚无虫角</t>
-  </si>
-  <si>
-    <t>虚无蜈膏</t>
   </si>
   <si>
     <t>虚无虫心</t>
@@ -6284,7 +6284,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="161" customHeight="1" spans="1:11">
+    <row r="161" customHeight="1" spans="3:11">
       <c r="C161" s="1">
         <v>40000206</v>
       </c>
@@ -6313,7 +6313,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="162" customHeight="1" spans="1:11">
+    <row r="162" customHeight="1" spans="3:11">
       <c r="C162" s="1">
         <v>40000207</v>
       </c>
@@ -6342,7 +6342,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="163" customHeight="1" spans="1:11">
+    <row r="163" customHeight="1" spans="3:11">
       <c r="C163" s="1">
         <v>40000208</v>
       </c>
@@ -6371,7 +6371,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="164" customHeight="1" spans="1:11">
+    <row r="164" customHeight="1" spans="3:11">
       <c r="C164" s="1">
         <v>40000209</v>
       </c>
@@ -6400,7 +6400,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="165" customHeight="1" spans="1:11">
+    <row r="165" customHeight="1" spans="3:11">
       <c r="C165" s="1">
         <v>40000210</v>
       </c>
@@ -6429,7 +6429,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="166" customHeight="1" spans="1:11">
+    <row r="166" customHeight="1" spans="3:11">
       <c r="C166" s="1">
         <v>40000211</v>
       </c>
@@ -6458,7 +6458,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="167" customHeight="1" spans="1:11">
+    <row r="167" customHeight="1" spans="3:11">
       <c r="C167" s="1">
         <v>40000212</v>
       </c>
@@ -6487,7 +6487,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="168" customHeight="1" spans="1:11">
+    <row r="168" customHeight="1" spans="3:11">
       <c r="C168" s="1">
         <v>40000213</v>
       </c>
@@ -6516,7 +6516,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="169" customHeight="1" spans="1:11">
+    <row r="169" customHeight="1" spans="3:11">
       <c r="C169" s="1">
         <v>40000214</v>
       </c>
@@ -6545,7 +6545,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="170" customHeight="1" spans="1:11">
+    <row r="170" customHeight="1" spans="3:11">
       <c r="C170" s="1">
         <v>40000215</v>
       </c>
@@ -6574,7 +6574,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="171" customHeight="1" spans="1:11">
+    <row r="171" customHeight="1" spans="3:11">
       <c r="C171" s="1">
         <v>40000216</v>
       </c>
@@ -6603,7 +6603,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="172" customHeight="1" spans="1:11">
+    <row r="172" customHeight="1" spans="3:11">
       <c r="C172" s="1">
         <v>40000217</v>
       </c>
@@ -6632,7 +6632,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="173" customHeight="1" spans="1:11">
+    <row r="173" customHeight="1" spans="3:11">
       <c r="C173" s="1">
         <v>40000218</v>
       </c>
@@ -6661,7 +6661,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="174" customHeight="1" spans="1:11">
+    <row r="174" customHeight="1" spans="3:11">
       <c r="C174" s="1">
         <v>40000219</v>
       </c>
@@ -6690,13 +6690,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="175" customHeight="1" spans="1:11">
-      <c r="A175" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="B175" s="1" t="s">
-        <v>207</v>
-      </c>
+    <row r="175" customHeight="1" spans="3:11">
       <c r="C175" s="1">
         <v>40000220</v>
       </c>
@@ -6707,7 +6701,7 @@
         <v>6</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G175" s="2">
         <v>2001</v>
@@ -6725,13 +6719,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="176" customHeight="1" spans="1:11">
-      <c r="A176" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="B176" s="1" t="s">
-        <v>207</v>
-      </c>
+    <row r="176" customHeight="1" spans="3:11">
       <c r="C176" s="1">
         <v>40000221</v>
       </c>
@@ -6742,7 +6730,7 @@
         <v>6</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G176" s="4">
         <v>2004</v>
@@ -6761,12 +6749,6 @@
       </c>
     </row>
     <row r="177" customHeight="1" spans="1:11">
-      <c r="A177" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="B177" s="1" t="s">
-        <v>207</v>
-      </c>
       <c r="C177" s="1">
         <v>40000222</v>
       </c>
@@ -6777,7 +6759,7 @@
         <v>6</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G177" s="1">
         <v>2005</v>
@@ -6796,12 +6778,6 @@
       </c>
     </row>
     <row r="178" customHeight="1" spans="1:11">
-      <c r="A178" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="B178" s="1" t="s">
-        <v>207</v>
-      </c>
       <c r="C178" s="1">
         <v>40000223</v>
       </c>
@@ -6812,7 +6788,7 @@
         <v>6</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G178" s="1">
         <v>2006</v>
@@ -6831,12 +6807,6 @@
       </c>
     </row>
     <row r="179" customHeight="1" spans="1:11">
-      <c r="A179" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="B179" s="1" t="s">
-        <v>207</v>
-      </c>
       <c r="C179" s="1">
         <v>40000224</v>
       </c>
@@ -6847,7 +6817,7 @@
         <v>6</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G179" s="1">
         <v>2010</v>
@@ -6867,10 +6837,10 @@
     </row>
     <row r="180" customHeight="1" spans="1:11">
       <c r="A180" s="1" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="C180" s="1">
         <v>40000225</v>
@@ -6902,10 +6872,10 @@
     </row>
     <row r="181" customHeight="1" spans="1:11">
       <c r="A181" s="1" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="C181" s="1">
         <v>40000226</v>
@@ -6937,10 +6907,10 @@
     </row>
     <row r="182" customHeight="1" spans="1:11">
       <c r="A182" s="1" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="C182" s="1">
         <v>40000227</v>
@@ -6972,10 +6942,10 @@
     </row>
     <row r="183" customHeight="1" spans="1:11">
       <c r="A183" s="1" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="C183" s="1">
         <v>40000228</v>
@@ -7007,10 +6977,10 @@
     </row>
     <row r="184" customHeight="1" spans="1:11">
       <c r="A184" s="1" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="C184" s="1">
         <v>40000229</v>
@@ -7042,10 +7012,10 @@
     </row>
     <row r="185" customHeight="1" spans="1:11">
       <c r="A185" s="1" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="C185" s="1">
         <v>40000230</v>
@@ -7077,10 +7047,10 @@
     </row>
     <row r="186" customHeight="1" spans="1:11">
       <c r="A186" s="1" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="C186" s="1">
         <v>40000231</v>
@@ -7112,10 +7082,10 @@
     </row>
     <row r="187" customHeight="1" spans="1:11">
       <c r="A187" s="1" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="C187" s="1">
         <v>40000232</v>
@@ -7147,10 +7117,10 @@
     </row>
     <row r="188" customHeight="1" spans="1:11">
       <c r="A188" s="1" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="C188" s="1">
         <v>40000233</v>
@@ -7182,10 +7152,10 @@
     </row>
     <row r="189" customHeight="1" spans="1:11">
       <c r="A189" s="1" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="C189" s="1">
         <v>40000234</v>
@@ -7217,10 +7187,10 @@
     </row>
     <row r="190" customHeight="1" spans="1:11">
       <c r="A190" s="1" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="C190" s="1">
         <v>40000235</v>
@@ -7252,10 +7222,10 @@
     </row>
     <row r="191" customHeight="1" spans="1:11">
       <c r="A191" s="1" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="C191" s="1">
         <v>40000236</v>
@@ -7287,10 +7257,10 @@
     </row>
     <row r="192" customHeight="1" spans="1:11">
       <c r="A192" s="1" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="C192" s="1">
         <v>40000237</v>
@@ -7322,10 +7292,10 @@
     </row>
     <row r="193" customHeight="1" spans="1:11">
       <c r="A193" s="1" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="C193" s="1">
         <v>40000238</v>
@@ -7357,10 +7327,10 @@
     </row>
     <row r="194" customHeight="1" spans="1:11">
       <c r="A194" s="1" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="C194" s="1">
         <v>40000239</v>
@@ -7392,10 +7362,10 @@
     </row>
     <row r="195" customHeight="1" spans="1:11">
       <c r="A195" s="1" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="C195" s="1">
         <v>40000240</v>
@@ -7427,10 +7397,10 @@
     </row>
     <row r="196" customHeight="1" spans="1:11">
       <c r="A196" s="1" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="C196" s="1">
         <v>40000241</v>
@@ -7462,10 +7432,10 @@
     </row>
     <row r="197" customHeight="1" spans="1:11">
       <c r="A197" s="1" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="C197" s="1">
         <v>40000242</v>
@@ -7497,10 +7467,10 @@
     </row>
     <row r="198" customHeight="1" spans="1:11">
       <c r="A198" s="1" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="C198" s="1">
         <v>40000243</v>
@@ -7532,10 +7502,10 @@
     </row>
     <row r="199" customHeight="1" spans="1:11">
       <c r="A199" s="1" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="C199" s="1">
         <v>40000244</v>

--- a/Excel/HalidomConfig.xlsx
+++ b/Excel/HalidomConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="233">
   <si>
     <t>Id</t>
   </si>
@@ -665,22 +665,22 @@
     <t>虚无蜈膏</t>
   </si>
   <si>
+    <t>虚无虫心</t>
+  </si>
+  <si>
+    <t>虚无龙皮</t>
+  </si>
+  <si>
+    <t>虚无猪皮</t>
+  </si>
+  <si>
+    <t>虚无猪心</t>
+  </si>
+  <si>
+    <t>虚无蝎皮</t>
+  </si>
+  <si>
     <t>#</t>
-  </si>
-  <si>
-    <t>虚无虫心</t>
-  </si>
-  <si>
-    <t>虚无龙皮</t>
-  </si>
-  <si>
-    <t>虚无猪皮</t>
-  </si>
-  <si>
-    <t>虚无猪心</t>
-  </si>
-  <si>
-    <t>虚无蝎皮</t>
   </si>
   <si>
     <t>虚无宝甲</t>
@@ -6836,12 +6836,6 @@
       </c>
     </row>
     <row r="180" customHeight="1" spans="1:11">
-      <c r="A180" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="B180" s="1" t="s">
-        <v>212</v>
-      </c>
       <c r="C180" s="1">
         <v>40000225</v>
       </c>
@@ -6852,7 +6846,7 @@
         <v>6</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G180" s="1">
         <v>2007</v>
@@ -6871,12 +6865,6 @@
       </c>
     </row>
     <row r="181" customHeight="1" spans="1:11">
-      <c r="A181" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="B181" s="1" t="s">
-        <v>212</v>
-      </c>
       <c r="C181" s="1">
         <v>40000226</v>
       </c>
@@ -6887,7 +6875,7 @@
         <v>6</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="G181" s="1">
         <v>2008</v>
@@ -6906,12 +6894,6 @@
       </c>
     </row>
     <row r="182" customHeight="1" spans="1:11">
-      <c r="A182" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="B182" s="1" t="s">
-        <v>212</v>
-      </c>
       <c r="C182" s="1">
         <v>40000227</v>
       </c>
@@ -6922,7 +6904,7 @@
         <v>6</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G182" s="1">
         <v>2009</v>
@@ -6941,12 +6923,6 @@
       </c>
     </row>
     <row r="183" customHeight="1" spans="1:11">
-      <c r="A183" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="B183" s="1" t="s">
-        <v>212</v>
-      </c>
       <c r="C183" s="1">
         <v>40000228</v>
       </c>
@@ -6957,7 +6933,7 @@
         <v>6</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G183" s="1">
         <v>2013</v>
@@ -6976,12 +6952,6 @@
       </c>
     </row>
     <row r="184" customHeight="1" spans="1:11">
-      <c r="A184" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="B184" s="1" t="s">
-        <v>212</v>
-      </c>
       <c r="C184" s="1">
         <v>40000229</v>
       </c>
@@ -6992,7 +6962,7 @@
         <v>6</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G184" s="1">
         <v>2003</v>
@@ -7012,10 +6982,10 @@
     </row>
     <row r="185" customHeight="1" spans="1:11">
       <c r="A185" s="1" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="C185" s="1">
         <v>40000230</v>
@@ -7047,10 +7017,10 @@
     </row>
     <row r="186" customHeight="1" spans="1:11">
       <c r="A186" s="1" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="C186" s="1">
         <v>40000231</v>
@@ -7082,10 +7052,10 @@
     </row>
     <row r="187" customHeight="1" spans="1:11">
       <c r="A187" s="1" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="C187" s="1">
         <v>40000232</v>
@@ -7117,10 +7087,10 @@
     </row>
     <row r="188" customHeight="1" spans="1:11">
       <c r="A188" s="1" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="C188" s="1">
         <v>40000233</v>
@@ -7152,10 +7122,10 @@
     </row>
     <row r="189" customHeight="1" spans="1:11">
       <c r="A189" s="1" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="C189" s="1">
         <v>40000234</v>
@@ -7187,10 +7157,10 @@
     </row>
     <row r="190" customHeight="1" spans="1:11">
       <c r="A190" s="1" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="C190" s="1">
         <v>40000235</v>
@@ -7222,10 +7192,10 @@
     </row>
     <row r="191" customHeight="1" spans="1:11">
       <c r="A191" s="1" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="C191" s="1">
         <v>40000236</v>
@@ -7257,10 +7227,10 @@
     </row>
     <row r="192" customHeight="1" spans="1:11">
       <c r="A192" s="1" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="C192" s="1">
         <v>40000237</v>
@@ -7292,10 +7262,10 @@
     </row>
     <row r="193" customHeight="1" spans="1:11">
       <c r="A193" s="1" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="C193" s="1">
         <v>40000238</v>
@@ -7327,10 +7297,10 @@
     </row>
     <row r="194" customHeight="1" spans="1:11">
       <c r="A194" s="1" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="C194" s="1">
         <v>40000239</v>
@@ -7362,10 +7332,10 @@
     </row>
     <row r="195" customHeight="1" spans="1:11">
       <c r="A195" s="1" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="C195" s="1">
         <v>40000240</v>
@@ -7397,10 +7367,10 @@
     </row>
     <row r="196" customHeight="1" spans="1:11">
       <c r="A196" s="1" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="C196" s="1">
         <v>40000241</v>
@@ -7432,10 +7402,10 @@
     </row>
     <row r="197" customHeight="1" spans="1:11">
       <c r="A197" s="1" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="C197" s="1">
         <v>40000242</v>
@@ -7467,10 +7437,10 @@
     </row>
     <row r="198" customHeight="1" spans="1:11">
       <c r="A198" s="1" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="C198" s="1">
         <v>40000243</v>
@@ -7502,10 +7472,10 @@
     </row>
     <row r="199" customHeight="1" spans="1:11">
       <c r="A199" s="1" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="C199" s="1">
         <v>40000244</v>

--- a/Excel/HalidomConfig.xlsx
+++ b/Excel/HalidomConfig.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WrittenLegend\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowHeight="17680"/>
   </bookViews>
@@ -27,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="233">
   <si>
     <t>Id</t>
   </si>
@@ -680,22 +685,22 @@
     <t>虚无蝎皮</t>
   </si>
   <si>
+    <t>虚无宝甲</t>
+  </si>
+  <si>
+    <t>虚无号角</t>
+  </si>
+  <si>
+    <t>虚无雕像</t>
+  </si>
+  <si>
+    <t>虚无神像</t>
+  </si>
+  <si>
+    <t>虚无獠牙</t>
+  </si>
+  <si>
     <t>#</t>
-  </si>
-  <si>
-    <t>虚无宝甲</t>
-  </si>
-  <si>
-    <t>虚无号角</t>
-  </si>
-  <si>
-    <t>虚无雕像</t>
-  </si>
-  <si>
-    <t>虚无神像</t>
-  </si>
-  <si>
-    <t>虚无獠牙</t>
   </si>
   <si>
     <t>虚无树心</t>
@@ -6981,12 +6986,6 @@
       </c>
     </row>
     <row r="185" customHeight="1" spans="1:11">
-      <c r="A185" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="B185" s="1" t="s">
-        <v>217</v>
-      </c>
       <c r="C185" s="1">
         <v>40000230</v>
       </c>
@@ -6997,7 +6996,7 @@
         <v>6</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="G185" s="2">
         <v>2001</v>
@@ -7016,12 +7015,6 @@
       </c>
     </row>
     <row r="186" customHeight="1" spans="1:11">
-      <c r="A186" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="B186" s="1" t="s">
-        <v>217</v>
-      </c>
       <c r="C186" s="1">
         <v>40000231</v>
       </c>
@@ -7032,7 +7025,7 @@
         <v>6</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G186" s="4">
         <v>2004</v>
@@ -7051,12 +7044,6 @@
       </c>
     </row>
     <row r="187" customHeight="1" spans="1:11">
-      <c r="A187" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="B187" s="1" t="s">
-        <v>217</v>
-      </c>
       <c r="C187" s="1">
         <v>40000232</v>
       </c>
@@ -7067,7 +7054,7 @@
         <v>6</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G187" s="1">
         <v>2005</v>
@@ -7086,12 +7073,6 @@
       </c>
     </row>
     <row r="188" customHeight="1" spans="1:11">
-      <c r="A188" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="B188" s="1" t="s">
-        <v>217</v>
-      </c>
       <c r="C188" s="1">
         <v>40000233</v>
       </c>
@@ -7102,7 +7083,7 @@
         <v>6</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="G188" s="1">
         <v>2006</v>
@@ -7121,12 +7102,6 @@
       </c>
     </row>
     <row r="189" customHeight="1" spans="1:11">
-      <c r="A189" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="B189" s="1" t="s">
-        <v>217</v>
-      </c>
       <c r="C189" s="1">
         <v>40000234</v>
       </c>
@@ -7137,7 +7112,7 @@
         <v>6</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G189" s="1">
         <v>2010</v>
@@ -7157,10 +7132,10 @@
     </row>
     <row r="190" customHeight="1" spans="1:11">
       <c r="A190" s="1" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="C190" s="1">
         <v>40000235</v>
@@ -7192,10 +7167,10 @@
     </row>
     <row r="191" customHeight="1" spans="1:11">
       <c r="A191" s="1" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="C191" s="1">
         <v>40000236</v>
@@ -7227,10 +7202,10 @@
     </row>
     <row r="192" customHeight="1" spans="1:11">
       <c r="A192" s="1" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="C192" s="1">
         <v>40000237</v>
@@ -7262,10 +7237,10 @@
     </row>
     <row r="193" customHeight="1" spans="1:11">
       <c r="A193" s="1" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="C193" s="1">
         <v>40000238</v>
@@ -7297,10 +7272,10 @@
     </row>
     <row r="194" customHeight="1" spans="1:11">
       <c r="A194" s="1" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="C194" s="1">
         <v>40000239</v>
@@ -7332,10 +7307,10 @@
     </row>
     <row r="195" customHeight="1" spans="1:11">
       <c r="A195" s="1" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="C195" s="1">
         <v>40000240</v>
@@ -7367,10 +7342,10 @@
     </row>
     <row r="196" customHeight="1" spans="1:11">
       <c r="A196" s="1" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="C196" s="1">
         <v>40000241</v>
@@ -7402,10 +7377,10 @@
     </row>
     <row r="197" customHeight="1" spans="1:11">
       <c r="A197" s="1" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="C197" s="1">
         <v>40000242</v>
@@ -7437,10 +7412,10 @@
     </row>
     <row r="198" customHeight="1" spans="1:11">
       <c r="A198" s="1" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="C198" s="1">
         <v>40000243</v>
@@ -7472,10 +7447,10 @@
     </row>
     <row r="199" customHeight="1" spans="1:11">
       <c r="A199" s="1" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="C199" s="1">
         <v>40000244</v>

--- a/Excel/HalidomConfig.xlsx
+++ b/Excel/HalidomConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="233">
   <si>
     <t>Id</t>
   </si>
@@ -700,22 +700,22 @@
     <t>虚无獠牙</t>
   </si>
   <si>
+    <t>虚无树心</t>
+  </si>
+  <si>
+    <t>虚无魔心</t>
+  </si>
+  <si>
+    <t>虚无尸心</t>
+  </si>
+  <si>
+    <t>虚无法杖</t>
+  </si>
+  <si>
+    <t>虚无权杖</t>
+  </si>
+  <si>
     <t>#</t>
-  </si>
-  <si>
-    <t>虚无树心</t>
-  </si>
-  <si>
-    <t>虚无魔心</t>
-  </si>
-  <si>
-    <t>虚无尸心</t>
-  </si>
-  <si>
-    <t>虚无法杖</t>
-  </si>
-  <si>
-    <t>虚无权杖</t>
   </si>
   <si>
     <t>虚无战锤</t>
@@ -6753,7 +6753,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="177" customHeight="1" spans="1:11">
+    <row r="177" customHeight="1" spans="3:11">
       <c r="C177" s="1">
         <v>40000222</v>
       </c>
@@ -6782,7 +6782,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="178" customHeight="1" spans="1:11">
+    <row r="178" customHeight="1" spans="3:11">
       <c r="C178" s="1">
         <v>40000223</v>
       </c>
@@ -6811,7 +6811,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="179" customHeight="1" spans="1:11">
+    <row r="179" customHeight="1" spans="3:11">
       <c r="C179" s="1">
         <v>40000224</v>
       </c>
@@ -6840,7 +6840,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="180" customHeight="1" spans="1:11">
+    <row r="180" customHeight="1" spans="3:11">
       <c r="C180" s="1">
         <v>40000225</v>
       </c>
@@ -6869,7 +6869,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="181" customHeight="1" spans="1:11">
+    <row r="181" customHeight="1" spans="3:11">
       <c r="C181" s="1">
         <v>40000226</v>
       </c>
@@ -6898,7 +6898,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="182" customHeight="1" spans="1:11">
+    <row r="182" customHeight="1" spans="3:11">
       <c r="C182" s="1">
         <v>40000227</v>
       </c>
@@ -6927,7 +6927,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="183" customHeight="1" spans="1:11">
+    <row r="183" customHeight="1" spans="3:11">
       <c r="C183" s="1">
         <v>40000228</v>
       </c>
@@ -6956,7 +6956,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="184" customHeight="1" spans="1:11">
+    <row r="184" customHeight="1" spans="3:11">
       <c r="C184" s="1">
         <v>40000229</v>
       </c>
@@ -6985,7 +6985,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="185" customHeight="1" spans="1:11">
+    <row r="185" customHeight="1" spans="3:11">
       <c r="C185" s="1">
         <v>40000230</v>
       </c>
@@ -7014,7 +7014,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="186" customHeight="1" spans="1:11">
+    <row r="186" customHeight="1" spans="3:11">
       <c r="C186" s="1">
         <v>40000231</v>
       </c>
@@ -7043,7 +7043,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="187" customHeight="1" spans="1:11">
+    <row r="187" customHeight="1" spans="3:11">
       <c r="C187" s="1">
         <v>40000232</v>
       </c>
@@ -7072,7 +7072,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="188" customHeight="1" spans="1:11">
+    <row r="188" customHeight="1" spans="3:11">
       <c r="C188" s="1">
         <v>40000233</v>
       </c>
@@ -7101,7 +7101,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="189" customHeight="1" spans="1:11">
+    <row r="189" customHeight="1" spans="3:11">
       <c r="C189" s="1">
         <v>40000234</v>
       </c>
@@ -7130,13 +7130,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="190" customHeight="1" spans="1:11">
-      <c r="A190" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="B190" s="1" t="s">
-        <v>222</v>
-      </c>
+    <row r="190" customHeight="1" spans="3:11">
       <c r="C190" s="1">
         <v>40000235</v>
       </c>
@@ -7147,7 +7141,7 @@
         <v>6</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G190" s="1">
         <v>2007</v>
@@ -7165,13 +7159,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="191" customHeight="1" spans="1:11">
-      <c r="A191" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="B191" s="1" t="s">
-        <v>222</v>
-      </c>
+    <row r="191" customHeight="1" spans="3:11">
       <c r="C191" s="1">
         <v>40000236</v>
       </c>
@@ -7182,7 +7170,7 @@
         <v>6</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="G191" s="1">
         <v>2008</v>
@@ -7200,13 +7188,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="192" customHeight="1" spans="1:11">
-      <c r="A192" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="B192" s="1" t="s">
-        <v>222</v>
-      </c>
+    <row r="192" customHeight="1" spans="3:11">
       <c r="C192" s="1">
         <v>40000237</v>
       </c>
@@ -7217,7 +7199,7 @@
         <v>6</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G192" s="1">
         <v>2009</v>
@@ -7236,12 +7218,6 @@
       </c>
     </row>
     <row r="193" customHeight="1" spans="1:11">
-      <c r="A193" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="B193" s="1" t="s">
-        <v>222</v>
-      </c>
       <c r="C193" s="1">
         <v>40000238</v>
       </c>
@@ -7252,7 +7228,7 @@
         <v>6</v>
       </c>
       <c r="F193" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G193" s="1">
         <v>2013</v>
@@ -7271,12 +7247,6 @@
       </c>
     </row>
     <row r="194" customHeight="1" spans="1:11">
-      <c r="A194" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="B194" s="1" t="s">
-        <v>222</v>
-      </c>
       <c r="C194" s="1">
         <v>40000239</v>
       </c>
@@ -7287,7 +7257,7 @@
         <v>6</v>
       </c>
       <c r="F194" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G194" s="1">
         <v>2003</v>
@@ -7307,10 +7277,10 @@
     </row>
     <row r="195" customHeight="1" spans="1:11">
       <c r="A195" s="1" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="C195" s="1">
         <v>40000240</v>
@@ -7342,10 +7312,10 @@
     </row>
     <row r="196" customHeight="1" spans="1:11">
       <c r="A196" s="1" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="C196" s="1">
         <v>40000241</v>
@@ -7377,10 +7347,10 @@
     </row>
     <row r="197" customHeight="1" spans="1:11">
       <c r="A197" s="1" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="C197" s="1">
         <v>40000242</v>
@@ -7412,10 +7382,10 @@
     </row>
     <row r="198" customHeight="1" spans="1:11">
       <c r="A198" s="1" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="C198" s="1">
         <v>40000243</v>
@@ -7447,10 +7417,10 @@
     </row>
     <row r="199" customHeight="1" spans="1:11">
       <c r="A199" s="1" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="C199" s="1">
         <v>40000244</v>
